--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN ISIDRO CUL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN ISIDRO CUL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC75"/>
+  <dimension ref="A1:AC78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1114,12 +1114,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>283799</t>
+          <t>109510</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>81300</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1129,17 +1129,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CITLALY ELIZABETH</t>
+          <t>FERNANDA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>LIZARRAGA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ESQUERRA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1149,63 +1149,79 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6871058742</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>6677480481</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MIN AVALENCIANA</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>26-09-1992</t>
+          <t>27-07-2001</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>citlaly_1992@hotmail.com</t>
+          <t>MARIALIZARRAGAGONZALES@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>18-03-2025 15:17:04</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>19-07-2022 11:32:55</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>04-02-2026 15:03:06</t>
+          <t>02-02-2026 12:03:30</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>04-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>02-02-2026 12:02:54</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1213,18 +1229,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26050522076690003121</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26050522008100002878</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1241,12 +1253,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>109510</t>
+          <t>283799</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7250</t>
+          <t>81300</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1256,17 +1268,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FERNANDA</t>
+          <t>CITLALY ELIZABETH</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LIZARRAGA</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>ESQUERRA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1276,79 +1288,63 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6677480481</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>MIN AVALENCIANA</t>
-        </is>
-      </c>
+          <t>6871058742</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>27-07-2001</t>
+          <t>26-09-1992</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>MARIALIZARRAGAGONZALES@HOTMAIL.COM</t>
+          <t>citlaly_1992@hotmail.com</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>19-07-2022 11:32:55</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>18-03-2025 15:17:04</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-02-2026 12:03:30</t>
+          <t>04-02-2026 15:03:06</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>02-02-2026 12:02:54</t>
-        </is>
-      </c>
+          <t>04-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1356,14 +1352,18 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26050522008100002878</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
+          <t>26050522076690003121</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1523,12 +1523,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>325665</t>
+          <t>340050</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22604</t>
+          <t>17868</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>XATZYRI YURALY</t>
+          <t xml:space="preserve">SUGEY </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t xml:space="preserve">CASTELLANOS </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AISPURO</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1558,10 +1558,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6864307582</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>6674722279</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ARTICULO 27</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1569,56 +1573,60 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>22-02-2008</t>
+          <t>28-08-1996</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>XATZYRIVALENZUELA656@GMAIL.COM</t>
+          <t>SUGEYCAASTG23@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>27-11-2025 16:11:06</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>02-02-2026 11:14:02</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>09-02-2026 10:18:24</t>
+          <t>06-02-2026 12:27:12</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr"/>
+          <t>06-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>06-02-2026 12:26:46</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1626,14 +1634,22 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26050522187630003547</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+          <t>26050522135370003356</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1777,12 +1793,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>340211</t>
+          <t>272287</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18029</t>
+          <t>69789</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1792,17 +1808,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MATTEA GUADALUPE</t>
+          <t>ENRIQUE FERNANDO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t xml:space="preserve">CUEN </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1812,28 +1828,28 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6674170714</t>
+          <t>6674136197</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>08-06-1998</t>
+          <t>25-09-1991</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>MATTEAGEG@GMAIL.COM</t>
+          <t>STARBLUEWIRELESS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-02-2026 15:24:37</t>
+          <t>07-01-2025 11:41:40</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1848,22 +1864,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-02-2026 15:32:28</t>
+          <t>19-02-2026 16:34:27</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1880,36 +1896,36 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26050522014630002901</t>
+          <t>26050522499150004636</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>340284</t>
+          <t>293161</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18102</t>
+          <t>90659</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1919,17 +1935,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELIZABETH </t>
+          <t>ALONSO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t xml:space="preserve">CAMPAÑA </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CABRERA</t>
+          <t>TOGO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1939,32 +1955,28 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6674631919</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>LOMAS DE SAN ISIDRO</t>
-        </is>
-      </c>
+          <t>6673244126</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>21-10-1985</t>
+          <t>14-10-2005</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>ECSS35064@GMAIL.COM</t>
+          <t>TOGOALONSO03@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-02-2026 16:43:43</t>
+          <t>15-05-2025 12:06:41</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1974,44 +1986,36 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-02-2026 16:49:13</t>
+          <t>16-02-2026 19:39:22</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>02-02-2026 16:49:03</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2019,36 +2023,36 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26050522017320002909</t>
+          <t>26040522408810002800</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>340294</t>
+          <t>340267</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18112</t>
+          <t>18085</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2058,17 +2062,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>JONATHAN ALEXIS</t>
+          <t>YAZMIN</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MACIAS</t>
+          <t>VALLE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>GAXIOLA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2078,32 +2082,32 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6672172754</t>
+          <t>6674799515</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BARRANCOS</t>
+          <t>VILLA BONITA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>24-01-1993</t>
+          <t>07-06-1976</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>JONATHANALEXISMACIASFLORES@GMAIL.COM</t>
+          <t>YAZVALLEG@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-02-2026 16:57:39</t>
+          <t>02-02-2026 16:29:51</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2124,7 +2128,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-02-2026 17:00:06</t>
+          <t>02-02-2026 16:34:26</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2134,7 +2138,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>02-02-2026 16:59:50</t>
+          <t>02-02-2026 16:33:26</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2154,7 +2158,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26050522017750002911</t>
+          <t>26050522016680002906</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2178,12 +2182,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>340302</t>
+          <t>340281</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18120</t>
+          <t>18099</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2193,17 +2197,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRANCISCO </t>
+          <t>CAMILA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>BURGOS</t>
+          <t>VALLE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2213,32 +2217,32 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6671777382</t>
+          <t>6731037377</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PRADOS DEL SOL</t>
+          <t>VILLA BONITA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>19-11-1990</t>
+          <t>20-08-2007</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>FRANCISCO123456789@HOTMAIL.COM</t>
+          <t>CAMILACAS0820@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-02-2026 17:06:58</t>
+          <t>02-02-2026 16:42:06</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2259,7 +2263,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-02-2026 17:10:35</t>
+          <t>02-02-2026 16:44:16</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2269,7 +2273,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>02-02-2026 17:10:24</t>
+          <t>02-02-2026 16:43:49</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2289,7 +2293,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26050522018100002915</t>
+          <t>26050522017120002908</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2301,24 +2305,24 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>340050</t>
+          <t>340288</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17868</t>
+          <t>18106</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2328,17 +2332,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUGEY </t>
+          <t>JESUS OSCAR</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTELLANOS </t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>ARAMBURO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2348,32 +2352,32 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6674722279</t>
+          <t>6671644312</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>ARTICULO 27</t>
+          <t>CAPISTRANO</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>28-08-1996</t>
+          <t>03-11-1982</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>SUGEYCAASTG23@GMAIL.COM</t>
+          <t>JOSCAR18203@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-02-2026 11:14:02</t>
+          <t>02-02-2026 16:51:17</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2394,17 +2398,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>06-02-2026 12:27:12</t>
+          <t>02-02-2026 16:55:47</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>06-02-2026 12:26:46</t>
+          <t>02-02-2026 16:55:14</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2414,7 +2418,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2424,19 +2428,11 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26050522135370003356</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>ABIGAIL AHUMADA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26050522017580002910</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
           <t>499</t>
@@ -2444,24 +2440,24 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>293161</t>
+          <t>340211</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90659</t>
+          <t>18029</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2471,17 +2467,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ALONSO</t>
+          <t>MATTEA GUADALUPE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMPAÑA </t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TOGO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2491,28 +2487,28 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6673244126</t>
+          <t>6674170714</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>14-10-2005</t>
+          <t>08-06-1998</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>TOGOALONSO03@GMAIL.COM</t>
+          <t>MATTEAGEG@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>15-05-2025 12:06:41</t>
+          <t>02-02-2026 15:24:37</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2527,28 +2523,28 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>16-02-2026 19:39:22</t>
+          <t>02-02-2026 15:32:28</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V16" t="inlineStr"/>
@@ -2559,36 +2555,36 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26040522408810002800</t>
+          <t>26050522014630002901</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>340267</t>
+          <t>340284</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18085</t>
+          <t>18102</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2598,17 +2594,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>YAZMIN</t>
+          <t xml:space="preserve">ELIZABETH </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>VALLE</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GAXIOLA</t>
+          <t>CABRERA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2618,12 +2614,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6674799515</t>
+          <t>6674631919</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>VILLA BONITA</t>
+          <t>LOMAS DE SAN ISIDRO</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2633,38 +2629,42 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>07-06-1976</t>
+          <t>21-10-1985</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>YAZVALLEG@GMAIL.COM</t>
+          <t>ECSS35064@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-02-2026 16:29:51</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>02-02-2026 16:43:43</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>02-02-2026 16:34:26</t>
+          <t>02-02-2026 16:49:13</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>02-02-2026 16:33:26</t>
+          <t>02-02-2026 16:49:03</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2694,14 +2694,14 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26050522016680002906</t>
+          <t>26050522017320002909</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2718,12 +2718,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>340281</t>
+          <t>340294</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18099</t>
+          <t>18112</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2733,17 +2733,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CAMILA</t>
+          <t>JONATHAN ALEXIS</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>MACIAS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VALLE</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2753,32 +2753,32 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6731037377</t>
+          <t>6672172754</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>VILLA BONITA</t>
+          <t>BARRANCOS</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>20-08-2007</t>
+          <t>24-01-1993</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CAMILACAS0820@GMAIL.COM</t>
+          <t>JONATHANALEXISMACIASFLORES@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>02-02-2026 16:42:06</t>
+          <t>02-02-2026 16:57:39</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>02-02-2026 16:44:16</t>
+          <t>02-02-2026 17:00:06</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>02-02-2026 16:43:49</t>
+          <t>02-02-2026 16:59:50</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26050522017120002908</t>
+          <t>26050522017750002911</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
@@ -2853,12 +2853,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>340288</t>
+          <t>322416</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18106</t>
+          <t>19355</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2868,17 +2868,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>JESUS OSCAR</t>
+          <t>LIZETH</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>CERVANTES</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ARAMBURO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2888,14 +2888,10 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6671644312</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>CAPISTRANO</t>
-        </is>
-      </c>
+          <t>6673117102</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2903,60 +2899,56 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>03-11-1982</t>
+          <t>28-04-1998</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>JOSCAR18203@GMAIL.COM</t>
+          <t>LIZETHCERVANTESS101@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-02-2026 16:51:17</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>06-11-2025 17:05:33</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>02-02-2026 16:55:47</t>
+          <t>03-02-2026 18:46:23</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>02-02-2026 16:55:14</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2964,36 +2956,36 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26050522017580002910</t>
+          <t>26050522054080003063</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>322416</t>
+          <t>340302</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19355</t>
+          <t>18120</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3003,17 +2995,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LIZETH</t>
+          <t xml:space="preserve">FRANCISCO </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CERVANTES</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>BURGOS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3023,10 +3015,14 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6673117102</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>6671777382</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>PRADOS DEL SOL</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3034,56 +3030,60 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>28-04-1998</t>
+          <t>19-11-1990</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>LIZETHCERVANTESS101@GMAIL.COM</t>
+          <t>FRANCISCO123456789@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>06-11-2025 17:05:33</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>02-02-2026 17:06:58</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>03-02-2026 18:46:23</t>
+          <t>02-02-2026 17:10:35</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>02-02-2026 17:10:24</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3091,14 +3091,14 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26050522054080003063</t>
+          <t>26050522018100002915</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3115,12 +3115,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>341183</t>
+          <t>340062</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19001</t>
+          <t>17880</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3130,17 +3130,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ISAAC ALEJANDRO</t>
+          <t>MIGUEL ALBERTO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PICOS</t>
+          <t>VELARDE</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3150,10 +3150,14 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6675823775</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>6674054276</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>PARQUE ANDARES</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3161,52 +3165,60 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>21-08-2006</t>
+          <t>03-04-2002</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ISAACLLANES999@GMAIL.COM</t>
+          <t>SERGIOMESSI334@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>04-02-2026 20:01:05</t>
+          <t>02-02-2026 11:31:11</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>16-02-2026 19:00:46</t>
+          <t>02-02-2026 11:39:13</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>02-02-2026 11:34:23</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3214,32 +3226,24 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26050522406720004345</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
-        </is>
-      </c>
+          <t>26050522007440002876</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -3373,12 +3377,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>340062</t>
+          <t>340051</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17880</t>
+          <t>17869</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3388,17 +3392,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MIGUEL ALBERTO</t>
+          <t>JOSUE ARMANDO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>MORGA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>VELARDE</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3408,12 +3412,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6674054276</t>
+          <t>6673455280</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>PARQUE ANDARES</t>
+          <t xml:space="preserve">C. HACIENDA DEL CONDE 5818 </t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3423,17 +3427,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>03-04-2002</t>
+          <t>20-02-2002</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>SERGIOMESSI334@GMAIL.COM</t>
+          <t>JOSUEMORGA2001@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>02-02-2026 11:31:11</t>
+          <t>02-02-2026 11:14:09</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3454,7 +3458,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>02-02-2026 11:39:13</t>
+          <t>02-02-2026 11:17:38</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3464,7 +3468,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>02-02-2026 11:34:23</t>
+          <t>02-02-2026 11:17:07</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3484,7 +3488,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26050522007440002876</t>
+          <t>26050522006620002874</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -3496,12 +3500,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -3635,12 +3639,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>340051</t>
+          <t>325665</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17869</t>
+          <t>22604</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3650,17 +3654,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>JOSUE ARMANDO</t>
+          <t>XATZYRI YURALY</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MORGA</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t>AISPURO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3670,75 +3674,67 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6673455280</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C. HACIENDA DEL CONDE 5818 </t>
-        </is>
-      </c>
+          <t>6864307582</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>20-02-2002</t>
+          <t>22-02-2008</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>JOSUEMORGA2001@GMAIL.COM</t>
+          <t>XATZYRIVALENZUELA656@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>02-02-2026 11:14:09</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>27-11-2025 16:11:06</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>02-02-2026 11:17:38</t>
+          <t>09-02-2026 10:18:24</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>02-02-2026 11:17:07</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3746,14 +3742,14 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26050522006620002874</t>
+          <t>26050522187630003547</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -3770,12 +3766,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>340278</t>
+          <t>341538</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18096</t>
+          <t>19356</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3785,17 +3781,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DIEGO</t>
+          <t>JACIEL MANUEL</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>CASTELLANOS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>VALLE</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3805,12 +3801,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6672689990</t>
+          <t>6677900100</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>VILLA BONITA</t>
+          <t>ARTICULO 27 3491</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3820,20 +3816,24 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>12-03-2004</t>
+          <t>30-03-1991</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>DIEGOCASTROVALLE1@GMAIL.COM</t>
+          <t>JACIEL.CASTELLANOS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>02-02-2026 16:38:29</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>06-02-2026 12:12:23</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3851,17 +3851,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>02-02-2026 16:41:10</t>
+          <t>17-02-2026 10:58:43</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>02-02-2026 16:40:49</t>
+          <t>17-02-2026 10:56:07</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3881,11 +3881,19 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26050522017020002907</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
+          <t>26050522424560004401</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>499</t>
@@ -3893,7 +3901,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3905,12 +3913,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>342046</t>
+          <t>341584</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19864</t>
+          <t>19402</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3920,19 +3928,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>KASSANDRA</t>
+          <t>IRVING ADOLFO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>FELIX</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>SANCHEZ</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>VIDAL</t>
-        </is>
-      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>52</t>
@@ -3940,67 +3948,63 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6673286036</t>
+          <t>6674711600</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MARIANO CARLON 4931</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>02-12-2004</t>
+          <t>28-11-1999</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>KASSANDRASANCH@GMAIL.COM</t>
+          <t>ADOLFO_IAFS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>09-02-2026 08:07:39</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>06-02-2026 14:45:39</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>09-02-2026 08:15:43</t>
+          <t>06-02-2026 14:49:50</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>06-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>09-02-2026 08:15:18</t>
+          <t>06-02-2026 14:49:22</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4020,36 +4024,36 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26050522184630003535</t>
+          <t>26050522137710003362</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>342052</t>
+          <t>342046</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19870</t>
+          <t>19864</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4059,17 +4063,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AMAYRANI YESSENIA</t>
+          <t>KASSANDRA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUINTERO </t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANDRADE </t>
+          <t>VIDAL</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4079,12 +4083,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6674832993</t>
+          <t>6673286036</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>JOEGE ROMERO ZAZUETA 2306</t>
+          <t>MARIANO CARLON 4931</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4094,38 +4098,42 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>21-11-2001</t>
+          <t>02-12-2004</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>AMAYRANI_QUINTERO@HOTMAIL.COM</t>
+          <t>KASSANDRASANCH@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>09-02-2026 08:35:57</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>09-02-2026 08:07:39</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>09-02-2026 08:46:58</t>
+          <t>09-02-2026 08:15:43</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -4135,7 +4143,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>09-02-2026 08:46:15</t>
+          <t>09-02-2026 08:15:18</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4155,14 +4163,14 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26050522185300003537</t>
+          <t>26050522184630003535</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -4179,12 +4187,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>342107</t>
+          <t>342052</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19925</t>
+          <t>19870</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4194,17 +4202,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NAUN ALAN</t>
+          <t>AMAYRANI YESSENIA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CHIQUETE</t>
+          <t xml:space="preserve">QUINTERO </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PALOMAREZ</t>
+          <t xml:space="preserve">ANDRADE </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4214,32 +4222,32 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6677976901</t>
+          <t>6674832993</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CERRO DEL CHIQUIHUITE</t>
+          <t>JOEGE ROMERO ZAZUETA 2306</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>02-02-1994</t>
+          <t>21-11-2001</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>NAUNALANCHIQUETE@GMAIL.COM</t>
+          <t>AMAYRANI_QUINTERO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>09-02-2026 11:16:00</t>
+          <t>09-02-2026 08:35:57</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4260,7 +4268,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>09-02-2026 11:18:05</t>
+          <t>09-02-2026 08:46:58</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -4270,7 +4278,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>09-02-2026 11:17:49</t>
+          <t>09-02-2026 08:46:15</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4280,7 +4288,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4290,7 +4298,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26050522188750003551</t>
+          <t>26050522185300003537</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
@@ -4302,7 +4310,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4314,12 +4322,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>342347</t>
+          <t>342107</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>19925</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4329,17 +4337,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>JAVIER GEOVANY</t>
+          <t>NAUN ALAN</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PELAYO</t>
+          <t>CHIQUETE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AVILA</t>
+          <t>PALOMAREZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4349,10 +4357,14 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6671055592</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>6677976901</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>CERRO DEL CHIQUIHUITE</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4360,52 +4372,60 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>08-11-2013</t>
+          <t>02-02-1994</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>JAVPA@GMAIL.COM</t>
+          <t>NAUNALANCHIQUETE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>09-02-2026 17:43:15</t>
+          <t>09-02-2026 11:16:00</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>10-02-2026 16:37:12</t>
+          <t>09-02-2026 11:18:05</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>10-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>09-02-2026 11:17:49</t>
+        </is>
+      </c>
       <c r="U30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4413,44 +4433,36 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26050522237050003717</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>ABIGAIL AHUMADA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26050522188750003551</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>341209</t>
+          <t>342306</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19027</t>
+          <t>20124</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4460,17 +4472,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ROCIO MARGARITA</t>
+          <t xml:space="preserve">AYELIN YAMILETH </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>CORRALES</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CIFUENTES</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4480,12 +4492,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6673305169</t>
+          <t>6674237913</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CAPISTRANO</t>
+          <t>CHULAVISTA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4495,48 +4507,52 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>19-08-1971</t>
+          <t>17-09-2001</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CRED9011037@GMAIL.COM</t>
+          <t>AYELENCORRALES52@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>05-02-2026 05:19:52</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>09-02-2026 17:10:32</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>05-02-2026 05:25:19</t>
+          <t>09-02-2026 17:15:55</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>05-02-2026 05:25:01</t>
+          <t>09-02-2026 17:15:08</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4556,36 +4572,36 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26050522097780003210</t>
+          <t>26050522201360003593</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>341210</t>
+          <t>342024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19028</t>
+          <t>19842</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4595,17 +4611,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ODALIZ BRISEIDA</t>
+          <t>AYAMARA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PATRON</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4615,12 +4631,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6671988044</t>
+          <t>6673527007</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>CAPISTRANO</t>
+          <t>CERRO DE PUNTA OESTE 743</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4630,17 +4646,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>10-04-2002</t>
+          <t>13-11-2005</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>PATRON.QUINTERO.ODALIZ18@GMAIL.COM</t>
+          <t>AYAMARAHERNANDEZ05@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>05-02-2026 05:31:53</t>
+          <t>09-02-2026 07:10:48</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4661,17 +4677,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>05-02-2026 05:36:08</t>
+          <t>09-02-2026 07:26:58</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>05-02-2026 05:35:58</t>
+          <t>09-02-2026 07:22:21</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4691,7 +4707,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26050522097920003212</t>
+          <t>26050522183300003529</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
@@ -4715,12 +4731,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>341416</t>
+          <t>340278</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19234</t>
+          <t>18096</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4730,17 +4746,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">OLIVER </t>
+          <t>DIEGO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SIMENTAL</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>URTUSUASTEGUI</t>
+          <t>VALLE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4750,10 +4766,14 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6672988277</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>6672689990</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>VILLA BONITA</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4761,56 +4781,60 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>07-09-2003</t>
+          <t>12-03-2004</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>OLIVER4647@ICLOUD.COM</t>
+          <t>DIEGOCASTROVALLE1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>05-02-2026 18:15:05</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>02-02-2026 16:38:29</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>05-02-2026 18:16:32</t>
+          <t>02-02-2026 16:41:10</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>02-02-2026 16:40:49</t>
+        </is>
+      </c>
       <c r="U33" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4818,19 +4842,19 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26050522115260003288</t>
+          <t>26050522017020002907</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Hector Noe Espinoza Ramirez</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4842,12 +4866,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>341538</t>
+          <t>342054</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19356</t>
+          <t>19872</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4857,17 +4881,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>JACIEL MANUEL</t>
+          <t>YAZMIN</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CASTELLANOS</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4877,39 +4901,35 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6677900100</t>
+          <t>8186031726</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>ARTICULO 27 3491</t>
+          <t>DE LAS VEREDAS</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>30-03-1991</t>
+          <t>28-07-2001</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>JACIEL.CASTELLANOS@HOTMAIL.COM</t>
+          <t>YAZ.LOPEZ17@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>06-02-2026 12:12:23</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 08:38:56</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4927,17 +4947,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>17-02-2026 10:58:43</t>
+          <t>09-02-2026 08:54:38</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>17-02-2026 10:56:07</t>
+          <t>09-02-2026 08:52:19</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4957,19 +4977,11 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26050522424560004401</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>ABIGAIL AHUMADA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26050522185440003538</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
           <t>499</t>
@@ -4989,12 +5001,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>341584</t>
+          <t>342363</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>19402</t>
+          <t>20181</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5004,17 +5016,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>IRVING ADOLFO</t>
+          <t>SILVIA GUADALUPE</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>LINDORO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5024,32 +5036,32 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6674711600</t>
+          <t>6671844971</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>28-11-1999</t>
+          <t>26-06-1996</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>ADOLFO_IAFS@HOTMAIL.COM</t>
+          <t>SILVIA_ML13@HOTMA.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>06-02-2026 14:45:39</t>
+          <t>09-02-2026 17:59:28</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -5070,17 +5082,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>06-02-2026 14:49:50</t>
+          <t>09-02-2026 18:06:03</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>06-02-2026 14:49:22</t>
+          <t>09-02-2026 18:03:54</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5100,7 +5112,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26050522137710003362</t>
+          <t>26050522205370003618</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5124,12 +5136,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>342363</t>
+          <t>339936</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20181</t>
+          <t>17754</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5139,17 +5151,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SILVIA GUADALUPE</t>
+          <t>HECTOR ALEJANDRO</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>LINDORO</t>
+          <t>IRIBE</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5159,75 +5171,67 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6671844971</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>6674294024</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>26-06-1996</t>
+          <t>15-07-2009</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>SILVIA_ML13@HOTMA.COM</t>
+          <t>HAIRO90715@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>09-02-2026 17:59:28</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>02-02-2026 09:08:54</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>09-02-2026 18:06:03</t>
+          <t>02-02-2026 09:10:01</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>09-02-2026 18:03:54</t>
-        </is>
-      </c>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5235,36 +5239,36 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26050522205370003618</t>
+          <t>26050522002290002854</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>342054</t>
+          <t>342376</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>19872</t>
+          <t>20194</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5274,17 +5278,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>YAZMIN</t>
+          <t>DANIEL SEBASTIAN</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5294,14 +5298,10 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8186031726</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>DE LAS VEREDAS</t>
-        </is>
-      </c>
+          <t>6671384521</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5309,38 +5309,42 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>28-07-2001</t>
+          <t>15-05-2009</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>YAZ.LOPEZ17@OUTLOOK.COM</t>
+          <t>DANIELCASTRO09410315@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>09-02-2026 08:38:56</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>09-02-2026 18:13:14</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>09-02-2026 08:54:38</t>
+          <t>09-02-2026 18:15:27</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -5348,21 +5352,13 @@
           <t>09-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>09-02-2026 08:52:19</t>
-        </is>
-      </c>
+      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5370,19 +5366,19 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26050522185440003538</t>
+          <t>26050522206250003624</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5394,12 +5390,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>342024</t>
+          <t>342649</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>19842</t>
+          <t>20466</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5409,17 +5405,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AYAMARA</t>
+          <t>MARIA FERNANDA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MONTOYA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>ZAZUETA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5429,12 +5425,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6673527007</t>
+          <t>6674603292</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>CERRO DE PUNTA OESTE 743</t>
+          <t>LOMAS</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5444,17 +5440,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>13-11-2005</t>
+          <t>14-06-2011</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>AYAMARAHERNANDEZ05@GMAIL.COM</t>
+          <t>MARIAFERNANDA19@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>09-02-2026 07:10:48</t>
+          <t>10-02-2026 14:53:32</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5475,17 +5471,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>09-02-2026 07:26:58</t>
+          <t>10-02-2026 14:57:06</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>09-02-2026 07:22:21</t>
+          <t>10-02-2026 14:56:25</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5505,7 +5501,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26050522183300003529</t>
+          <t>26050522233480003703</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
@@ -5517,12 +5513,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -5664,12 +5660,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>342649</t>
+          <t>340032</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20466</t>
+          <t>17850</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5679,17 +5675,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA</t>
+          <t>KEVIN ARON</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>MONTOYA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ZAZUETA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5699,32 +5695,32 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6674603292</t>
+          <t>6673555568</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>LOMAS</t>
+          <t>URBIVILLAS DEL SOL 2676</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>14-06-2011</t>
+          <t>13-10-2006</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>MARIAFERNANDA19@GMAIL.COM</t>
+          <t>KAEVINGONZALEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>10-02-2026 14:53:32</t>
+          <t>02-02-2026 10:55:15</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5745,17 +5741,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>10-02-2026 14:57:06</t>
+          <t>02-02-2026 11:13:58</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>10-02-2026 14:56:25</t>
+          <t>02-02-2026 11:13:24</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5775,7 +5771,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26050522233480003703</t>
+          <t>26050522006460002873</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
@@ -5787,24 +5783,24 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>342306</t>
+          <t>340044</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20124</t>
+          <t>17862</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5814,17 +5810,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">AYELIN YAMILETH </t>
+          <t xml:space="preserve">MARIA FERNANDA </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CORRALES</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>PAREDES</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5834,12 +5830,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6674237913</t>
+          <t>6672539772</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>CHULAVISTA</t>
+          <t>C ARTICULO 27 3491</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5849,52 +5845,48 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>17-09-2001</t>
+          <t>18-01-1998</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>AYELENCORRALES52@GMAIL.COM</t>
+          <t>FERNANDAPAREDESS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>09-02-2026 17:10:32</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>02-02-2026 11:10:29</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>09-02-2026 17:15:55</t>
+          <t>06-02-2026 12:24:08</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>06-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>09-02-2026 17:15:08</t>
+          <t>06-02-2026 12:23:13</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5914,14 +5906,22 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26050522201360003593</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
+          <t>26050522135340003355</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -5938,12 +5938,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>343951</t>
+          <t>341209</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>21768</t>
+          <t>19027</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5953,17 +5953,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ADILENE BERENYCE</t>
+          <t>ROCIO MARGARITA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDINA </t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>CIFUENTES</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6674304996</t>
+          <t>6673305169</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>COLINAS DE AMBAR 4640</t>
+          <t>CAPISTRANO</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5988,24 +5988,20 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>22-10-1990</t>
+          <t>19-08-1971</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>BERECARDENAS102@GMAIL.COM</t>
+          <t>CRED9011037@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>16-02-2026 07:28:02</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>05-02-2026 05:19:52</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6023,17 +6019,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>16-02-2026 07:35:05</t>
+          <t>05-02-2026 05:25:19</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>16-02-2026 07:34:19</t>
+          <t>05-02-2026 05:25:01</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6053,7 +6049,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26050522379390004219</t>
+          <t>26050522097780003210</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -6065,24 +6061,24 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>344219</t>
+          <t>341210</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>22036</t>
+          <t>19028</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6092,17 +6088,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>JETSSY YERANI</t>
+          <t>ODALIZ BRISEIDA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>PATRON</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6112,12 +6108,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6671955010</t>
+          <t>6671988044</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>PRADOS</t>
+          <t>CAPISTRANO</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6127,52 +6123,48 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>01-11-2002</t>
+          <t>10-04-2002</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CHJETSSY@GMAIL.COM</t>
+          <t>PATRON.QUINTERO.ODALIZ108@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>16-02-2026 17:35:23</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>05-02-2026 05:31:53</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>16-02-2026 17:40:31</t>
+          <t>05-02-2026 05:36:08</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>16-02-2026 17:39:31</t>
+          <t>05-02-2026 05:35:58</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6192,36 +6184,36 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26050522400210004318</t>
+          <t>26050522097920003212</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>342376</t>
+          <t>341416</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20194</t>
+          <t>19234</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6231,17 +6223,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DANIEL SEBASTIAN</t>
+          <t xml:space="preserve">OLIVER </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>SIMENTAL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>URTUSUASTEGUI</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6251,28 +6243,28 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6671384521</t>
+          <t>6672988277</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>15-05-2009</t>
+          <t>07-09-2003</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>DANIELCASTRO09410315@GMAIL.COM</t>
+          <t>OLIVER4647@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>09-02-2026 18:13:14</t>
+          <t>05-02-2026 18:15:05</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6287,28 +6279,28 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>09-02-2026 18:15:27</t>
+          <t>05-02-2026 18:16:32</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V44" t="inlineStr"/>
@@ -6319,19 +6311,19 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26050522206250003624</t>
+          <t>26050522115260003288</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>Hector Noe Espinoza Ramirez</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6343,12 +6335,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>339936</t>
+          <t>341183</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17754</t>
+          <t>19001</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6358,17 +6350,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HECTOR ALEJANDRO</t>
+          <t>ISAAC ALEJANDRO</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>IRIBE</t>
+          <t>PICOS</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6378,7 +6370,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6674294024</t>
+          <t>6675823775</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6389,24 +6381,20 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>15-07-2009</t>
+          <t>21-08-2006</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>HAIRO90715@GMAIL.COM</t>
+          <t>ISAACLLANES999@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>02-02-2026 09:08:54</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>04-02-2026 20:01:05</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -6414,28 +6402,28 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>02-02-2026 09:10:01</t>
+          <t>16-02-2026 19:00:46</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>16-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V45" t="inlineStr"/>
@@ -6446,36 +6434,44 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26050522002290002854</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
+          <t>26050522406720004345</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>340032</t>
+          <t>343144</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>17850</t>
+          <t>20961</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6485,17 +6481,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>KEVIN ARON</t>
+          <t>VICTORIA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>OJEDA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6505,38 +6501,38 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6673555568</t>
+          <t>6673796592</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>URBIVILLAS DEL SOL 2676</t>
+          <t>PAULINO MACHORRO1896</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>13-10-2006</t>
+          <t>17-11-1994</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>KAEVINGONZALEZ@GMAIL.COM</t>
+          <t>VICTORIAOJEDAAAA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>02-02-2026 10:55:15</t>
+          <t>11-02-2026 21:38:13</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6551,29 +6547,21 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>02-02-2026 11:13:58</t>
+          <t>13-02-2026 19:49:17</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>02-02-2026 11:13:24</t>
-        </is>
-      </c>
+          <t>14-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6581,11 +6569,19 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26050522006460002873</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
+          <t>26050522330490004130</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>Carmen Michel Navarrete  Nevarez</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>499</t>
@@ -6593,24 +6589,24 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>344330</t>
+          <t>343449</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>22147</t>
+          <t>21266</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6620,17 +6616,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CRISTOPHER LUCIANO</t>
+          <t>BIANCA AZUCENA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ZAVALA</t>
+          <t>LANDELL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ANGULO</t>
+          <t>PARRA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6640,67 +6636,75 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6671833791</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>6674842233</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>MINA DEL PEÑON BLANCO 560</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>04-09-2013</t>
+          <t>21-12-2000</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLOSETYCOCINASSR@GMAIL.COM</t>
+          <t>BIANCALANDELL21@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>16-02-2026 19:04:29</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>13-02-2026 09:39:01</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>16-02-2026 19:14:09</t>
+          <t>13-02-2026 09:48:06</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>13-02-2026 09:45:49</t>
+        </is>
+      </c>
       <c r="U47" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6708,36 +6712,36 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26050522407600004347</t>
+          <t>26050522317680004073</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>342176</t>
+          <t>343859</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>19994</t>
+          <t>21676</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6747,17 +6751,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ALMA LILIA</t>
+          <t>CLAUDIA LIBERTAD</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>PORTILLO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SAMANO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6767,12 +6771,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6676020923</t>
+          <t>6674275957</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>PASEO HIMALAYAS</t>
+          <t>PRADOS DEL SOL</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6782,17 +6786,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>09-01-1989</t>
+          <t>11-10-1995</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>QUINTEROALMA733@GMAIL.COM</t>
+          <t>LIBERTAD-PORTILLO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>09-02-2026 14:27:03</t>
+          <t>15-02-2026 13:41:31</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -6803,7 +6807,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -6813,17 +6817,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>09-02-2026 14:33:43</t>
+          <t>15-02-2026 13:45:48</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>09-02-2026 14:31:37</t>
+          <t>15-02-2026 13:45:01</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6843,7 +6847,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26050522193270003559</t>
+          <t>26050522366990004185</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
@@ -6867,12 +6871,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>342351</t>
+          <t>341207</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20169</t>
+          <t>19025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6882,17 +6886,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CAROLINA</t>
+          <t>FRANCISCO ALEJANDRO</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>PEÑUELAS</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6902,32 +6906,32 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6674744257</t>
+          <t>6673168474</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>LOMAS</t>
+          <t>MANUEL PAYNO 2161</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>08-04-1994</t>
+          <t>25-10-1997</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CAROLINASOTO.MKT@GMAIL.COM</t>
+          <t>ALEX209725@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>09-02-2026 17:48:21</t>
+          <t>05-02-2026 04:45:19</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6948,17 +6952,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>09-02-2026 17:53:10</t>
+          <t>10-02-2026 04:46:51</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>09-02-2026 17:52:28</t>
+          <t>10-02-2026 04:44:41</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -6968,7 +6972,7 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -6978,11 +6982,19 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26050522204390003615</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
+          <t>26050522216510003662</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>499</t>
@@ -7002,12 +7014,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>343449</t>
+          <t>344402</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21266</t>
+          <t>22219</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7017,17 +7029,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>BIANCA AZUCENA</t>
+          <t>LESLY LIZBETH</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>LANDELL</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>PARRA</t>
+          <t>ALBA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7037,14 +7049,10 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6674842233</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>MINA DEL PEÑON BLANCO 560</t>
-        </is>
-      </c>
+          <t>6679956390</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7052,60 +7060,56 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>21-12-2000</t>
+          <t>20-12-2011</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>BIANCALANDELL@GMAIL.COM</t>
+          <t>ALBALESLY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>13-02-2026 09:39:01</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>17-02-2026 07:40:14</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>13-02-2026 09:48:06</t>
+          <t>17-02-2026 08:27:15</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>13-02-2026 09:45:49</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7113,36 +7117,36 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26050522317680004073</t>
+          <t>26050522421850004396</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>344602</t>
+          <t>344004</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>22419</t>
+          <t>21821</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7152,17 +7156,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ROXANA GABRIELA</t>
+          <t>IVAN JARETH</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SAMANIEGO</t>
+          <t xml:space="preserve">HIRATA </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7172,12 +7176,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6471226799</t>
+          <t>6672295585</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>C MIGUEL HIDALGO</t>
+          <t>CERRO CULIACAN 1391</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7187,17 +7191,17 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>23-11-1999</t>
+          <t>04-10-1996</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>ROXANASAMANIEGO487@GMAIL.COM</t>
+          <t>C98667145@COPPEL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>17-02-2026 17:21:04</t>
+          <t>16-02-2026 10:33:07</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7222,17 +7226,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>17-02-2026 17:25:35</t>
+          <t>16-02-2026 10:58:09</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>17-02-2026 17:24:51</t>
+          <t>16-02-2026 10:41:22</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -7252,7 +7256,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26050522437350004443</t>
+          <t>26050522384690004236</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr"/>
@@ -7276,12 +7280,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>340044</t>
+          <t>344058</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>17862</t>
+          <t>21875</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7291,17 +7295,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA FERNANDA </t>
+          <t xml:space="preserve">ADRIAN ALEJANDRO </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>GAMBOA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>PAREDES</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7311,75 +7315,67 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6672539772</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>C ARTICULO 27 3491</t>
-        </is>
-      </c>
+          <t>2212182749</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>18-01-1998</t>
+          <t>01-01-2000</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>FERNANDAPAREDESS@HOTMAIL.COM</t>
+          <t>AGAMBOA515@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>02-02-2026 11:10:29</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>16-02-2026 12:55:37</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>06-02-2026 12:24:08</t>
+          <t>16-02-2026 17:16:42</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>06-02-2026 12:23:13</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7387,22 +7383,14 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26050522135340003355</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>ABIGAIL AHUMADA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26050522398420004302</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
@@ -7419,12 +7407,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>342708</t>
+          <t>342176</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20525</t>
+          <t>19994</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7434,17 +7422,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>JESUS ANTONIO</t>
+          <t>ALMA LILIA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">AISPURO </t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>IMPERIAL</t>
+          <t>SAMANO</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7454,12 +7442,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6671966948</t>
+          <t>6676020923</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ALTURAS</t>
+          <t>PASEO HIMALAYAS</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7469,17 +7457,17 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>03-09-1998</t>
+          <t>09-01-1989</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>AISPUROIMPERIALJESUSANTONIO@GMAIL.COM</t>
+          <t>QUINTEROALMA733@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>10-02-2026 16:30:39</t>
+          <t>09-02-2026 14:27:03</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -7500,17 +7488,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>10-02-2026 16:35:19</t>
+          <t>09-02-2026 14:33:43</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>10-02-2026 16:34:48</t>
+          <t>09-02-2026 14:31:37</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -7520,7 +7508,7 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -7530,7 +7518,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26050522236970003716</t>
+          <t>26050522193270003559</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
@@ -7542,24 +7530,24 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>343859</t>
+          <t>342351</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21676</t>
+          <t>20169</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7569,17 +7557,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CLAUDIA LIBERTAD</t>
+          <t>CAROLINA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>PORTILLO</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7589,12 +7577,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6674275957</t>
+          <t>6674744257</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>PRADOS DEL SOL</t>
+          <t>LOMAS</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7604,17 +7592,17 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>11-10-1995</t>
+          <t>08-04-1994</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>LIBERTAD-PORTILLO@HOTMAIL.COM</t>
+          <t>CAROLINASOTO.MKT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>15-02-2026 13:41:31</t>
+          <t>09-02-2026 17:48:21</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -7625,7 +7613,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -7635,17 +7623,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>15-02-2026 13:45:48</t>
+          <t>09-02-2026 17:53:10</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>15-02-2026 13:45:01</t>
+          <t>09-02-2026 17:52:28</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -7655,7 +7643,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7665,7 +7653,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26050522366990004185</t>
+          <t>26050522204390003615</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr"/>
@@ -7689,12 +7677,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>343144</t>
+          <t>344007</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20961</t>
+          <t>21824</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7704,17 +7692,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VICTORIA</t>
+          <t>JOSE LUIS</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>OJEDA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7724,38 +7712,42 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6673796592</t>
+          <t>6671901876</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>PAULINO MACHORRO1896</t>
+          <t>CERRO DEL TENAYO 1285</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>17-11-1994</t>
+          <t>08-10-1988</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>VICTORIAOJEDAAAA@GMAIL.COM</t>
+          <t>JOSELUISDIAZRIVERA68@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>11-02-2026 21:38:13</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>16-02-2026 10:51:16</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -7770,21 +7762,29 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>13-02-2026 19:49:17</t>
+          <t>16-02-2026 10:56:29</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>16-02-2026 10:55:40</t>
+        </is>
+      </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W55" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7792,19 +7792,11 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26050522330490004130</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>Carmen Michel Navarrete  Nevarez</t>
-        </is>
-      </c>
+          <t>26050522384660004235</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
           <t>499</t>
@@ -7812,24 +7804,24 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>344004</t>
+          <t>344100</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21821</t>
+          <t>21917</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7839,17 +7831,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>IVAN JARETH</t>
+          <t>AIDEE</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">HIRATA </t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>CORRALES</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7859,57 +7851,53 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6672295585</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>CERRO CULIACAN 1391</t>
-        </is>
-      </c>
+          <t>6673888721</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>04-10-1996</t>
+          <t>02-08-2004</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>C98667145@COPPEL.COM</t>
+          <t>AUDEESITI84@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>16-02-2026 10:33:07</t>
+          <t>16-02-2026 14:42:18</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>16-02-2026 10:58:09</t>
+          <t>16-02-2026 14:44:30</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -7917,21 +7905,13 @@
           <t>16-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>16-02-2026 10:41:22</t>
-        </is>
-      </c>
+      <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7939,14 +7919,14 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26050522384690004236</t>
+          <t>26050522390910004257</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
@@ -7963,12 +7943,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>344058</t>
+          <t>345351</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21875</t>
+          <t>87516</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7978,17 +7958,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADRIAN ALEJANDRO </t>
+          <t>ROSA LAURA</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>GAMBOA</t>
+          <t>ALBA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -7998,35 +7978,31 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2212182749</t>
+          <t>6676945948</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>01-01-2000</t>
+          <t>12-06-1986</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>AGAMBOA515@GMAIL.COM</t>
+          <t>178563586@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>16-02-2026 12:55:37</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>20-02-2026 17:09:02</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -8034,22 +8010,22 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>16-02-2026 17:16:42</t>
+          <t>20-02-2026 17:31:55</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>21-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
@@ -8066,14 +8042,22 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26050522398420004302</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
+          <t>26050522531930004755</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
@@ -8090,12 +8074,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>342728</t>
+          <t>344114</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>20545</t>
+          <t>21931</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8105,17 +8089,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SANTIAGO</t>
+          <t>ALEJANDRO GUADALUPE</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RUBI</t>
+          <t xml:space="preserve">LEON </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>NAVARRETE</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8125,7 +8109,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6674364372</t>
+          <t>6673888815</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -8136,17 +8120,17 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>17-09-2010</t>
+          <t>25-12-2008</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>SANTI.RUBI102@GMAIL.COM</t>
+          <t>ALEXLEONLOPEZ08@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>10-02-2026 16:59:03</t>
+          <t>16-02-2026 15:08:28</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -8161,28 +8145,28 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>10-02-2026 17:12:49</t>
+          <t>17-02-2026 14:06:24</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V58" t="inlineStr"/>
@@ -8193,14 +8177,14 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26050522238860003735</t>
+          <t>26050522428770004410</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
@@ -8217,12 +8201,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>344114</t>
+          <t>344151</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21931</t>
+          <t>21968</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8232,17 +8216,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ALEJANDRO GUADALUPE</t>
+          <t>JOSE</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEON </t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>ACEVO</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8252,7 +8236,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6673888815</t>
+          <t>6673549962</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8263,24 +8247,20 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>25-12-2008</t>
+          <t>28-01-1989</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>ALEXLEONLOPEZ08@GMAIL.COM</t>
+          <t>JOSUE.MDZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>16-02-2026 15:08:28</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>16-02-2026 16:17:24</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -8288,28 +8268,28 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>17-02-2026 14:06:24</t>
+          <t>16-02-2026 16:20:42</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>16-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V59" t="inlineStr"/>
@@ -8320,14 +8300,14 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26050522428770004410</t>
+          <t>26050522395110004278</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
@@ -8344,12 +8324,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>344151</t>
+          <t>342347</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21968</t>
+          <t>20165</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8359,17 +8339,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>JAVIER GEOVANY</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>PELAYO</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ACEVO</t>
+          <t>AVILA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8379,7 +8359,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>6673549962</t>
+          <t>6671055592</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -8390,17 +8370,17 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>28-01-1989</t>
+          <t>08-11-2013</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>JOSUE.MDZA@GMAIL.COM</t>
+          <t>JAVPA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>16-02-2026 16:17:24</t>
+          <t>09-02-2026 17:43:15</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -8421,12 +8401,12 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>16-02-2026 16:20:42</t>
+          <t>10-02-2026 16:37:12</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
+          <t>10-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T60" t="inlineStr"/>
@@ -8443,11 +8423,19 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26050522395110004278</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
+          <t>26050522237050003717</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>1899</t>
@@ -8467,12 +8455,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>344007</t>
+          <t>344408</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21824</t>
+          <t>22225</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8482,17 +8470,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>JOSE LUIS</t>
+          <t>CLAUDIA VIANEY</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>CHAVARIN</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8502,79 +8490,63 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>6671901876</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>CERRO DEL TENAYO 1285</t>
-        </is>
-      </c>
+          <t>6677853393</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>08-10-1988</t>
+          <t>19-07-1994</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>JOSELUISDIAZRIVERA68@GMAIL.COM</t>
+          <t>EMIR.DAN103@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>16-02-2026 10:51:16</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>17-02-2026 08:06:40</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>16-02-2026 10:56:29</t>
+          <t>19-02-2026 07:41:19</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>16-02-2026 10:55:40</t>
-        </is>
-      </c>
+          <t>19-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8582,36 +8554,44 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26050522384660004235</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
+          <t>26050522488330004601</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>344100</t>
+          <t>344563</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21917</t>
+          <t>22380</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8621,17 +8601,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>AIDEE</t>
+          <t>JESUS ADRIAN</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CORRALES</t>
+          <t>POMPA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8641,67 +8621,79 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6673888721</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>6672490628</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>VOLCAN S</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>02-08-2004</t>
+          <t>15-07-1987</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>AUDEESITI84@GMAIL.COM</t>
+          <t>JESUSADRIANSP@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>16-02-2026 14:42:18</t>
+          <t>17-02-2026 16:22:49</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>16-02-2026 14:44:30</t>
+          <t>17-02-2026 16:47:28</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>17-02-2026 16:27:05</t>
+        </is>
+      </c>
       <c r="U62" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr"/>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W62" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8709,36 +8701,36 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26050522390910004257</t>
+          <t>26050522435210004433</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Hector Noe Espinoza Ramirez</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>344563</t>
+          <t>342708</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>22380</t>
+          <t>20525</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8748,17 +8740,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>JESUS ADRIAN</t>
+          <t>JESUS ANTONIO</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t xml:space="preserve">AISPURO </t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>POMPA</t>
+          <t>IMPERIAL</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8768,39 +8760,35 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6672490628</t>
+          <t>6671966948</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>VOLCAN S</t>
+          <t>ALTURAS</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>15-07-1987</t>
+          <t>03-09-1998</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>JESUSADRIANSP@GMAIL.COM</t>
+          <t>AISPUROIMPERIALJESUSANTONIO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>17-02-2026 16:22:49</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>10-02-2026 16:30:39</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8818,17 +8806,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>17-02-2026 16:47:28</t>
+          <t>10-02-2026 16:35:19</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>17-02-2026 16:27:05</t>
+          <t>10-02-2026 16:34:48</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -8838,7 +8826,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -8848,7 +8836,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26050522435210004433</t>
+          <t>26050522236970003716</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr"/>
@@ -8860,24 +8848,24 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Hector Noe Espinoza Ramirez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>341207</t>
+          <t>342728</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>19025</t>
+          <t>20545</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8887,17 +8875,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>FRANCISCO ALEJANDRO</t>
+          <t>SANTIAGO</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>RUBI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>PEÑUELAS</t>
+          <t>NAVARRETE</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -8907,14 +8895,10 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6673168474</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>MANUEL PAYNO 2161</t>
-        </is>
-      </c>
+          <t>6674364372</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -8922,38 +8906,42 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>25-10-1997</t>
+          <t>17-09-2010</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>ALEX209725@GMAIL.COM</t>
+          <t>SANTI.RUBI102@GMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>05-02-2026 04:45:19</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
+          <t>10-02-2026 16:59:03</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>10-02-2026 04:46:51</t>
+          <t>10-02-2026 17:12:49</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -8961,21 +8949,13 @@
           <t>10-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>10-02-2026 04:44:41</t>
-        </is>
-      </c>
+      <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8983,44 +8963,36 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26050522216510003662</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>ABIGAIL AHUMADA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26050522238860003735</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>344402</t>
+          <t>344544</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>22219</t>
+          <t>22361</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9030,17 +9002,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LESLY LIZBETH</t>
+          <t>JESUS ABRAHAM</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>MONTAÑO</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ALBA</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9050,7 +9022,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6679956390</t>
+          <t>6675819023</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -9061,24 +9033,20 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>20-12-2011</t>
+          <t>15-07-2006</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>ALBALESLY@GMAIL.COM</t>
+          <t>M0NTAN0JSUS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>17-02-2026 07:40:14</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>17-02-2026 16:04:14</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -9086,28 +9054,28 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>17-02-2026 08:27:15</t>
+          <t>17-02-2026 16:06:36</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>17-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V65" t="inlineStr"/>
@@ -9118,36 +9086,36 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26050522421850004396</t>
+          <t>26050522432880004420</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>343911</t>
+          <t>342381</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>21728</t>
+          <t>20199</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9157,17 +9125,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CARLOS GABRIEL</t>
+          <t>DANIEL</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>OLIVAS</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -9177,14 +9145,10 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6674119225</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>RAFAEL MARTINEZ 2620</t>
-        </is>
-      </c>
+          <t>6673281864</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -9192,64 +9156,56 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>01-12-2000</t>
+          <t>19-11-1975</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CMEZAGR10@GMAIL.COM</t>
+          <t>DCASTROO@AFORECOPPEL.COM</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>16-02-2026 05:00:53</t>
+          <t>09-02-2026 18:17:28</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>16-02-2026 05:08:16</t>
+          <t>09-02-2026 18:22:04</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>16-02-2026 05:04:59</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9257,36 +9213,36 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>26050522369740004204</t>
+          <t>26050522206810003627</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>344544</t>
+          <t>342619</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>22361</t>
+          <t>20436</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9296,17 +9252,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>JESUS ABRAHAM</t>
+          <t>CAMILA YAMILET</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MONTAÑO</t>
+          <t>ROMAN</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>NORIEGA</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -9316,10 +9272,14 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>6675819023</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>6671538009</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>HACIENDA DEL VALLE</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -9327,20 +9287,24 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>15-07-2006</t>
+          <t>13-07-2007</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>M0NTAN0JSUS@GMAIL.COM</t>
+          <t>YAMILETHROMAN704@GMAIL.COM</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>17-02-2026 16:04:14</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+          <t>10-02-2026 13:50:59</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O67" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -9348,22 +9312,22 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>17-02-2026 16:06:36</t>
+          <t>10-02-2026 15:14:35</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>17-05-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T67" t="inlineStr"/>
@@ -9380,14 +9344,14 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>26050522432880004420</t>
+          <t>26050522233960003704</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
@@ -9404,12 +9368,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>342381</t>
+          <t>342639</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>20199</t>
+          <t>20456</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9419,17 +9383,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>DANIEL</t>
+          <t>DAMARIS</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t xml:space="preserve">ZAZUETA </t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>OLIVAS</t>
+          <t>URIARTE</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -9439,67 +9403,75 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>6673281864</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>6674646163</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>LOMAS</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>19-11-1975</t>
+          <t>01-08-1987</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>DCASTROO@AFORECOPPEL.COM</t>
+          <t>BLANCA32NICE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>09-02-2026 18:17:28</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>10-02-2026 14:32:18</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>09-02-2026 18:22:04</t>
+          <t>10-02-2026 14:50:58</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>10-02-2026 14:49:25</t>
+        </is>
+      </c>
       <c r="U68" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr"/>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W68" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9507,36 +9479,36 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>26050522206810003627</t>
+          <t>26050522233370003701</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>342619</t>
+          <t>343951</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>20436</t>
+          <t>21768</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9546,17 +9518,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>CAMILA YAMILET</t>
+          <t>ADILENE BERENYCE</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ROMAN</t>
+          <t xml:space="preserve">MEDINA </t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>NORIEGA</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -9566,12 +9538,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>6671538009</t>
+          <t>6674304996</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>HACIENDA DEL VALLE</t>
+          <t>COLINAS DE AMBAR 4640</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9581,56 +9553,64 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>13-07-2007</t>
+          <t>22-10-1990</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>YAMILETHROMAN704@GMAIL.COM</t>
+          <t>BERECARDENAS102@GMAIL.COM</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>10-02-2026 13:50:59</t>
+          <t>16-02-2026 07:28:02</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>10-02-2026 15:14:35</t>
+          <t>16-02-2026 07:35:05</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T69" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>16-02-2026 07:34:19</t>
+        </is>
+      </c>
       <c r="U69" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr"/>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W69" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9638,14 +9618,14 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>26050522233960003704</t>
+          <t>26050522379390004219</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="inlineStr"/>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
@@ -9662,12 +9642,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>342639</t>
+          <t>343138</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>20456</t>
+          <t>20955</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9677,17 +9657,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>DAMARIS</t>
+          <t>NORMA ALICIA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAZUETA </t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>URIARTE</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -9697,12 +9677,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>6674646163</t>
+          <t>6674953867</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>LOMAS</t>
+          <t>SAN ISIDRO</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9712,17 +9692,17 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>01-08-1987</t>
+          <t>27-09-1971</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>BLANCA32NICE@GMAIL.COM</t>
+          <t>NORMAALICIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>10-02-2026 14:32:18</t>
+          <t>11-02-2026 20:48:11</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -9733,7 +9713,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -9743,17 +9723,17 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>10-02-2026 14:50:58</t>
+          <t>11-02-2026 20:51:25</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>10-02-2026 14:49:25</t>
+          <t>11-02-2026 20:50:52</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -9773,7 +9753,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>26050522233370003701</t>
+          <t>26050522278960003916</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr"/>
@@ -9797,12 +9777,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>343138</t>
+          <t>343911</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>20955</t>
+          <t>21728</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9812,17 +9792,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NORMA ALICIA</t>
+          <t>CARLOS GABRIEL</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -9832,35 +9812,39 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>6674953867</t>
+          <t>6674119225</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>SAN ISIDRO</t>
+          <t>RAFAEL MARTINEZ 2620</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>27-09-1971</t>
+          <t>01-12-2000</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>NORMAALICIA@GMAIL.COM</t>
+          <t>CMEZAGR10@GMAIL.COM</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>11-02-2026 20:48:11</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
+          <t>16-02-2026 05:00:53</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O71" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -9868,7 +9852,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -9878,17 +9862,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>11-02-2026 20:51:25</t>
+          <t>16-02-2026 05:08:16</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>11-02-2026 20:50:52</t>
+          <t>16-02-2026 05:04:59</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -9908,7 +9892,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>26050522278960003916</t>
+          <t>26050522369740004204</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr"/>
@@ -9932,12 +9916,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>344348</t>
+          <t>344219</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>22165</t>
+          <t>22036</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -9947,17 +9931,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>OLIBLISH</t>
+          <t>JETSSY YERANI</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RECENDIZ</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SMER</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -9967,12 +9951,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>6671404207</t>
+          <t>6671955010</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>HACIENDA</t>
+          <t>PRADOS</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9982,42 +9966,42 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>30-08-2001</t>
+          <t>01-11-2002</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>OLIBLISHRECENDIZ@GMAIL.COM</t>
+          <t>CHJETSSY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>16-02-2026 19:50:40</t>
+          <t>16-02-2026 17:35:23</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>16-02-2026 19:55:43</t>
+          <t>16-02-2026 17:40:31</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -10027,7 +10011,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>16-02-2026 19:54:36</t>
+          <t>16-02-2026 17:39:31</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -10047,36 +10031,36 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>26050522409440004358</t>
+          <t>26050522400210004318</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>344406</t>
+          <t>344330</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>22223</t>
+          <t>22147</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -10086,17 +10070,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>MARIA JOSE</t>
+          <t>CRISTOPHER LUCIANO</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>VELAZQUEZ</t>
+          <t>ZAVALA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>OLIVAS</t>
+          <t>ANGULO</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -10106,31 +10090,35 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>6674694221</t>
+          <t>6671833791</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>20-06-2006</t>
+          <t>04-09-2013</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>MARIAJOSEVELAZQUEZOLIVAS@GMAIL.COM</t>
+          <t>CLOSETYCOCINASSR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>17-02-2026 08:01:38</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
+          <t>16-02-2026 19:04:29</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O73" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -10138,22 +10126,22 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>17-02-2026 08:04:53</t>
+          <t>16-02-2026 19:14:09</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>17-05-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T73" t="inlineStr"/>
@@ -10170,36 +10158,36 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>26050522421390004393</t>
+          <t>26050522407600004347</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>344529</t>
+          <t>344602</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>22346</t>
+          <t>22419</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10209,17 +10197,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>JACQUELINE QUETZALI</t>
+          <t>ROXANA GABRIELA</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>SAMANIEGO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>PERAZA</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -10229,63 +10217,79 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>6672654267</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>6471226799</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>C MIGUEL HIDALGO</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>22-10-1990</t>
+          <t>23-11-1999</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>QUETZALI_JACKY@HOTMAIL.COM</t>
+          <t>ROXANASAMANIEGO487@GMAIL.COM</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>17-02-2026 15:23:38</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
+          <t>17-02-2026 17:21:04</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>17-02-2026 15:31:57</t>
+          <t>17-02-2026 17:25:35</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>17-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>17-02-2026 17:24:51</t>
+        </is>
+      </c>
       <c r="U74" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V74" t="inlineStr"/>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W74" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10293,36 +10297,36 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>26050522431570004417</t>
+          <t>26050522437350004443</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>344684</t>
+          <t>344348</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>22165</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10332,17 +10336,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LAURA FERNANDA</t>
+          <t>OLIBLISH</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">BELTRAN </t>
+          <t>RECENDIZ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>SMER</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -10352,10 +10356,14 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>6671852522</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>6671404207</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>HACIENDA</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -10363,56 +10371,64 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>30-12-2012</t>
+          <t>30-08-2001</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>666PEREZADRIA@GMAIL.COM</t>
+          <t>OLIBLISHRECENDIZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>17-02-2026 19:24:52</t>
+          <t>16-02-2026 19:50:40</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>17-02-2026 19:26:14</t>
+          <t>16-02-2026 19:55:43</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T75" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>16-02-2026 19:54:36</t>
+        </is>
+      </c>
       <c r="U75" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V75" t="inlineStr"/>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W75" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10420,22 +10436,395 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>26050522444240004472</t>
+          <t>26050522409440004358</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="inlineStr">
         <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>Carlos Aurelio Monzon Ayala</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>344406</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>22223</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>MARIA JOSE</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>VELAZQUEZ</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>OLIVAS</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>6674694221</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>20-06-2006</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>MARIAJOSEVELAZQUEZOLIVAS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>17-02-2026 08:01:38</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>17-02-2026 08:04:53</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>17-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>26050522421390004393</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>Gilberto Tavarez Soto</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>344529</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>22346</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>JACQUELINE QUETZALI</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>PERAZA</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>6672654267</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>22-10-1990</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>QUETZALI_JACKY@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>17-02-2026 15:23:38</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>17-02-2026 15:31:57</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>17-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>26050522431570004417</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>Carlos Aurelio Monzon Ayala</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>344684</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LAURA FERNANDA</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BELTRAN </t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>MORENO</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>6671852522</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>30-12-2012</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>666PEREZADRIA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>17-02-2026 19:24:52</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
           <t>549</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>17-02-2026 19:26:14</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>26050522444240004472</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
         <is>
           <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
+      <c r="AC78" t="inlineStr">
         <is>
           <t>con rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN ISIDRO CUL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN ISIDRO CUL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC78"/>
+  <dimension ref="A1:AC86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1793,12 +1793,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>272287</t>
+          <t>340267</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>69789</t>
+          <t>18085</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1808,17 +1808,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ENRIQUE FERNANDO</t>
+          <t>YAZMIN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUEN </t>
+          <t>VALLE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>GAXIOLA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1828,67 +1828,75 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6674136197</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>6674799515</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>VILLA BONITA</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>25-09-1991</t>
+          <t>07-06-1976</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>STARBLUEWIRELESS@GMAIL.COM</t>
+          <t>YAZVALLEG@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>07-01-2025 11:41:40</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>02-02-2026 16:29:51</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>19-02-2026 16:34:27</t>
+          <t>02-02-2026 16:34:26</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>02-02-2026 16:33:26</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1896,36 +1904,36 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26050522499150004636</t>
+          <t>26050522016680002906</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>293161</t>
+          <t>340281</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90659</t>
+          <t>18099</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1935,17 +1943,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ALONSO</t>
+          <t>CAMILA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMPAÑA </t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TOGO</t>
+          <t>VALLE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1955,67 +1963,75 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6673244126</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>6731037377</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>VILLA BONITA</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>14-10-2005</t>
+          <t>20-08-2007</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>TOGOALONSO03@GMAIL.COM</t>
+          <t>CAMILACAS0820@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>15-05-2025 12:06:41</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>02-02-2026 16:42:06</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>16-02-2026 19:39:22</t>
+          <t>02-02-2026 16:44:16</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>02-02-2026 16:43:49</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2023,36 +2039,36 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26040522408810002800</t>
+          <t>26050522017120002908</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>340267</t>
+          <t>340288</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18085</t>
+          <t>18106</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2062,17 +2078,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>YAZMIN</t>
+          <t>JESUS OSCAR</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VALLE</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>GAXIOLA</t>
+          <t>ARAMBURO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2082,32 +2098,32 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6674799515</t>
+          <t>6671644312</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>VILLA BONITA</t>
+          <t>CAPISTRANO</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>07-06-1976</t>
+          <t>03-11-1982</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>YAZVALLEG@GMAIL.COM</t>
+          <t>JOSCAR18203@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-02-2026 16:29:51</t>
+          <t>02-02-2026 16:51:17</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2128,7 +2144,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-02-2026 16:34:26</t>
+          <t>02-02-2026 16:55:47</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2138,7 +2154,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>02-02-2026 16:33:26</t>
+          <t>02-02-2026 16:55:14</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2148,7 +2164,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2158,7 +2174,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26050522016680002906</t>
+          <t>26050522017580002910</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2182,12 +2198,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>340281</t>
+          <t>272287</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18099</t>
+          <t>69789</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2197,17 +2213,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CAMILA</t>
+          <t>ENRIQUE FERNANDO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t xml:space="preserve">CUEN </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>VALLE</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2217,75 +2233,67 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6731037377</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>VILLA BONITA</t>
-        </is>
-      </c>
+          <t>6674136197</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>20-08-2007</t>
+          <t>25-09-1991</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CAMILACAS0820@GMAIL.COM</t>
+          <t>STARBLUEWIRELESS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-02-2026 16:42:06</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>07-01-2025 11:41:40</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-02-2026 16:44:16</t>
+          <t>19-02-2026 16:34:27</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>02-02-2026 16:43:49</t>
-        </is>
-      </c>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2293,36 +2301,36 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26050522017120002908</t>
+          <t>26050522499150004636</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>340288</t>
+          <t>293161</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18106</t>
+          <t>90659</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2332,17 +2340,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>JESUS OSCAR</t>
+          <t>ALONSO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">CAMPAÑA </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ARAMBURO</t>
+          <t>TOGO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2352,14 +2360,10 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6671644312</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>CAPISTRANO</t>
-        </is>
-      </c>
+          <t>6673244126</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2367,60 +2371,56 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>03-11-1982</t>
+          <t>14-10-2005</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>JOSCAR18203@GMAIL.COM</t>
+          <t>TOGOALONSO03@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-02-2026 16:51:17</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>15-05-2025 12:06:41</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-02-2026 16:55:47</t>
+          <t>16-02-2026 19:39:22</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>02-02-2026 16:55:14</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2428,24 +2428,24 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26050522017580002910</t>
+          <t>26040522408810002800</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>340062</t>
+          <t>339874</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17880</t>
+          <t>17692</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3130,17 +3130,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MIGUEL ALBERTO</t>
+          <t>VICTOR MANUEL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VELARDE</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3150,14 +3150,10 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6674054276</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>PARQUE ANDARES</t>
-        </is>
-      </c>
+          <t>6676511429</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3165,38 +3161,42 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>03-04-2002</t>
+          <t>23-01-1987</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>SERGIOMESSI334@GMAIL.COM</t>
+          <t>AVERALEJANDROPARRA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>02-02-2026 11:31:11</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>02-02-2026 06:57:03</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>02-02-2026 11:39:13</t>
+          <t>02-02-2026 06:58:34</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -3204,21 +3204,13 @@
           <t>02-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>02-02-2026 11:34:23</t>
-        </is>
-      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3226,19 +3218,19 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26050522007440002876</t>
+          <t>26050521999050002836</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>Hector Noe Espinoza Ramirez</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3250,12 +3242,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>339874</t>
+          <t>340051</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17692</t>
+          <t>17869</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3265,17 +3257,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VICTOR MANUEL</t>
+          <t>JOSUE ARMANDO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>MORGA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3285,10 +3277,14 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6676511429</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>6673455280</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C. HACIENDA DEL CONDE 5818 </t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3296,42 +3292,38 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>23-01-1987</t>
+          <t>20-02-2002</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>AVERALEJANDROPARRA@GMAIL.COM</t>
+          <t>JOSUEMORGA2001@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>02-02-2026 06:57:03</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>02-02-2026 11:14:09</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>02-02-2026 06:58:34</t>
+          <t>02-02-2026 11:17:38</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3339,13 +3331,21 @@
           <t>02-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>02-02-2026 11:17:07</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3353,36 +3353,36 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26050521999050002836</t>
+          <t>26050522006620002874</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Hector Noe Espinoza Ramirez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>340051</t>
+          <t>340062</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17869</t>
+          <t>17880</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3392,17 +3392,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>JOSUE ARMANDO</t>
+          <t>MIGUEL ALBERTO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MORGA</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t>VELARDE</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3412,12 +3412,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6673455280</t>
+          <t>6674054276</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">C. HACIENDA DEL CONDE 5818 </t>
+          <t>PARQUE ANDARES</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3427,17 +3427,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>20-02-2002</t>
+          <t>03-04-2002</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>JOSUEMORGA2001@GMAIL.COM</t>
+          <t>SERGIOMESSI334@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>02-02-2026 11:14:09</t>
+          <t>02-02-2026 11:31:11</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>02-02-2026 11:17:38</t>
+          <t>02-02-2026 11:39:13</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>02-02-2026 11:17:07</t>
+          <t>02-02-2026 11:34:23</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26050522006620002874</t>
+          <t>26050522007440002876</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -3500,12 +3500,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -3766,12 +3766,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>341538</t>
+          <t>342363</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19356</t>
+          <t>20181</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>JACIEL MANUEL</t>
+          <t>SILVIA GUADALUPE</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CASTELLANOS</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>LINDORO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3801,39 +3801,35 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6677900100</t>
+          <t>6671844971</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ARTICULO 27 3491</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>30-03-1991</t>
+          <t>26-06-1996</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>JACIEL.CASTELLANOS@HOTMAIL.COM</t>
+          <t>SILVIA_ML13@HOTMA.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>06-02-2026 12:12:23</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 17:59:28</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3851,17 +3847,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>17-02-2026 10:58:43</t>
+          <t>09-02-2026 18:06:03</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>17-02-2026 10:56:07</t>
+          <t>09-02-2026 18:03:54</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3881,19 +3877,11 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26050522424560004401</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>ABIGAIL AHUMADA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26050522205370003618</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
           <t>499</t>
@@ -3901,24 +3889,24 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>341584</t>
+          <t>342046</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19402</t>
+          <t>19864</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3928,17 +3916,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>IRVING ADOLFO</t>
+          <t>KASSANDRA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>VIDAL</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3948,63 +3936,67 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6674711600</t>
+          <t>6673286036</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>MARIANO CARLON 4931</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>28-11-1999</t>
+          <t>02-12-2004</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ADOLFO_IAFS@HOTMAIL.COM</t>
+          <t>KASSANDRASANCH@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>06-02-2026 14:45:39</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>09-02-2026 08:07:39</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>06-02-2026 14:49:50</t>
+          <t>09-02-2026 08:15:43</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>06-02-2026 14:49:22</t>
+          <t>09-02-2026 08:15:18</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4024,36 +4016,36 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26050522137710003362</t>
+          <t>26050522184630003535</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>342046</t>
+          <t>342052</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19864</t>
+          <t>19870</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4063,17 +4055,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>KASSANDRA</t>
+          <t>AMAYRANI YESSENIA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t xml:space="preserve">QUINTERO </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>VIDAL</t>
+          <t xml:space="preserve">ANDRADE </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4083,12 +4075,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6673286036</t>
+          <t>6674832993</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>MARIANO CARLON 4931</t>
+          <t>JOEGE ROMERO ZAZUETA 2306</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4098,42 +4090,38 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>02-12-2004</t>
+          <t>21-11-2001</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>KASSANDRASANCH@GMAIL.COM</t>
+          <t>AMAYRANI_QUINTERO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>09-02-2026 08:07:39</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>09-02-2026 08:35:57</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>09-02-2026 08:15:43</t>
+          <t>09-02-2026 08:46:58</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -4143,7 +4131,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>09-02-2026 08:15:18</t>
+          <t>09-02-2026 08:46:15</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4163,14 +4151,14 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26050522184630003535</t>
+          <t>26050522185300003537</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -4187,12 +4175,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>342052</t>
+          <t>342107</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19870</t>
+          <t>19925</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4202,17 +4190,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AMAYRANI YESSENIA</t>
+          <t>NAUN ALAN</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUINTERO </t>
+          <t>CHIQUETE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANDRADE </t>
+          <t>PALOMAREZ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4222,32 +4210,32 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6674832993</t>
+          <t>6677976901</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>JOEGE ROMERO ZAZUETA 2306</t>
+          <t>CERRO DEL CHIQUIHUITE</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>21-11-2001</t>
+          <t>02-02-1994</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>AMAYRANI_QUINTERO@HOTMAIL.COM</t>
+          <t>NAUNALANCHIQUETE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>09-02-2026 08:35:57</t>
+          <t>09-02-2026 11:16:00</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4268,7 +4256,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>09-02-2026 08:46:58</t>
+          <t>09-02-2026 11:18:05</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -4278,7 +4266,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>09-02-2026 08:46:15</t>
+          <t>09-02-2026 11:17:49</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4288,7 +4276,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4298,7 +4286,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26050522185300003537</t>
+          <t>26050522188750003551</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
@@ -4310,7 +4298,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4322,12 +4310,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>342107</t>
+          <t>341538</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19925</t>
+          <t>19356</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4337,17 +4325,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NAUN ALAN</t>
+          <t>JACIEL MANUEL</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CHIQUETE</t>
+          <t>CASTELLANOS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PALOMAREZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4357,12 +4345,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6677976901</t>
+          <t>6677900100</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>CERRO DEL CHIQUIHUITE</t>
+          <t>ARTICULO 27 3491</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4372,20 +4360,24 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>02-02-1994</t>
+          <t>30-03-1991</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>NAUNALANCHIQUETE@GMAIL.COM</t>
+          <t>JACIEL.CASTELLANOS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>09-02-2026 11:16:00</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>06-02-2026 12:12:23</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4403,17 +4395,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>09-02-2026 11:18:05</t>
+          <t>17-02-2026 10:58:43</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>09-02-2026 11:17:49</t>
+          <t>17-02-2026 10:56:07</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4423,7 +4415,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4433,11 +4425,19 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26050522188750003551</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
+          <t>26050522424560004401</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>499</t>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4457,12 +4457,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>342306</t>
+          <t>341584</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20124</t>
+          <t>19402</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4472,17 +4472,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">AYELIN YAMILETH </t>
+          <t>IRVING ADOLFO</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CORRALES</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4492,67 +4492,63 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6674237913</t>
+          <t>6674711600</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CHULAVISTA</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>17-09-2001</t>
+          <t>28-11-1999</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>AYELENCORRALES52@GMAIL.COM</t>
+          <t>ADOLFO_IAFS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>09-02-2026 17:10:32</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>06-02-2026 14:45:39</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>09-02-2026 17:15:55</t>
+          <t>06-02-2026 14:49:50</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>06-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>09-02-2026 17:15:08</t>
+          <t>06-02-2026 14:49:22</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4572,14 +4568,14 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26050522201360003593</t>
+          <t>26050522137710003362</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4596,12 +4592,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>342024</t>
+          <t>342649</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19842</t>
+          <t>20466</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4611,17 +4607,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AYAMARA</t>
+          <t>MARIA FERNANDA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MONTOYA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>ZAZUETA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4631,12 +4627,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6673527007</t>
+          <t>6674603292</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>CERRO DE PUNTA OESTE 743</t>
+          <t>LOMAS</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4646,17 +4642,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>13-11-2005</t>
+          <t>14-06-2011</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>AYAMARAHERNANDEZ05@GMAIL.COM</t>
+          <t>MARIAFERNANDA19@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>09-02-2026 07:10:48</t>
+          <t>10-02-2026 14:53:32</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4677,17 +4673,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>09-02-2026 07:26:58</t>
+          <t>10-02-2026 14:57:06</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>09-02-2026 07:22:21</t>
+          <t>10-02-2026 14:56:25</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4707,7 +4703,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26050522183300003529</t>
+          <t>26050522233480003703</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
@@ -4719,24 +4715,24 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>340278</t>
+          <t>342054</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18096</t>
+          <t>19872</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4746,17 +4742,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DIEGO</t>
+          <t>YAZMIN</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>VALLE</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4766,32 +4762,32 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6672689990</t>
+          <t>8186031726</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>VILLA BONITA</t>
+          <t>DE LAS VEREDAS</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>12-03-2004</t>
+          <t>28-07-2001</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>DIEGOCASTROVALLE1@GMAIL.COM</t>
+          <t>YAZ.LOPEZ17@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>02-02-2026 16:38:29</t>
+          <t>09-02-2026 08:38:56</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4812,17 +4808,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>02-02-2026 16:41:10</t>
+          <t>09-02-2026 08:54:38</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>02-02-2026 16:40:49</t>
+          <t>09-02-2026 08:52:19</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4842,7 +4838,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26050522017020002907</t>
+          <t>26050522185440003538</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
@@ -4854,7 +4850,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4866,12 +4862,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>342054</t>
+          <t>342306</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19872</t>
+          <t>20124</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4881,19 +4877,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>YAZMIN</t>
+          <t xml:space="preserve">AYELIN YAMILETH </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>CORRALES</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>LOPEZ</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>SANCHEZ</t>
-        </is>
-      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>52</t>
@@ -4901,12 +4897,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8186031726</t>
+          <t>6674237913</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>DE LAS VEREDAS</t>
+          <t>CHULAVISTA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4916,38 +4912,42 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>28-07-2001</t>
+          <t>17-09-2001</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>YAZ.LOPEZ17@OUTLOOK.COM</t>
+          <t>AYELENCORRALES52@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>09-02-2026 08:38:56</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>09-02-2026 17:10:32</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>09-02-2026 08:54:38</t>
+          <t>09-02-2026 17:15:55</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>09-02-2026 08:52:19</t>
+          <t>09-02-2026 17:15:08</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4977,36 +4977,36 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26050522185440003538</t>
+          <t>26050522201360003593</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>342363</t>
+          <t>342024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20181</t>
+          <t>19842</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5016,17 +5016,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SILVIA GUADALUPE</t>
+          <t>AYAMARA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>LINDORO</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6671844971</t>
+          <t>6673527007</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>CERRO DE PUNTA OESTE 743</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>26-06-1996</t>
+          <t>13-11-2005</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>SILVIA_ML13@HOTMA.COM</t>
+          <t>AYAMARAHERNANDEZ05@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>09-02-2026 17:59:28</t>
+          <t>09-02-2026 07:10:48</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>09-02-2026 18:06:03</t>
+          <t>09-02-2026 07:26:58</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>09-02-2026 18:03:54</t>
+          <t>09-02-2026 07:22:21</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26050522205370003618</t>
+          <t>26050522183300003529</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5136,12 +5136,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>339936</t>
+          <t>342376</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17754</t>
+          <t>20194</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5151,17 +5151,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>HECTOR ALEJANDRO</t>
+          <t>DANIEL SEBASTIAN</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>IRIBE</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5171,28 +5171,28 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6674294024</t>
+          <t>6671384521</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>15-07-2009</t>
+          <t>15-05-2009</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>HAIRO90715@GMAIL.COM</t>
+          <t>DANIELCASTRO09410315@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>02-02-2026 09:08:54</t>
+          <t>09-02-2026 18:13:14</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5217,18 +5217,18 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>02-02-2026 09:10:01</t>
+          <t>09-02-2026 18:15:27</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V36" t="inlineStr"/>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26050522002290002854</t>
+          <t>26050522206250003624</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
@@ -5263,12 +5263,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>342376</t>
+          <t>339936</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20194</t>
+          <t>17754</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5278,17 +5278,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DANIEL SEBASTIAN</t>
+          <t>HECTOR ALEJANDRO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>IRIBE</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5298,28 +5298,28 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6671384521</t>
+          <t>6674294024</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>15-05-2009</t>
+          <t>15-07-2009</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>DANIELCASTRO09410315@GMAIL.COM</t>
+          <t>HAIRO90715@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>09-02-2026 18:13:14</t>
+          <t>02-02-2026 09:08:54</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5344,18 +5344,18 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>09-02-2026 18:15:27</t>
+          <t>02-02-2026 09:10:01</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V37" t="inlineStr"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26050522206250003624</t>
+          <t>26050522002290002854</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
@@ -5390,12 +5390,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>342649</t>
+          <t>342706</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20466</t>
+          <t>20523</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5405,17 +5405,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA</t>
+          <t>JESUS ANDRES</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>MONTOYA</t>
+          <t>LEY</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ZAZUETA</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5425,32 +5425,32 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6674603292</t>
+          <t>6678403979</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>LOMAS</t>
+          <t>MISION DE SAN MIGUEL 8559</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>14-06-2011</t>
+          <t>30-06-2000</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>MARIAFERNANDA19@GMAIL.COM</t>
+          <t>LEYCASTROANDRES@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>10-02-2026 14:53:32</t>
+          <t>10-02-2026 16:29:39</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>10-02-2026 14:57:06</t>
+          <t>10-02-2026 16:37:39</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>10-02-2026 14:56:25</t>
+          <t>10-02-2026 16:37:12</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26050522233480003703</t>
+          <t>26050522237060003718</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
@@ -5513,24 +5513,24 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>342706</t>
+          <t>340032</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20523</t>
+          <t>17850</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5540,17 +5540,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>JESUS ANDRES</t>
+          <t>KEVIN ARON</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>LEY</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6678403979</t>
+          <t>6673555568</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>MISION DE SAN MIGUEL 8559</t>
+          <t>URBIVILLAS DEL SOL 2676</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5575,17 +5575,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>30-06-2000</t>
+          <t>13-10-2006</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>LEYCASTROANDRES@GMAIL.COM</t>
+          <t>KAEVINGONZALEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>10-02-2026 16:29:39</t>
+          <t>02-02-2026 10:55:15</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5606,17 +5606,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>10-02-2026 16:37:39</t>
+          <t>02-02-2026 11:13:58</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>10-02-2026 16:37:12</t>
+          <t>02-02-2026 11:13:24</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26050522237060003718</t>
+          <t>26050522006460002873</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
@@ -5660,12 +5660,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>340032</t>
+          <t>340044</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>17850</t>
+          <t>17862</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5675,17 +5675,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>KEVIN ARON</t>
+          <t xml:space="preserve">MARIA FERNANDA </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>PAREDES</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5695,32 +5695,32 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6673555568</t>
+          <t>6672539772</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>URBIVILLAS DEL SOL 2676</t>
+          <t>C ARTICULO 27 3491</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>13-10-2006</t>
+          <t>18-01-1998</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>KAEVINGONZALEZ@GMAIL.COM</t>
+          <t>FERNANDAPAREDESS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>02-02-2026 10:55:15</t>
+          <t>02-02-2026 11:10:29</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5741,17 +5741,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>02-02-2026 11:13:58</t>
+          <t>06-02-2026 12:24:08</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>06-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>02-02-2026 11:13:24</t>
+          <t>06-02-2026 12:23:13</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5771,11 +5771,19 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26050522006460002873</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
+          <t>26050522135340003355</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>499</t>
@@ -5795,12 +5803,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>340044</t>
+          <t>340278</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>17862</t>
+          <t>18096</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5810,17 +5818,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA FERNANDA </t>
+          <t>DIEGO</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PAREDES</t>
+          <t>VALLE</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5830,32 +5838,32 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6672539772</t>
+          <t>6672689990</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>C ARTICULO 27 3491</t>
+          <t>VILLA BONITA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>18-01-1998</t>
+          <t>12-03-2004</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>FERNANDAPAREDESS@HOTMAIL.COM</t>
+          <t>DIEGOCASTROVALLE1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>02-02-2026 11:10:29</t>
+          <t>02-02-2026 16:38:29</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5876,17 +5884,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>06-02-2026 12:24:08</t>
+          <t>02-02-2026 16:41:10</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>06-02-2026 12:23:13</t>
+          <t>02-02-2026 16:40:49</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5906,19 +5914,11 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26050522135340003355</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>ABIGAIL AHUMADA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26050522017020002907</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
           <t>499</t>
@@ -5926,24 +5926,24 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>341209</t>
+          <t>343859</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>19027</t>
+          <t>21676</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5953,17 +5953,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ROCIO MARGARITA</t>
+          <t>CLAUDIA LIBERTAD</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>PORTILLO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CIFUENTES</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6673305169</t>
+          <t>6674275957</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>CAPISTRANO</t>
+          <t>PRADOS DEL SOL</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5988,17 +5988,17 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>19-08-1971</t>
+          <t>11-10-1995</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CRED9011037@GMAIL.COM</t>
+          <t>LIBERTAD-PORTILLO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>05-02-2026 05:19:52</t>
+          <t>15-02-2026 13:41:31</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -6009,7 +6009,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -6019,17 +6019,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>05-02-2026 05:25:19</t>
+          <t>15-02-2026 13:45:48</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>05-02-2026 05:25:01</t>
+          <t>15-02-2026 13:45:01</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26050522097780003210</t>
+          <t>26050522366990004185</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6073,12 +6073,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>341210</t>
+          <t>341183</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>19028</t>
+          <t>19001</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6088,17 +6088,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ODALIZ BRISEIDA</t>
+          <t>ISAAC ALEJANDRO</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PATRON</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>PICOS</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6108,75 +6108,63 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6671988044</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>CAPISTRANO</t>
-        </is>
-      </c>
+          <t>6675823775</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>10-04-2002</t>
+          <t>21-08-2006</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>PATRON.QUINTERO.ODALIZ108@GMAIL.COM</t>
+          <t>ISAACLLANES999@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>05-02-2026 05:31:53</t>
+          <t>04-02-2026 20:01:05</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>05-02-2026 05:36:08</t>
+          <t>16-02-2026 19:00:46</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>05-02-2026 05:35:58</t>
-        </is>
-      </c>
+          <t>16-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6184,36 +6172,44 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26050522097920003212</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
+          <t>26050522406720004345</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>341416</t>
+          <t>343144</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>19234</t>
+          <t>20961</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6223,17 +6219,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">OLIVER </t>
+          <t>VICTORIA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SIMENTAL</t>
+          <t>OJEDA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>URTUSUASTEGUI</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6243,35 +6239,35 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6672988277</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>6673796592</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>PAULINO MACHORRO1896</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>07-09-2003</t>
+          <t>17-11-1994</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>OLIVER4647@ICLOUD.COM</t>
+          <t>VICTORIAOJEDAAAA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>05-02-2026 18:15:05</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>11-02-2026 21:38:13</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -6279,28 +6275,28 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>05-02-2026 18:16:32</t>
+          <t>13-02-2026 19:49:17</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V44" t="inlineStr"/>
@@ -6311,19 +6307,27 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26050522115260003288</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
+          <t>26050522330490004130</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>Carmen Michel Navarrete  Nevarez</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Hector Noe Espinoza Ramirez</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6335,12 +6339,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>341183</t>
+          <t>343449</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>19001</t>
+          <t>21266</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6350,17 +6354,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ISAAC ALEJANDRO</t>
+          <t>BIANCA AZUCENA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>LANDELL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>PICOS</t>
+          <t>PARRA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6370,63 +6374,75 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6675823775</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>6674842233</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>MINA DEL PEÑON BLANCO 560</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>21-08-2006</t>
+          <t>21-12-2000</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>ISAACLLANES999@GMAIL.COM</t>
+          <t>BIANCALANDELL21@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>04-02-2026 20:01:05</t>
+          <t>13-02-2026 09:39:01</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>16-02-2026 19:00:46</t>
+          <t>13-02-2026 09:48:06</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>13-02-2026 09:45:49</t>
+        </is>
+      </c>
       <c r="U45" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr"/>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W45" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6434,44 +6450,36 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26050522406720004345</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
-        </is>
-      </c>
+          <t>26050522317680004073</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>343144</t>
+          <t>341207</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20961</t>
+          <t>19025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6481,17 +6489,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VICTORIA</t>
+          <t>FRANCISCO ALEJANDRO</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>OJEDA</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>PEÑUELAS</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6501,38 +6509,38 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6673796592</t>
+          <t>6673168474</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>PAULINO MACHORRO1896</t>
+          <t>MANUEL PAYNO 2161</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>17-11-1994</t>
+          <t>25-10-1997</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>VICTORIAOJEDAAAA@GMAIL.COM</t>
+          <t>ALEX209725@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>11-02-2026 21:38:13</t>
+          <t>05-02-2026 04:45:19</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6547,21 +6555,29 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>13-02-2026 19:49:17</t>
+          <t>10-02-2026 04:46:51</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>10-02-2026 04:44:41</t>
+        </is>
+      </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W46" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6569,17 +6585,17 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26050522330490004130</t>
+          <t>26050522216510003662</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>Carmen Michel Navarrete  Nevarez</t>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6589,24 +6605,24 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>343449</t>
+          <t>341209</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21266</t>
+          <t>19027</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6616,17 +6632,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>BIANCA AZUCENA</t>
+          <t>ROCIO MARGARITA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>LANDELL</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>PARRA</t>
+          <t>CIFUENTES</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6636,12 +6652,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6674842233</t>
+          <t>6673305169</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>MINA DEL PEÑON BLANCO 560</t>
+          <t>CAPISTRANO</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6651,17 +6667,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>21-12-2000</t>
+          <t>19-08-1971</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>BIANCALANDELL21@GMAIL.COM</t>
+          <t>CRED9011037@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>13-02-2026 09:39:01</t>
+          <t>05-02-2026 05:19:52</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -6682,17 +6698,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>13-02-2026 09:48:06</t>
+          <t>05-02-2026 05:25:19</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>13-02-2026 09:45:49</t>
+          <t>05-02-2026 05:25:01</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -6712,7 +6728,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26050522317680004073</t>
+          <t>26050522097780003210</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
@@ -6736,12 +6752,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>343859</t>
+          <t>341210</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21676</t>
+          <t>19028</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6751,17 +6767,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>CLAUDIA LIBERTAD</t>
+          <t>ODALIZ BRISEIDA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PORTILLO</t>
+          <t>PATRON</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6771,12 +6787,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6674275957</t>
+          <t>6671988044</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>PRADOS DEL SOL</t>
+          <t>CAPISTRANO</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6786,17 +6802,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>11-10-1995</t>
+          <t>10-04-2002</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>LIBERTAD-PORTILLO@HOTMAIL.COM</t>
+          <t>PATRON.QUINTERO.ODALIZ108@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>15-02-2026 13:41:31</t>
+          <t>05-02-2026 05:31:53</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -6807,7 +6823,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -6817,17 +6833,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>15-02-2026 13:45:48</t>
+          <t>05-02-2026 05:36:08</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>15-02-2026 13:45:01</t>
+          <t>05-02-2026 05:35:58</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6847,7 +6863,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26050522366990004185</t>
+          <t>26050522097920003212</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
@@ -6859,7 +6875,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -6871,12 +6887,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>341207</t>
+          <t>345351</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>19025</t>
+          <t>87516</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6886,17 +6902,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>FRANCISCO ALEJANDRO</t>
+          <t>ROSA LAURA</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>ALBA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>PEÑUELAS</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6906,75 +6922,63 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6673168474</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>MANUEL PAYNO 2161</t>
-        </is>
-      </c>
+          <t>6676945948</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>25-10-1997</t>
+          <t>12-06-1986</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>ALEX209725@GMAIL.COM</t>
+          <t>178563586@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>05-02-2026 04:45:19</t>
+          <t>20-02-2026 17:09:02</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>10-02-2026 04:46:51</t>
+          <t>20-02-2026 17:31:55</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>10-02-2026 04:44:41</t>
-        </is>
-      </c>
+          <t>21-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6982,7 +6986,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26050522216510003662</t>
+          <t>26050522531930004755</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -6992,12 +6996,12 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>ABIGAIL AHUMADA MARTINEZ</t>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
@@ -7014,12 +7018,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>344402</t>
+          <t>344004</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>22219</t>
+          <t>21821</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7029,17 +7033,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LESLY LIZBETH</t>
+          <t>IVAN JARETH</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t xml:space="preserve">HIRATA </t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ALBA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7049,67 +7053,79 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6679956390</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>6672295585</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>CERRO CULIACAN 1391</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>20-12-2011</t>
+          <t>04-10-1996</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>ALBALESLY@GMAIL.COM</t>
+          <t>C98667145@COPPEL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>17-02-2026 07:40:14</t>
+          <t>16-02-2026 10:33:07</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>17-02-2026 08:27:15</t>
+          <t>16-02-2026 10:58:09</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>16-02-2026 10:41:22</t>
+        </is>
+      </c>
       <c r="U50" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7117,36 +7133,36 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26050522421850004396</t>
+          <t>26050522384690004236</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>344004</t>
+          <t>344058</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21821</t>
+          <t>21875</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7156,17 +7172,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>IVAN JARETH</t>
+          <t xml:space="preserve">ADRIAN ALEJANDRO </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">HIRATA </t>
+          <t>GAMBOA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7176,14 +7192,10 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6672295585</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>CERRO CULIACAN 1391</t>
-        </is>
-      </c>
+          <t>2212182749</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7191,42 +7203,42 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>04-10-1996</t>
+          <t>01-01-2000</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>C98667145@COPPEL.COM</t>
+          <t>AGAMBOA515@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>16-02-2026 10:33:07</t>
+          <t>16-02-2026 12:55:37</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>16-02-2026 10:58:09</t>
+          <t>16-02-2026 17:16:42</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -7234,21 +7246,13 @@
           <t>16-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>16-02-2026 10:41:22</t>
-        </is>
-      </c>
+      <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7256,14 +7260,14 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26050522384690004236</t>
+          <t>26050522398420004302</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
@@ -7280,12 +7284,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>344058</t>
+          <t>344007</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21875</t>
+          <t>21824</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7295,17 +7299,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADRIAN ALEJANDRO </t>
+          <t>JOSE LUIS</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>GAMBOA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7315,10 +7319,14 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2212182749</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>6671901876</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>CERRO DEL TENAYO 1285</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7326,42 +7334,42 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>01-01-2000</t>
+          <t>08-10-1988</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>AGAMBOA515@GMAIL.COM</t>
+          <t>JOSELUISDIAZRIVERA68@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>16-02-2026 12:55:37</t>
+          <t>16-02-2026 10:51:16</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>16-02-2026 17:16:42</t>
+          <t>16-02-2026 10:56:29</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -7369,13 +7377,21 @@
           <t>16-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr"/>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>16-02-2026 10:55:40</t>
+        </is>
+      </c>
       <c r="U52" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr"/>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W52" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7383,14 +7399,14 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26050522398420004302</t>
+          <t>26050522384660004235</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
@@ -7407,12 +7423,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>342176</t>
+          <t>344100</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>19994</t>
+          <t>21917</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7422,17 +7438,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ALMA LILIA</t>
+          <t>AIDEE</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SAMANO</t>
+          <t>CORRALES</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7442,14 +7458,10 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6676020923</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>PASEO HIMALAYAS</t>
-        </is>
-      </c>
+          <t>6673888721</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7457,60 +7469,56 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>09-01-1989</t>
+          <t>02-08-2004</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>QUINTEROALMA733@GMAIL.COM</t>
+          <t>AUDEESITI84@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>09-02-2026 14:27:03</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>16-02-2026 14:42:18</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>09-02-2026 14:33:43</t>
+          <t>16-02-2026 14:44:30</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>09-02-2026 14:31:37</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7518,36 +7526,36 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26050522193270003559</t>
+          <t>26050522390910004257</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>342351</t>
+          <t>341416</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20169</t>
+          <t>19234</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7557,17 +7565,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CAROLINA</t>
+          <t xml:space="preserve">OLIVER </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>SIMENTAL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>URTUSUASTEGUI</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7577,75 +7585,67 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6674744257</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>LOMAS</t>
-        </is>
-      </c>
+          <t>6672988277</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>08-04-1994</t>
+          <t>07-09-2003</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CAROLINASOTO.MKT@GMAIL.COM</t>
+          <t>OLIVER4647@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>09-02-2026 17:48:21</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>05-02-2026 18:15:05</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>09-02-2026 17:53:10</t>
+          <t>05-02-2026 18:16:32</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>09-02-2026 17:52:28</t>
-        </is>
-      </c>
+          <t>05-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7653,36 +7653,36 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26050522204390003615</t>
+          <t>26050522115260003288</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Hector Noe Espinoza Ramirez</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>344007</t>
+          <t>344114</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21824</t>
+          <t>21931</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7692,17 +7692,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>JOSE LUIS</t>
+          <t>ALEJANDRO GUADALUPE</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t xml:space="preserve">LEON </t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7712,14 +7712,10 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6671901876</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>CERRO DEL TENAYO 1285</t>
-        </is>
-      </c>
+          <t>6673888815</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7727,64 +7723,56 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>08-10-1988</t>
+          <t>25-12-2008</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>JOSELUISDIAZRIVERA68@GMAIL.COM</t>
+          <t>ALEXLEONLOPEZ08@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>16-02-2026 10:51:16</t>
+          <t>16-02-2026 15:08:28</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>16-02-2026 10:56:29</t>
+          <t>17-02-2026 14:06:24</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>16-02-2026 10:55:40</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7792,14 +7780,14 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26050522384660004235</t>
+          <t>26050522428770004410</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
@@ -7816,12 +7804,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>344100</t>
+          <t>344151</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21917</t>
+          <t>21968</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7831,17 +7819,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>AIDEE</t>
+          <t>JOSE</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CORRALES</t>
+          <t>ACEVO</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7851,35 +7839,31 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6673888721</t>
+          <t>6673549962</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>02-08-2004</t>
+          <t>28-01-1989</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>AUDEESITI84@GMAIL.COM</t>
+          <t>JOSUE.MDZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>16-02-2026 14:42:18</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>16-02-2026 16:17:24</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -7887,22 +7871,22 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>16-02-2026 14:44:30</t>
+          <t>16-02-2026 16:20:42</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>16-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T56" t="inlineStr"/>
@@ -7919,14 +7903,14 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26050522390910004257</t>
+          <t>26050522395110004278</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
@@ -7943,12 +7927,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>345351</t>
+          <t>344402</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>87516</t>
+          <t>22219</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7958,19 +7942,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ROSA LAURA</t>
+          <t>LESLY LIZBETH</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t>ALBA</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>GARCIA</t>
-        </is>
-      </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>52</t>
@@ -7978,7 +7962,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6676945948</t>
+          <t>6679956390</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7989,20 +7973,24 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>12-06-1986</t>
+          <t>20-12-2011</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>178563586@GMAIL.COM</t>
+          <t>ALBALESLY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>20-02-2026 17:09:02</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>17-02-2026 07:40:14</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O57" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -8010,28 +7998,28 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>20-02-2026 17:31:55</t>
+          <t>17-02-2026 08:27:15</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>21-05-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V57" t="inlineStr"/>
@@ -8042,44 +8030,36 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26050522531930004755</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
-        </is>
-      </c>
+          <t>26050522421850004396</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>344114</t>
+          <t>342347</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21931</t>
+          <t>20165</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8089,17 +8069,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ALEJANDRO GUADALUPE</t>
+          <t>JAVIER GEOVANY</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEON </t>
+          <t>PELAYO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>AVILA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8109,7 +8089,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6673888815</t>
+          <t>6671055592</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -8120,24 +8100,20 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>25-12-2008</t>
+          <t>08-11-2013</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>ALEXLEONLOPEZ08@GMAIL.COM</t>
+          <t>JAVPA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>16-02-2026 15:08:28</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>09-02-2026 17:43:15</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -8145,28 +8121,28 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>17-02-2026 14:06:24</t>
+          <t>10-02-2026 16:37:12</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>10-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V58" t="inlineStr"/>
@@ -8177,14 +8153,22 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26050522428770004410</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
+          <t>26050522237050003717</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
@@ -8201,12 +8185,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>344151</t>
+          <t>344408</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21968</t>
+          <t>22225</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8216,17 +8200,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>CLAUDIA VIANEY</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>CHAVARIN</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ACEVO</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8236,28 +8220,28 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6673549962</t>
+          <t>6677853393</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>28-01-1989</t>
+          <t>19-07-1994</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>JOSUE.MDZA@GMAIL.COM</t>
+          <t>EMIR.DAN103@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>16-02-2026 16:17:24</t>
+          <t>17-02-2026 08:06:40</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -8278,18 +8262,18 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>16-02-2026 16:20:42</t>
+          <t>19-02-2026 07:41:19</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
+          <t>19-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V59" t="inlineStr"/>
@@ -8300,11 +8284,19 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26050522395110004278</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr"/>
+          <t>26050522488330004601</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>1899</t>
@@ -8312,24 +8304,24 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>342347</t>
+          <t>344563</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>22380</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8339,17 +8331,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>JAVIER GEOVANY</t>
+          <t>JESUS ADRIAN</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>PELAYO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AVILA</t>
+          <t>POMPA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8359,10 +8351,14 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>6671055592</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>6672490628</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>VOLCAN S</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -8370,52 +8366,64 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>08-11-2013</t>
+          <t>15-07-1987</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>JAVPA@GMAIL.COM</t>
+          <t>JESUSADRIANSP@GMAIL.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>09-02-2026 17:43:15</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
+          <t>17-02-2026 16:22:49</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>10-02-2026 16:37:12</t>
+          <t>17-02-2026 16:47:28</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>10-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>17-02-2026 16:27:05</t>
+        </is>
+      </c>
       <c r="U60" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr"/>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W60" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8423,44 +8431,36 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26050522237050003717</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>ABIGAIL AHUMADA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26050522435210004433</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Hector Noe Espinoza Ramirez</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>344408</t>
+          <t>345641</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>22225</t>
+          <t>87806</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8470,17 +8470,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>CLAUDIA VIANEY</t>
+          <t>JESUS DAVID</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CHAVARIN</t>
+          <t>PARRA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8490,63 +8490,79 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>6677853393</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>6677853209</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>CERRO DEL MEZQUITE</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>19-07-1994</t>
+          <t>02-07-2004</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>EMIR.DAN103@GMAIL.COM</t>
+          <t>DAVIDSILLO2004@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>17-02-2026 08:06:40</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
+          <t>23-02-2026 04:40:43</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>19-02-2026 07:41:19</t>
+          <t>23-02-2026 04:47:31</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>19-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>23-02-2026 04:46:51</t>
+        </is>
+      </c>
       <c r="U61" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8554,44 +8570,36 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26050522488330004601</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>ABIGAIL AHUMADA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26050522565460004828</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>344563</t>
+          <t>342176</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22380</t>
+          <t>19994</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8601,17 +8609,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>JESUS ADRIAN</t>
+          <t>ALMA LILIA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>POMPA</t>
+          <t>SAMANO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8621,39 +8629,35 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6672490628</t>
+          <t>6676020923</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>VOLCAN S</t>
+          <t>PASEO HIMALAYAS</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>15-07-1987</t>
+          <t>09-01-1989</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>JESUSADRIANSP@GMAIL.COM</t>
+          <t>QUINTEROALMA733@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>17-02-2026 16:22:49</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 14:27:03</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8671,17 +8675,17 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>17-02-2026 16:47:28</t>
+          <t>09-02-2026 14:33:43</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>17-02-2026 16:27:05</t>
+          <t>09-02-2026 14:31:37</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -8701,7 +8705,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26050522435210004433</t>
+          <t>26050522193270003559</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr"/>
@@ -8713,7 +8717,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>Hector Noe Espinoza Ramirez</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -8725,12 +8729,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>342708</t>
+          <t>342351</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>20525</t>
+          <t>20169</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8740,17 +8744,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>JESUS ANTONIO</t>
+          <t>CAROLINA</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">AISPURO </t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>IMPERIAL</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8760,12 +8764,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6671966948</t>
+          <t>6674744257</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>ALTURAS</t>
+          <t>LOMAS</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8775,17 +8779,17 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>03-09-1998</t>
+          <t>08-04-1994</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>AISPUROIMPERIALJESUSANTONIO@GMAIL.COM</t>
+          <t>CAROLINASOTO.MKT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>10-02-2026 16:30:39</t>
+          <t>09-02-2026 17:48:21</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -8806,17 +8810,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>10-02-2026 16:35:19</t>
+          <t>09-02-2026 17:53:10</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>10-02-2026 16:34:48</t>
+          <t>09-02-2026 17:52:28</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -8836,7 +8840,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26050522236970003716</t>
+          <t>26050522204390003615</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr"/>
@@ -8860,12 +8864,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>342728</t>
+          <t>345683</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>20545</t>
+          <t>87848</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8875,17 +8879,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SANTIAGO</t>
+          <t>MARTIN GUADALUPE</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RUBI</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>NAVARRETE</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -8895,67 +8899,79 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6674364372</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>6671537144</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>DE LA CANTERA 736</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>17-09-2010</t>
+          <t>29-10-1985</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>SANTI.RUBI102@GMAIL.COM</t>
+          <t>MARTYNCYO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>10-02-2026 16:59:03</t>
+          <t>23-02-2026 09:46:26</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>10-02-2026 17:12:49</t>
+          <t>23-02-2026 09:50:08</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>23-02-2026 09:49:57</t>
+        </is>
+      </c>
       <c r="U64" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr"/>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W64" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8963,14 +8979,14 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26050522238860003735</t>
+          <t>26050522575390004858</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
@@ -8987,12 +9003,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>344544</t>
+          <t>345824</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>22361</t>
+          <t>87989</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9002,17 +9018,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>JESUS ABRAHAM</t>
+          <t>CARLOS HUMBERTO</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>MONTAÑO</t>
+          <t>ONTIVEROS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>ENRIQUEZ</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9022,10 +9038,14 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6675819023</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>6671012383</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>CALLE PRESIDENTE</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -9033,52 +9053,64 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>15-07-2006</t>
+          <t>02-02-2011</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>M0NTAN0JSUS@GMAIL.COM</t>
+          <t>CARLOSHERRERA92242@GMAIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>17-02-2026 16:04:14</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
+          <t>23-02-2026 15:12:22</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>17-02-2026 16:06:36</t>
+          <t>23-02-2026 15:14:50</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>17-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>23-02-2026 15:14:29</t>
+        </is>
+      </c>
       <c r="U65" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr"/>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W65" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9086,36 +9118,36 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26050522432880004420</t>
+          <t>26050522584150004888</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>342381</t>
+          <t>344544</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>20199</t>
+          <t>22361</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9125,17 +9157,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>DANIEL</t>
+          <t>JESUS ABRAHAM</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>MONTAÑO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>OLIVAS</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -9145,35 +9177,31 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6673281864</t>
+          <t>6675819023</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>19-11-1975</t>
+          <t>15-07-2006</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>DCASTROO@AFORECOPPEL.COM</t>
+          <t>M0NTAN0JSUS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>09-02-2026 18:17:28</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>17-02-2026 16:04:14</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -9181,22 +9209,22 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>09-02-2026 18:22:04</t>
+          <t>17-02-2026 16:06:36</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>17-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T66" t="inlineStr"/>
@@ -9213,36 +9241,36 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>26050522206810003627</t>
+          <t>26050522432880004420</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>342619</t>
+          <t>342381</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>20436</t>
+          <t>20199</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9252,17 +9280,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>CAMILA YAMILET</t>
+          <t>DANIEL</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ROMAN</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>NORIEGA</t>
+          <t>OLIVAS</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -9272,32 +9300,28 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>6671538009</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>HACIENDA DEL VALLE</t>
-        </is>
-      </c>
+          <t>6673281864</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>13-07-2007</t>
+          <t>19-11-1975</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>YAMILETHROMAN704@GMAIL.COM</t>
+          <t>DCASTROO@AFORECOPPEL.COM</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>10-02-2026 13:50:59</t>
+          <t>09-02-2026 18:17:28</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -9322,12 +9346,12 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>10-02-2026 15:14:35</t>
+          <t>09-02-2026 18:22:04</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T67" t="inlineStr"/>
@@ -9344,7 +9368,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>26050522233960003704</t>
+          <t>26050522206810003627</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
@@ -9356,24 +9380,24 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>342639</t>
+          <t>345817</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>20456</t>
+          <t>87982</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9383,17 +9407,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>DAMARIS</t>
+          <t>KARLA ANDREA</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAZUETA </t>
+          <t>ENRIQUEZ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>URIARTE</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -9403,12 +9427,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>6674646163</t>
+          <t>6676327717</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>LOMAS</t>
+          <t>PRESIDENTE IGNACIO COMONFORT</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -9418,20 +9442,24 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>01-08-1987</t>
+          <t>06-11-1994</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>BLANCA32NICE@GMAIL.COM</t>
+          <t>KAEL2042@GMAIL.COM</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>10-02-2026 14:32:18</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
+          <t>23-02-2026 15:02:26</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O68" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -9449,17 +9477,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>10-02-2026 14:50:58</t>
+          <t>23-02-2026 15:05:37</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>10-02-2026 14:49:25</t>
+          <t>23-02-2026 15:05:12</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -9479,7 +9507,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>26050522233370003701</t>
+          <t>26050522583660004884</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr"/>
@@ -9491,24 +9519,24 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>343951</t>
+          <t>345644</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>21768</t>
+          <t>87809</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9518,17 +9546,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ADILENE BERENYCE</t>
+          <t>DANIELA</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDINA </t>
+          <t>GAXIOLA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>GASTELUM</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -9538,12 +9566,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>6674304996</t>
+          <t>6672665175</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>COLINAS DE AMBAR 4640</t>
+          <t>AV SICALCO 5998</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9553,17 +9581,17 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>22-10-1990</t>
+          <t>06-09-1995</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>BERECARDENAS102@GMAIL.COM</t>
+          <t>DANIELAGAXIOLAMEXICO@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>16-02-2026 07:28:02</t>
+          <t>23-02-2026 05:40:30</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -9588,17 +9616,17 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>16-02-2026 07:35:05</t>
+          <t>23-02-2026 05:47:38</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>16-02-2026 07:34:19</t>
+          <t>23-02-2026 05:46:25</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -9608,7 +9636,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
@@ -9618,7 +9646,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>26050522379390004219</t>
+          <t>26050522566200004838</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr"/>
@@ -9642,12 +9670,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>343138</t>
+          <t>342619</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>20955</t>
+          <t>20436</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9657,17 +9685,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NORMA ALICIA</t>
+          <t>CAMILA YAMILET</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>ROMAN</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>NORIEGA</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -9677,12 +9705,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>6674953867</t>
+          <t>6671538009</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>SAN ISIDRO</t>
+          <t>HACIENDA DEL VALLE</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9692,60 +9720,56 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>27-09-1971</t>
+          <t>13-07-2007</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>NORMAALICIA@GMAIL.COM</t>
+          <t>YAMILETHROMAN704@GMAIL.COM</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>11-02-2026 20:48:11</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>10-02-2026 13:50:59</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>11-02-2026 20:51:25</t>
+          <t>10-02-2026 15:14:35</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>11-02-2026 20:50:52</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9753,14 +9777,14 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>26050522278960003916</t>
+          <t>26050522233960003704</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
@@ -9777,12 +9801,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>343911</t>
+          <t>342639</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>21728</t>
+          <t>20456</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9792,17 +9816,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>CARLOS GABRIEL</t>
+          <t>DAMARIS</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t xml:space="preserve">ZAZUETA </t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>URIARTE</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -9812,39 +9836,35 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>6674119225</t>
+          <t>6674646163</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>RAFAEL MARTINEZ 2620</t>
+          <t>LOMAS</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>01-12-2000</t>
+          <t>01-08-1987</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>CMEZAGR10@GMAIL.COM</t>
+          <t>BLANCA32NICE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>16-02-2026 05:00:53</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>10-02-2026 14:32:18</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -9862,17 +9882,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>16-02-2026 05:08:16</t>
+          <t>10-02-2026 14:50:58</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>16-02-2026 05:04:59</t>
+          <t>10-02-2026 14:49:25</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -9892,7 +9912,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>26050522369740004204</t>
+          <t>26050522233370003701</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr"/>
@@ -9916,12 +9936,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>344219</t>
+          <t>342708</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>22036</t>
+          <t>20525</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -9931,17 +9951,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>JETSSY YERANI</t>
+          <t>JESUS ANTONIO</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t xml:space="preserve">AISPURO </t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>IMPERIAL</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -9951,12 +9971,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>6671955010</t>
+          <t>6671966948</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>PRADOS</t>
+          <t>ALTURAS</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9966,52 +9986,48 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>01-11-2002</t>
+          <t>03-09-1998</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>CHJETSSY@GMAIL.COM</t>
+          <t>AISPUROIMPERIALJESUSANTONIO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>16-02-2026 17:35:23</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>10-02-2026 16:30:39</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>16-02-2026 17:40:31</t>
+          <t>10-02-2026 16:35:19</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>16-02-2026 17:39:31</t>
+          <t>10-02-2026 16:34:48</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -10021,7 +10037,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
@@ -10031,14 +10047,14 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>26050522400210004318</t>
+          <t>26050522236970003716</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
@@ -10055,12 +10071,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>344330</t>
+          <t>342728</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>22147</t>
+          <t>20545</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -10070,17 +10086,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>CRISTOPHER LUCIANO</t>
+          <t>SANTIAGO</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ZAVALA</t>
+          <t>RUBI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ANGULO</t>
+          <t>NAVARRETE</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -10090,7 +10106,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>6671833791</t>
+          <t>6674364372</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -10101,17 +10117,17 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>04-09-2013</t>
+          <t>17-09-2010</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>CLOSETYCOCINASSR@GMAIL.COM</t>
+          <t>SANTI.RUBI102@GMAIL.COM</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>16-02-2026 19:04:29</t>
+          <t>10-02-2026 16:59:03</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -10136,18 +10152,18 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>16-02-2026 19:14:09</t>
+          <t>10-02-2026 17:12:49</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V73" t="inlineStr"/>
@@ -10158,7 +10174,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>26050522407600004347</t>
+          <t>26050522238860003735</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr"/>
@@ -10170,24 +10186,24 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>344602</t>
+          <t>343951</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>22419</t>
+          <t>21768</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10197,17 +10213,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ROXANA GABRIELA</t>
+          <t>ADILENE BERENYCE</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SAMANIEGO</t>
+          <t xml:space="preserve">MEDINA </t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -10217,32 +10233,32 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>6471226799</t>
+          <t>6674304996</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>C MIGUEL HIDALGO</t>
+          <t>COLINAS DE AMBAR 4640</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>23-11-1999</t>
+          <t>22-10-1990</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>ROXANASAMANIEGO487@GMAIL.COM</t>
+          <t>BERECARDENAS102@GMAIL.COM</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>17-02-2026 17:21:04</t>
+          <t>16-02-2026 07:28:02</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -10267,17 +10283,17 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>17-02-2026 17:25:35</t>
+          <t>16-02-2026 07:35:05</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>17-02-2026 17:24:51</t>
+          <t>16-02-2026 07:34:19</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -10297,7 +10313,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>26050522437350004443</t>
+          <t>26050522379390004219</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr"/>
@@ -10321,12 +10337,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>344348</t>
+          <t>344219</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>22165</t>
+          <t>22036</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10336,17 +10352,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>OLIBLISH</t>
+          <t>JETSSY YERANI</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RECENDIZ</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SMER</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -10356,12 +10372,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>6671404207</t>
+          <t>6671955010</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>HACIENDA</t>
+          <t>PRADOS</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -10371,42 +10387,42 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>30-08-2001</t>
+          <t>01-11-2002</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>OLIBLISHRECENDIZ@GMAIL.COM</t>
+          <t>CHJETSSY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>16-02-2026 19:50:40</t>
+          <t>16-02-2026 17:35:23</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>16-02-2026 19:55:43</t>
+          <t>16-02-2026 17:40:31</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -10416,7 +10432,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>16-02-2026 19:54:36</t>
+          <t>16-02-2026 17:39:31</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -10436,36 +10452,36 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>26050522409440004358</t>
+          <t>26050522400210004318</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>344406</t>
+          <t>344330</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>22223</t>
+          <t>22147</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10475,17 +10491,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>MARIA JOSE</t>
+          <t>CRISTOPHER LUCIANO</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>VELAZQUEZ</t>
+          <t>ZAVALA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>OLIVAS</t>
+          <t>ANGULO</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -10495,31 +10511,35 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>6674694221</t>
+          <t>6671833791</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>20-06-2006</t>
+          <t>04-09-2013</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>MARIAJOSEVELAZQUEZOLIVAS@GMAIL.COM</t>
+          <t>CLOSETYCOCINASSR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>17-02-2026 08:01:38</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
+          <t>16-02-2026 19:04:29</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O76" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -10527,22 +10547,22 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>17-02-2026 08:04:53</t>
+          <t>16-02-2026 19:14:09</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>17-05-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T76" t="inlineStr"/>
@@ -10559,36 +10579,36 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>26050522421390004393</t>
+          <t>26050522407600004347</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="inlineStr"/>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>344529</t>
+          <t>343138</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>22346</t>
+          <t>20955</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -10598,17 +10618,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>JACQUELINE QUETZALI</t>
+          <t>NORMA ALICIA</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>PERAZA</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -10618,10 +10638,14 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>6672654267</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>6674953867</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -10629,52 +10653,60 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>22-10-1990</t>
+          <t>27-09-1971</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>QUETZALI_JACKY@HOTMAIL.COM</t>
+          <t>NORMAALICIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>17-02-2026 15:23:38</t>
+          <t>11-02-2026 20:48:11</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>17-02-2026 15:31:57</t>
+          <t>11-02-2026 20:51:25</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>17-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T77" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>11-02-2026 20:50:52</t>
+        </is>
+      </c>
       <c r="U77" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V77" t="inlineStr"/>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W77" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10682,36 +10714,36 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>26050522431570004417</t>
+          <t>26050522278960003916</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>344684</t>
+          <t>344602</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>22419</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -10721,17 +10753,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LAURA FERNANDA</t>
+          <t>ROXANA GABRIELA</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">BELTRAN </t>
+          <t>SAMANIEGO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -10741,53 +10773,57 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>6671852522</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>6471226799</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>C MIGUEL HIDALGO</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>30-12-2012</t>
+          <t>23-11-1999</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>666PEREZADRIA@GMAIL.COM</t>
+          <t>ROXANASAMANIEGO487@GMAIL.COM</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>17-02-2026 19:24:52</t>
+          <t>17-02-2026 17:21:04</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>17-02-2026 19:26:14</t>
+          <t>17-02-2026 17:25:35</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -10795,13 +10831,21 @@
           <t>17-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T78" t="inlineStr"/>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>17-02-2026 17:24:51</t>
+        </is>
+      </c>
       <c r="U78" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V78" t="inlineStr"/>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W78" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10809,22 +10853,1090 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>26050522444240004472</t>
+          <t>26050522437350004443</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="inlineStr"/>
       <c r="AA78" t="inlineStr">
         <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>343911</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>21728</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>CARLOS GABRIEL</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RAMIREZ</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>MEZA</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>6674119225</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>RAFAEL MARTINEZ 2620</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>01-12-2000</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>CMEZAGR10@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>16-02-2026 05:00:53</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>16-02-2026 05:08:16</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>16-02-2026 05:04:59</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>26050522369740004204</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>344348</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>22165</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>OLIBLISH</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RECENDIZ</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>SMER</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>6671404207</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>HACIENDA</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>30-08-2001</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>OLIBLISHRECENDIZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>16-02-2026 19:50:40</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>16-02-2026 19:55:43</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>16-02-2026 19:54:36</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>26050522409440004358</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>Carlos Aurelio Monzon Ayala</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>344406</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>22223</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>MARIA JOSE</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>VELAZQUEZ</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>OLIVAS</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>6674694221</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>20-06-2006</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>MARIAJOSEVELAZQUEZOLIVAS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>17-02-2026 08:01:38</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>17-02-2026 08:04:53</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>17-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>26050522421390004393</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>Gilberto Tavarez Soto</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>344529</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>22346</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>JACQUELINE QUETZALI</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>PERAZA</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>6672654267</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>22-10-1990</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>QUETZALI_JACKY@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>17-02-2026 15:23:38</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>17-02-2026 15:31:57</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>17-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>26050522431570004417</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr"/>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>Carlos Aurelio Monzon Ayala</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>344684</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LAURA FERNANDA</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BELTRAN </t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>MORENO</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>6671852522</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>30-12-2012</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>666PEREZADRIA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>17-02-2026 19:24:52</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
           <t>549</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>17-02-2026 19:26:14</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>26050522444240004472</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr"/>
+      <c r="Z83" t="inlineStr"/>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
         <is>
           <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>345682</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>87847</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ALMA ROSA</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>ESPARZA</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>BUENO</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>6675066381</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>DE LA CANTERA 736</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>20-02-1985</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>ALMA.ESPARZA.BUENO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>23-02-2026 09:34:05</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>23-02-2026 09:45:00</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>23-02-2026 09:39:21</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>26050522575290004857</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr"/>
+      <c r="Z84" t="inlineStr"/>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>Gilberto Tavarez Soto</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>345749</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>87914</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SARA </t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>ROCHA</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>PARRA</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>6675758326</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>CALLE PRIMERA 697</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>05-01-1984</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>SARA.13@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>23-02-2026 12:47:26</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>23-02-2026 12:53:53</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>23-02-2026 12:52:28</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>26050522579700004867</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr"/>
+      <c r="Z85" t="inlineStr"/>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>345819</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>87984</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>HUMBERTO GUADALUPE</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>ONTIVEROS</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>HERRERA</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>6671837620</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CALLE PRESIDENTE </t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>25-03-1990</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>HUM60H2503@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>23-02-2026 15:08:17</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>23-02-2026 15:10:55</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>23-02-2026 15:10:21</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>26050522583980004887</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr"/>
+      <c r="Z86" t="inlineStr"/>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>Carlos Aurelio Monzon Ayala</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
         <is>
           <t>con rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN ISIDRO CUL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN ISIDRO CUL.xlsx
@@ -2325,12 +2325,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>339875</t>
+          <t>325665</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17693</t>
+          <t>22604</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2340,17 +2340,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MARILYN JANETH</t>
+          <t>XATZYRI YURALY</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>AISPURO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6671398253</t>
+          <t>6864307582</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2371,17 +2371,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>07-03-1987</t>
+          <t>22-02-2008</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>JANETHMARO@GMAIL.COM</t>
+          <t>XATZYRIVALENZUELA656@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-02-2026 07:00:20</t>
+          <t>27-11-2025 16:11:06</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2396,22 +2396,22 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-02-2026 07:00:47</t>
+          <t>09-02-2026 10:18:24</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2428,14 +2428,14 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26050521999140002837</t>
+          <t>26050522187630003547</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2452,12 +2452,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>340211</t>
+          <t>339875</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>18029</t>
+          <t>17693</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MATTEA GUADALUPE</t>
+          <t>MARILYN JANETH</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6674170714</t>
+          <t>6671398253</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2498,17 +2498,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>08-06-1998</t>
+          <t>07-03-1987</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>MATTEAGEG@GMAIL.COM</t>
+          <t>JANETHMARO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-02-2026 15:24:37</t>
+          <t>02-02-2026 07:00:20</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2523,17 +2523,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-02-2026 15:32:28</t>
+          <t>02-02-2026 07:00:47</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2544,7 +2544,7 @@
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V16" t="inlineStr"/>
@@ -2555,36 +2555,36 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26050522014630002901</t>
+          <t>26050521999140002837</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>239092</t>
+          <t>340211</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>36597</t>
+          <t>18029</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2594,17 +2594,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DANIELA ADILENE</t>
+          <t>MATTEA GUADALUPE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RETAMOZA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2614,14 +2614,10 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6673198984</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>PRIVADA LA CAPILLA 9061</t>
-        </is>
-      </c>
+          <t>6674170714</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2629,64 +2625,56 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>25-08-1998</t>
+          <t>08-06-1998</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>DANI_RETAMOZA_E@HOTMAIL.COM</t>
+          <t>MATTEAGEG@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>10-06-2024 19:47:11</t>
+          <t>02-02-2026 15:24:37</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>24-02-2026 07:22:21</t>
+          <t>02-02-2026 15:32:28</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>24-02-2026 07:21:53</t>
-        </is>
-      </c>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2694,22 +2682,14 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26050522611380004986</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Carmen Michel Navarrete  Nevarez</t>
-        </is>
-      </c>
+          <t>26050522014630002901</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2726,12 +2706,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>340284</t>
+          <t>239092</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18102</t>
+          <t>36597</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2741,17 +2721,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELIZABETH </t>
+          <t>DANIELA ADILENE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CABRERA</t>
+          <t>RETAMOZA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2761,12 +2741,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6674631919</t>
+          <t>6673198984</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>LOMAS DE SAN ISIDRO</t>
+          <t>PRIVADA LA CAPILLA 9061</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2776,52 +2756,52 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>21-10-1985</t>
+          <t>25-08-1998</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>ECSS35064@GMAIL.COM</t>
+          <t>DANI_RETAMOZA_E@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>02-02-2026 16:43:43</t>
+          <t>10-06-2024 19:47:11</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>02-02-2026 16:49:13</t>
+          <t>24-02-2026 07:22:21</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>24-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>02-02-2026 16:49:03</t>
+          <t>24-02-2026 07:21:53</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2831,7 +2811,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2841,19 +2821,27 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26050522017320002909</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+          <t>26050522611380004986</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Carmen Michel Navarrete  Nevarez</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2865,12 +2853,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>340294</t>
+          <t>340284</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18112</t>
+          <t>18102</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2880,17 +2868,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>JONATHAN ALEXIS</t>
+          <t xml:space="preserve">ELIZABETH </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MACIAS</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>CABRERA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2900,53 +2888,57 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6672172754</t>
+          <t>6674631919</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>BARRANCOS</t>
+          <t>LOMAS DE SAN ISIDRO</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>24-01-1993</t>
+          <t>21-10-1985</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>JONATHANALEXISMACIASFLORES@GMAIL.COM</t>
+          <t>ECSS35064@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-02-2026 16:57:39</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>02-02-2026 16:43:43</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>02-02-2026 17:00:06</t>
+          <t>02-02-2026 16:49:13</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2956,7 +2948,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>02-02-2026 16:59:50</t>
+          <t>02-02-2026 16:49:03</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2966,7 +2958,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2976,14 +2968,14 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26050522017750002911</t>
+          <t>26050522017320002909</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -3000,12 +2992,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>340302</t>
+          <t>340294</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18120</t>
+          <t>18112</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3015,17 +3007,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRANCISCO </t>
+          <t>JONATHAN ALEXIS</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t>MACIAS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BURGOS</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3035,12 +3027,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6671777382</t>
+          <t>6672172754</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>PRADOS DEL SOL</t>
+          <t>BARRANCOS</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3050,17 +3042,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>19-11-1990</t>
+          <t>24-01-1993</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>FRANCISCO123456789@HOTMAIL.COM</t>
+          <t>JONATHANALEXISMACIASFLORES@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-02-2026 17:06:58</t>
+          <t>02-02-2026 16:57:39</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3081,7 +3073,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>02-02-2026 17:10:35</t>
+          <t>02-02-2026 17:00:06</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -3091,7 +3083,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>02-02-2026 17:10:24</t>
+          <t>02-02-2026 16:59:50</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3111,7 +3103,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26050522018100002915</t>
+          <t>26050522017750002911</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3123,24 +3115,24 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>325665</t>
+          <t>340302</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>22604</t>
+          <t>18120</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3150,17 +3142,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>XATZYRI YURALY</t>
+          <t xml:space="preserve">FRANCISCO </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AISPURO</t>
+          <t>BURGOS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3170,67 +3162,75 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6864307582</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>6671777382</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>PRADOS DEL SOL</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>22-02-2008</t>
+          <t>19-11-1990</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>XATZYRIVALENZUELA656@GMAIL.COM</t>
+          <t>FRANCISCO123456789@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>27-11-2025 16:11:06</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>02-02-2026 17:06:58</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>09-02-2026 10:18:24</t>
+          <t>02-02-2026 17:10:35</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>02-02-2026 17:10:24</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3238,14 +3238,14 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26050522187630003547</t>
+          <t>26050522018100002915</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -5136,12 +5136,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>341538</t>
+          <t>341183</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19356</t>
+          <t>19001</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5151,17 +5151,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>JACIEL MANUEL</t>
+          <t>ISAAC ALEJANDRO</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CASTELLANOS</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>PICOS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5171,14 +5171,10 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6677900100</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>ARTICULO 27 3491</t>
-        </is>
-      </c>
+          <t>6675823775</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5186,64 +5182,52 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>30-03-1991</t>
+          <t>21-08-2006</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>JACIEL.CASTELLANOS@HOTMAIL.COM</t>
+          <t>ISAACLLANES999@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>06-02-2026 12:12:23</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>04-02-2026 20:01:05</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>17-02-2026 10:58:43</t>
+          <t>16-02-2026 19:00:46</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>17-02-2026 10:56:07</t>
-        </is>
-      </c>
+          <t>16-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5251,7 +5235,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26050522424560004401</t>
+          <t>26050522406720004345</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -5261,34 +5245,34 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>ABIGAIL AHUMADA MARTINEZ</t>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>342052</t>
+          <t>341538</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>19870</t>
+          <t>19356</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5298,17 +5282,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AMAYRANI YESSENIA</t>
+          <t>JACIEL MANUEL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUINTERO </t>
+          <t>CASTELLANOS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANDRADE </t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5318,35 +5302,39 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6674832993</t>
+          <t>6677900100</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>JOEGE ROMERO ZAZUETA 2306</t>
+          <t>ARTICULO 27 3491</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>21-11-2001</t>
+          <t>30-03-1991</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>AMAYRANI_QUINTERO@HOTMAIL.COM</t>
+          <t>JACIEL.CASTELLANOS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>09-02-2026 08:35:57</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>06-02-2026 12:12:23</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5364,17 +5352,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>09-02-2026 08:46:58</t>
+          <t>17-02-2026 10:58:43</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>09-02-2026 08:46:15</t>
+          <t>17-02-2026 10:56:07</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5394,11 +5382,19 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26050522185300003537</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
+          <t>26050522424560004401</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>499</t>
@@ -5418,12 +5414,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>342107</t>
+          <t>342052</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>19925</t>
+          <t>19870</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5433,17 +5429,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NAUN ALAN</t>
+          <t>AMAYRANI YESSENIA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CHIQUETE</t>
+          <t xml:space="preserve">QUINTERO </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PALOMAREZ</t>
+          <t xml:space="preserve">ANDRADE </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5453,32 +5449,32 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6677976901</t>
+          <t>6674832993</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>CERRO DEL CHIQUIHUITE</t>
+          <t>JOEGE ROMERO ZAZUETA 2306</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>02-02-1994</t>
+          <t>21-11-2001</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>NAUNALANCHIQUETE@GMAIL.COM</t>
+          <t>AMAYRANI_QUINTERO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>09-02-2026 11:16:00</t>
+          <t>09-02-2026 08:35:57</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5499,7 +5495,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>09-02-2026 11:18:05</t>
+          <t>09-02-2026 08:46:58</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -5509,7 +5505,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>09-02-2026 11:17:49</t>
+          <t>09-02-2026 08:46:15</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5519,7 +5515,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -5529,7 +5525,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26050522188750003551</t>
+          <t>26050522185300003537</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
@@ -5541,7 +5537,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5553,12 +5549,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>341209</t>
+          <t>342107</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>19027</t>
+          <t>19925</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5568,17 +5564,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ROCIO MARGARITA</t>
+          <t>NAUN ALAN</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>CHIQUETE</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CIFUENTES</t>
+          <t>PALOMAREZ</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5588,32 +5584,32 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6673305169</t>
+          <t>6677976901</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>CAPISTRANO</t>
+          <t>CERRO DEL CHIQUIHUITE</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>19-08-1971</t>
+          <t>02-02-1994</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CRED9011037@GMAIL.COM</t>
+          <t>NAUNALANCHIQUETE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>05-02-2026 05:19:52</t>
+          <t>09-02-2026 11:16:00</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5634,17 +5630,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>05-02-2026 05:25:19</t>
+          <t>09-02-2026 11:18:05</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>05-02-2026 05:25:01</t>
+          <t>09-02-2026 11:17:49</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5654,7 +5650,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -5664,7 +5660,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26050522097780003210</t>
+          <t>26050522188750003551</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
@@ -5676,7 +5672,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5688,12 +5684,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>341210</t>
+          <t>341209</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>19028</t>
+          <t>19027</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5703,17 +5699,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ODALIZ BRISEIDA</t>
+          <t>ROCIO MARGARITA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PATRON</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>CIFUENTES</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5723,7 +5719,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6671988044</t>
+          <t>6673305169</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5738,17 +5734,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>10-04-2002</t>
+          <t>19-08-1971</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>PATRON.QUINTERO.ODALIZ108@GMAIL.COM</t>
+          <t>CRED9011037@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>05-02-2026 05:31:53</t>
+          <t>05-02-2026 05:19:52</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5769,7 +5765,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>05-02-2026 05:36:08</t>
+          <t>05-02-2026 05:25:19</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5779,7 +5775,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>05-02-2026 05:35:58</t>
+          <t>05-02-2026 05:25:01</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5799,7 +5795,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26050522097920003212</t>
+          <t>26050522097780003210</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
@@ -5823,12 +5819,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>341183</t>
+          <t>341210</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>19001</t>
+          <t>19028</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5838,17 +5834,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ISAAC ALEJANDRO</t>
+          <t>ODALIZ BRISEIDA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>PATRON</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PICOS</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5858,63 +5854,75 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6675823775</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>6671988044</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>CAPISTRANO</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>21-08-2006</t>
+          <t>10-04-2002</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>ISAACLLANES999@GMAIL.COM</t>
+          <t>PATRON.QUINTERO.ODALIZ108@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>04-02-2026 20:01:05</t>
+          <t>05-02-2026 05:31:53</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>16-02-2026 19:00:46</t>
+          <t>05-02-2026 05:36:08</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr"/>
+          <t>05-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>05-02-2026 05:35:58</t>
+        </is>
+      </c>
       <c r="U41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5922,32 +5930,24 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26050522406720004345</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
-        </is>
-      </c>
+          <t>26050522097920003212</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -6351,12 +6351,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>342706</t>
+          <t>344402</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20523</t>
+          <t>22219</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6366,17 +6366,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>JESUS ANDRES</t>
+          <t>LESLY LIZBETH</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>LEY</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>ALBA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6386,75 +6386,67 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6678403979</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>MISION DE SAN MIGUEL 8559</t>
-        </is>
-      </c>
+          <t>6679956390</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>30-06-2000</t>
+          <t>20-12-2011</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>LEYCASTROANDRES@GMAIL.COM</t>
+          <t>ALBALESLY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>10-02-2026 16:29:39</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>17-02-2026 07:40:14</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>10-02-2026 16:37:39</t>
+          <t>17-02-2026 08:27:15</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>10-02-2026 16:37:12</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6462,36 +6454,36 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26050522237060003718</t>
+          <t>26050522421850004396</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>341207</t>
+          <t>345212</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>19025</t>
+          <t>87377</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6501,17 +6493,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FRANCISCO ALEJANDRO</t>
+          <t>KIMBERLY</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>PAVIA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>PEÑUELAS</t>
+          <t>PAYAN</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6521,35 +6513,39 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6673168474</t>
+          <t>6674812322</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>MANUEL PAYNO 2161</t>
+          <t>BELIZARIO DOMINGUEZ 5841</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>25-10-1997</t>
+          <t>26-01-1999</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>ALEX209725@GMAIL.COM</t>
+          <t>KIMPAVIIA99@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>05-02-2026 04:45:19</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>20-02-2026 04:47:34</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6567,17 +6563,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>10-02-2026 04:46:51</t>
+          <t>27-02-2026 04:54:17</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>27-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>10-02-2026 04:44:41</t>
+          <t>27-02-2026 04:52:45</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6587,7 +6583,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -6597,7 +6593,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26050522216510003662</t>
+          <t>26050522698550005336</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -6607,7 +6603,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>ABIGAIL AHUMADA MARTINEZ</t>
+          <t>Carmen Michel Navarrete  Nevarez</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6629,12 +6625,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>344402</t>
+          <t>345351</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>22219</t>
+          <t>87516</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6644,17 +6640,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LESLY LIZBETH</t>
+          <t>ROSA LAURA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>ALBA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ALBA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6664,7 +6660,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6679956390</t>
+          <t>6676945948</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6675,24 +6671,20 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>20-12-2011</t>
+          <t>12-06-1986</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>ALBALESLY@GMAIL.COM</t>
+          <t>178563586@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>17-02-2026 07:40:14</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>20-02-2026 17:09:02</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -6700,28 +6692,28 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>17-02-2026 08:27:15</t>
+          <t>20-02-2026 17:31:55</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>21-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V47" t="inlineStr"/>
@@ -6732,36 +6724,44 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26050522421850004396</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
+          <t>26050522531930004755</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>342054</t>
+          <t>342706</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>19872</t>
+          <t>20523</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6771,17 +6771,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>YAZMIN</t>
+          <t>JESUS ANDRES</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>LEY</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6791,32 +6791,32 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>8186031726</t>
+          <t>6678403979</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>DE LAS VEREDAS</t>
+          <t>MISION DE SAN MIGUEL 8559</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>28-07-2001</t>
+          <t>30-06-2000</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>YAZ.LOPEZ17@OUTLOOK.COM</t>
+          <t>LEYCASTROANDRES@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>09-02-2026 08:38:56</t>
+          <t>10-02-2026 16:29:39</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -6837,17 +6837,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>09-02-2026 08:54:38</t>
+          <t>10-02-2026 16:37:39</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>09-02-2026 08:52:19</t>
+          <t>10-02-2026 16:37:12</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26050522185440003538</t>
+          <t>26050522237060003718</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
@@ -6879,24 +6879,24 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>345212</t>
+          <t>342054</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>87377</t>
+          <t>19872</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6906,17 +6906,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>KIMBERLY</t>
+          <t>YAZMIN</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PAVIA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>PAYAN</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6674812322</t>
+          <t>8186031726</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>BELIZARIO DOMINGUEZ 5841</t>
+          <t>DE LAS VEREDAS</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6941,24 +6941,20 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>26-01-1999</t>
+          <t>28-07-2001</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>KIMPAVIIA99@GMAIL.COM</t>
+          <t>YAZ.LOPEZ17@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>20-02-2026 04:47:34</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 08:38:56</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6976,17 +6972,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>27-02-2026 04:54:17</t>
+          <t>09-02-2026 08:54:38</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>27-02-2026 04:52:45</t>
+          <t>09-02-2026 08:52:19</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -6996,7 +6992,7 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -7006,19 +7002,11 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26050522698550005336</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>Carmen Michel Navarrete  Nevarez</t>
-        </is>
-      </c>
+          <t>26050522185440003538</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
           <t>499</t>
@@ -7026,24 +7014,24 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>345351</t>
+          <t>341207</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>87516</t>
+          <t>19025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7053,17 +7041,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ROSA LAURA</t>
+          <t>FRANCISCO ALEJANDRO</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ALBA</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>PEÑUELAS</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7073,63 +7061,75 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6676945948</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>6673168474</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>MANUEL PAYNO 2161</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>12-06-1986</t>
+          <t>25-10-1997</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>178563586@GMAIL.COM</t>
+          <t>ALEX209725@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>20-02-2026 17:09:02</t>
+          <t>05-02-2026 04:45:19</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>20-02-2026 17:31:55</t>
+          <t>10-02-2026 04:46:51</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>21-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>10-02-2026 04:44:41</t>
+        </is>
+      </c>
       <c r="U50" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr"/>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W50" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7137,7 +7137,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26050522531930004755</t>
+          <t>26050522216510003662</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -7147,12 +7147,12 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
@@ -7439,12 +7439,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>342376</t>
+          <t>342347</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20194</t>
+          <t>20165</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>DANIEL SEBASTIAN</t>
+          <t>JAVIER GEOVANY</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>PELAYO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>AVILA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7474,35 +7474,31 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6671384521</t>
+          <t>6671055592</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>15-05-2009</t>
+          <t>08-11-2013</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>DANIELCASTRO09410315@GMAIL.COM</t>
+          <t>JAVPA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>09-02-2026 18:13:14</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>09-02-2026 17:43:15</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -7510,22 +7506,22 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>09-02-2026 18:15:27</t>
+          <t>10-02-2026 16:37:12</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -7542,36 +7538,44 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26050522206250003624</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
+          <t>26050522237050003717</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>343449</t>
+          <t>346270</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21266</t>
+          <t>88435</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7581,17 +7585,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BIANCA AZUCENA</t>
+          <t>ANTONIA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>LANDELL</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>PARRA</t>
+          <t>HEREDIA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7601,12 +7605,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6674842233</t>
+          <t>6674928716</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>MINA DEL PEÑON BLANCO 560</t>
+          <t>IBERICA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7616,20 +7620,24 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>21-12-2000</t>
+          <t>13-06-1969</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>BIANCALANDELL21@GMAIL.COM</t>
+          <t>ANTONIACAMACHOHEREDIA23@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>13-02-2026 09:39:01</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>24-02-2026 17:42:56</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O54" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7647,17 +7655,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>13-02-2026 09:48:06</t>
+          <t>27-02-2026 17:13:33</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>27-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>13-02-2026 09:45:49</t>
+          <t>27-02-2026 17:12:56</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -7667,7 +7675,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7677,11 +7685,19 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26050522317680004073</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
+          <t>26050522720040005389</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>499</t>
@@ -7689,7 +7705,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -7701,12 +7717,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>342347</t>
+          <t>342376</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>20194</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7716,17 +7732,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>JAVIER GEOVANY</t>
+          <t>DANIEL SEBASTIAN</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>PELAYO</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>AVILA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7736,31 +7752,35 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6671055592</t>
+          <t>6671384521</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>08-11-2013</t>
+          <t>15-05-2009</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>JAVPA@GMAIL.COM</t>
+          <t>DANIELCASTRO09410315@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>09-02-2026 17:43:15</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>09-02-2026 18:13:14</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O55" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -7768,22 +7788,22 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>10-02-2026 16:37:12</t>
+          <t>09-02-2026 18:15:27</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>10-05-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T55" t="inlineStr"/>
@@ -7800,44 +7820,36 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26050522237050003717</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>ABIGAIL AHUMADA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26050522206250003624</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>346270</t>
+          <t>343449</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>88435</t>
+          <t>21266</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7847,17 +7859,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ANTONIA</t>
+          <t>BIANCA AZUCENA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>LANDELL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>HEREDIA</t>
+          <t>PARRA</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7867,12 +7879,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6674928716</t>
+          <t>6674842233</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>IBERICA</t>
+          <t>MINA DEL PEÑON BLANCO 560</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7882,24 +7894,20 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>13-06-1969</t>
+          <t>21-12-2000</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>ANTONIACAMACHOHEREDIA23@GMAIL.COM</t>
+          <t>BIANCALANDELL21@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>24-02-2026 17:42:56</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>13-02-2026 09:39:01</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7917,17 +7925,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>27-02-2026 17:13:33</t>
+          <t>13-02-2026 09:48:06</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>27-02-2026 17:12:56</t>
+          <t>13-02-2026 09:45:49</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -7937,7 +7945,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -7947,19 +7955,11 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26050522720040005389</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>ABIGAIL AHUMADA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26050522317680004073</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
           <t>499</t>
@@ -7967,7 +7967,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -7979,12 +7979,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>342708</t>
+          <t>346785</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>20525</t>
+          <t>88950</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7994,17 +7994,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>JESUS ANTONIO</t>
+          <t>SILVIA G</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">AISPURO </t>
+          <t xml:space="preserve">GASTELUM </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>IMPERIAL</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8014,14 +8014,10 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6671966948</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>ALTURAS</t>
-        </is>
-      </c>
+          <t>6673817224</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8029,60 +8025,56 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>03-09-1998</t>
+          <t>31-01-1990</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>AISPUROIMPERIALJESUSANTONIO@GMAIL.COM</t>
+          <t>SILVIAGASTELUM18@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>10-02-2026 16:30:39</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>26-02-2026 17:46:56</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>10-02-2026 16:35:19</t>
+          <t>26-02-2026 17:48:45</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>10-02-2026 16:34:48</t>
-        </is>
-      </c>
+          <t>26-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8090,14 +8082,14 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26050522236970003716</t>
+          <t>26050522690790005306</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
@@ -8114,12 +8106,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>342728</t>
+          <t>342708</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>20545</t>
+          <t>20525</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8129,17 +8121,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SANTIAGO</t>
+          <t>JESUS ANTONIO</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RUBI</t>
+          <t xml:space="preserve">AISPURO </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>NAVARRETE</t>
+          <t>IMPERIAL</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8149,53 +8141,53 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6674364372</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>6671966948</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>ALTURAS</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>17-09-2010</t>
+          <t>03-09-1998</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>SANTI.RUBI102@GMAIL.COM</t>
+          <t>AISPUROIMPERIALJESUSANTONIO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>10-02-2026 16:59:03</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>10-02-2026 16:30:39</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>10-02-2026 17:12:49</t>
+          <t>10-02-2026 16:35:19</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -8203,13 +8195,21 @@
           <t>10-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr"/>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>10-02-2026 16:34:48</t>
+        </is>
+      </c>
       <c r="U58" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr"/>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W58" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8217,36 +8217,36 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26050522238860003735</t>
+          <t>26050522236970003716</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>342381</t>
+          <t>342728</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>20199</t>
+          <t>20545</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8256,17 +8256,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>DANIEL</t>
+          <t>SANTIAGO</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>RUBI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>OLIVAS</t>
+          <t>NAVARRETE</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6673281864</t>
+          <t>6674364372</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8287,17 +8287,17 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>19-11-1975</t>
+          <t>17-09-2010</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>DCASTROO@AFORECOPPEL.COM</t>
+          <t>SANTI.RUBI102@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>09-02-2026 18:17:28</t>
+          <t>10-02-2026 16:59:03</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -8322,12 +8322,12 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>09-02-2026 18:22:04</t>
+          <t>10-02-2026 17:12:49</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T59" t="inlineStr"/>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26050522206810003627</t>
+          <t>26050522238860003735</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr"/>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -8368,12 +8368,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>342619</t>
+          <t>342381</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>20436</t>
+          <t>20199</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8383,17 +8383,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CAMILA YAMILET</t>
+          <t>DANIEL</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ROMAN</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>NORIEGA</t>
+          <t>OLIVAS</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8403,32 +8403,28 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>6671538009</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>HACIENDA DEL VALLE</t>
-        </is>
-      </c>
+          <t>6673281864</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>13-07-2007</t>
+          <t>19-11-1975</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>YAMILETHROMAN704@GMAIL.COM</t>
+          <t>DCASTROO@AFORECOPPEL.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>10-02-2026 13:50:59</t>
+          <t>09-02-2026 18:17:28</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -8453,12 +8449,12 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>10-02-2026 15:14:35</t>
+          <t>09-02-2026 18:22:04</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T60" t="inlineStr"/>
@@ -8475,7 +8471,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26050522233960003704</t>
+          <t>26050522206810003627</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
@@ -8499,12 +8495,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>345641</t>
+          <t>342619</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>87806</t>
+          <t>20436</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8514,17 +8510,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>JESUS DAVID</t>
+          <t>CAMILA YAMILET</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>PARRA</t>
+          <t>ROMAN</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>NORIEGA</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8534,79 +8530,71 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>6677853209</t>
+          <t>6671538009</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>CERRO DEL MEZQUITE</t>
+          <t>HACIENDA DEL VALLE</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>02-07-2004</t>
+          <t>13-07-2007</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>DAVIDSILLO2004@GMAIL.COM</t>
+          <t>YAMILETHROMAN704@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>23-02-2026 04:40:43</t>
+          <t>10-02-2026 13:50:59</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>23-02-2026 04:47:31</t>
+          <t>10-02-2026 15:14:35</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>23-02-2026 04:46:51</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8614,36 +8602,36 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26050522565460004828</t>
+          <t>26050522233960003704</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>345817</t>
+          <t>345641</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>87982</t>
+          <t>87806</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8653,17 +8641,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>KARLA ANDREA</t>
+          <t>JESUS DAVID</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ENRIQUEZ</t>
+          <t>PARRA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8673,32 +8661,32 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6676327717</t>
+          <t>6677853209</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>PRESIDENTE IGNACIO COMONFORT</t>
+          <t>CERRO DEL MEZQUITE</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>06-11-1994</t>
+          <t>02-07-2004</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>KAEL2042@GMAIL.COM</t>
+          <t>DAVIDSILLO2004@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>23-02-2026 15:02:26</t>
+          <t>23-02-2026 04:40:43</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -8723,7 +8711,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>23-02-2026 15:05:37</t>
+          <t>23-02-2026 04:47:31</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -8733,7 +8721,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>23-02-2026 15:05:12</t>
+          <t>23-02-2026 04:46:51</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -8753,7 +8741,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26050522583660004884</t>
+          <t>26050522565460004828</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr"/>
@@ -8765,24 +8753,24 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>343144</t>
+          <t>345817</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>20961</t>
+          <t>87982</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8792,17 +8780,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VICTORIA</t>
+          <t>KARLA ANDREA</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>OJEDA</t>
+          <t>ENRIQUEZ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8812,12 +8800,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6673796592</t>
+          <t>6676327717</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>PAULINO MACHORRO1896</t>
+          <t>PRESIDENTE IGNACIO COMONFORT</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8827,23 +8815,27 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>17-11-1994</t>
+          <t>06-11-1994</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>VICTORIAOJEDAAAA@GMAIL.COM</t>
+          <t>KAEL2042@GMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>11-02-2026 21:38:13</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
+          <t>23-02-2026 15:02:26</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -8858,21 +8850,29 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>13-02-2026 19:49:17</t>
+          <t>23-02-2026 15:05:37</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>23-02-2026 15:05:12</t>
+        </is>
+      </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W63" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8880,19 +8880,11 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26050522330490004130</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>Carmen Michel Navarrete  Nevarez</t>
-        </is>
-      </c>
+          <t>26050522583660004884</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr">
         <is>
           <t>499</t>
@@ -8900,7 +8892,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -8912,12 +8904,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>344004</t>
+          <t>343144</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>21821</t>
+          <t>20961</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8927,17 +8919,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>IVAN JARETH</t>
+          <t>VICTORIA</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">HIRATA </t>
+          <t>OJEDA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -8947,42 +8939,38 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6672295585</t>
+          <t>6673796592</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>CERRO CULIACAN 1391</t>
+          <t>PAULINO MACHORRO1896</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>04-10-1996</t>
+          <t>17-11-1994</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>C98667145@COPPEL.COM</t>
+          <t>VICTORIAOJEDAAAA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>16-02-2026 10:33:07</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>11-02-2026 21:38:13</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8997,29 +8985,21 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>16-02-2026 10:58:09</t>
+          <t>13-02-2026 19:49:17</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>16-02-2026 10:41:22</t>
-        </is>
-      </c>
+          <t>14-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9027,11 +9007,19 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26050522384690004236</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr"/>
-      <c r="Z64" t="inlineStr"/>
+          <t>26050522330490004130</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>Carmen Michel Navarrete  Nevarez</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>499</t>
@@ -9039,24 +9027,24 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>344058</t>
+          <t>346007</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>21875</t>
+          <t>88172</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9066,17 +9054,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADRIAN ALEJANDRO </t>
+          <t>VALENTINA JAYDE</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>GAMBOA</t>
+          <t xml:space="preserve">GUERRA </t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9086,35 +9074,31 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2212182749</t>
+          <t>6674600504</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>01-01-2000</t>
+          <t>11-01-2010</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>AGAMBOA515@GMAIL.COM</t>
+          <t>VALENTINAJGG10@GMAIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>16-02-2026 12:55:37</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>23-02-2026 18:54:22</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -9122,28 +9106,28 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>16-02-2026 17:16:42</t>
+          <t>24-02-2026 18:06:25</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>24-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V65" t="inlineStr"/>
@@ -9154,36 +9138,44 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26050522398420004302</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr"/>
-      <c r="Z65" t="inlineStr"/>
+          <t>26050522630450005079</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Hector Noe Espinoza Ramirez</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>344114</t>
+          <t>342639</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>21931</t>
+          <t>20456</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9193,17 +9185,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ALEJANDRO GUADALUPE</t>
+          <t>DAMARIS</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEON </t>
+          <t xml:space="preserve">ZAZUETA </t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>URIARTE</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -9213,67 +9205,75 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6673888815</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>6674646163</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>LOMAS</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>25-12-2008</t>
+          <t>01-08-1987</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>ALEXLEONLOPEZ08@GMAIL.COM</t>
+          <t>BLANCA32NICE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>16-02-2026 15:08:28</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>10-02-2026 14:32:18</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>17-02-2026 14:06:24</t>
+          <t>10-02-2026 14:50:58</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>10-02-2026 14:49:25</t>
+        </is>
+      </c>
       <c r="U66" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9281,14 +9281,14 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>26050522428770004410</t>
+          <t>26050522233370003701</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
@@ -9305,12 +9305,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>344151</t>
+          <t>344004</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>21968</t>
+          <t>21821</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9320,17 +9320,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>IVAN JARETH</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t xml:space="preserve">HIRATA </t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ACEVO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -9340,10 +9340,14 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>6673549962</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>6672295585</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>CERRO CULIACAN 1391</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -9351,52 +9355,64 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>28-01-1989</t>
+          <t>04-10-1996</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>JOSUE.MDZA@GMAIL.COM</t>
+          <t>C98667145@COPPEL.COM</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>16-02-2026 16:17:24</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+          <t>16-02-2026 10:33:07</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>16-02-2026 16:20:42</t>
+          <t>16-02-2026 10:58:09</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>16-02-2026 10:41:22</t>
+        </is>
+      </c>
       <c r="U67" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr"/>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W67" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9404,14 +9420,14 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>26050522395110004278</t>
+          <t>26050522384690004236</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
@@ -9428,12 +9444,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>346785</t>
+          <t>344058</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>88950</t>
+          <t>21875</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9443,17 +9459,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SILVIA G</t>
+          <t xml:space="preserve">ADRIAN ALEJANDRO </t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">GASTELUM </t>
+          <t>GAMBOA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -9463,28 +9479,28 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>6673817224</t>
+          <t>2212182749</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>31-01-1990</t>
+          <t>01-01-2000</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>SILVIAGASTELUM18@GMAIL.COM</t>
+          <t>AGAMBOA515@GMAIL.COM</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>26-02-2026 17:46:56</t>
+          <t>16-02-2026 12:55:37</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -9509,18 +9525,18 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>26-02-2026 17:48:45</t>
+          <t>16-02-2026 17:16:42</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>26-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V68" t="inlineStr"/>
@@ -9531,7 +9547,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>26050522690790005306</t>
+          <t>26050522398420004302</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr"/>
@@ -9555,12 +9571,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>346007</t>
+          <t>344114</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>88172</t>
+          <t>21931</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9570,17 +9586,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VALENTINA JAYDE</t>
+          <t>ALEJANDRO GUADALUPE</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUERRA </t>
+          <t xml:space="preserve">LEON </t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -9590,31 +9606,35 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>6674600504</t>
+          <t>6673888815</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>11-01-2010</t>
+          <t>25-12-2008</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>VALENTINAJGG10@GMAIL.COM</t>
+          <t>ALEXLEONLOPEZ08@GMAIL.COM</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>23-02-2026 18:54:22</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+          <t>16-02-2026 15:08:28</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O69" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -9622,22 +9642,22 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>24-02-2026 18:06:25</t>
+          <t>17-02-2026 14:06:24</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>24-05-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T69" t="inlineStr"/>
@@ -9654,44 +9674,36 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>26050522630450005079</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
-        </is>
-      </c>
+          <t>26050522428770004410</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>Hector Noe Espinoza Ramirez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>342639</t>
+          <t>344151</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>20456</t>
+          <t>21968</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9701,17 +9713,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>DAMARIS</t>
+          <t>JOSE</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAZUETA </t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>URIARTE</t>
+          <t>ACEVO</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -9721,75 +9733,63 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>6674646163</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>LOMAS</t>
-        </is>
-      </c>
+          <t>6673549962</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>01-08-1987</t>
+          <t>28-01-1989</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>BLANCA32NICE@GMAIL.COM</t>
+          <t>JOSUE.MDZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>10-02-2026 14:32:18</t>
+          <t>16-02-2026 16:17:24</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>10-02-2026 14:50:58</t>
+          <t>16-02-2026 16:20:42</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>10-02-2026 14:49:25</t>
-        </is>
-      </c>
+          <t>16-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9797,14 +9797,14 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>26050522233370003701</t>
+          <t>26050522395110004278</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
@@ -9821,12 +9821,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>344408</t>
+          <t>343951</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>22225</t>
+          <t>21768</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9836,17 +9836,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>CLAUDIA VIANEY</t>
+          <t>ADILENE BERENYCE</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CHAVARIN</t>
+          <t xml:space="preserve">MEDINA </t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -9856,10 +9856,14 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>6677853393</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>6674304996</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>COLINAS DE AMBAR 4640</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -9867,52 +9871,64 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>19-07-1994</t>
+          <t>22-10-1990</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>EMIR.DAN103@GMAIL.COM</t>
+          <t>BERECARDENAS102@GMAIL.COM</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>17-02-2026 08:06:40</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
+          <t>16-02-2026 07:28:02</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>19-02-2026 07:41:19</t>
+          <t>16-02-2026 07:35:05</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>19-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T71" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>16-02-2026 07:34:19</t>
+        </is>
+      </c>
       <c r="U71" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9920,44 +9936,36 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>26050522488330004601</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>ABIGAIL AHUMADA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26050522379390004219</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>343138</t>
+          <t>344219</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>20955</t>
+          <t>22036</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -9967,17 +9975,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NORMA ALICIA</t>
+          <t>JETSSY YERANI</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -9987,12 +9995,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>6674953867</t>
+          <t>6671955010</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>SAN ISIDRO</t>
+          <t>PRADOS</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -10002,48 +10010,52 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>27-09-1971</t>
+          <t>01-11-2002</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>NORMAALICIA@GMAIL.COM</t>
+          <t>CHJETSSY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>11-02-2026 20:48:11</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
+          <t>16-02-2026 17:35:23</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>11-02-2026 20:51:25</t>
+          <t>16-02-2026 17:40:31</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>11-02-2026 20:50:52</t>
+          <t>16-02-2026 17:39:31</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -10063,14 +10075,14 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>26050522278960003916</t>
+          <t>26050522400210004318</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
@@ -10087,12 +10099,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>343951</t>
+          <t>343138</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>21768</t>
+          <t>20955</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -10102,17 +10114,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ADILENE BERENYCE</t>
+          <t>NORMA ALICIA</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDINA </t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -10122,12 +10134,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>6674304996</t>
+          <t>6674953867</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>COLINAS DE AMBAR 4640</t>
+          <t>SAN ISIDRO</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -10137,24 +10149,20 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>22-10-1990</t>
+          <t>27-09-1971</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>BERECARDENAS102@GMAIL.COM</t>
+          <t>NORMAALICIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>16-02-2026 07:28:02</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>11-02-2026 20:48:11</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -10162,7 +10170,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -10172,17 +10180,17 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>16-02-2026 07:35:05</t>
+          <t>11-02-2026 20:51:25</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>16-02-2026 07:34:19</t>
+          <t>11-02-2026 20:50:52</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -10202,7 +10210,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>26050522379390004219</t>
+          <t>26050522278960003916</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr"/>
@@ -10226,12 +10234,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>344219</t>
+          <t>346714</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>22036</t>
+          <t>88879</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10241,17 +10249,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>JETSSY YERANI</t>
+          <t>JESUS ALEJANDRO</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>MANJARREZ</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -10261,7 +10269,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>6671955010</t>
+          <t>6674159683</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -10271,57 +10279,57 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>01-11-2002</t>
+          <t>24-11-2004</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>CHJETSSY@GMAIL.COM</t>
+          <t>AE753490@GMAIL.COM</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>16-02-2026 17:35:23</t>
+          <t>26-02-2026 14:31:17</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>16-02-2026 17:40:31</t>
+          <t>26-02-2026 16:08:54</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>26-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>16-02-2026 17:39:31</t>
+          <t>26-02-2026 16:07:26</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -10341,14 +10349,14 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>26050522400210004318</t>
+          <t>26050522686340005286</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
@@ -10365,12 +10373,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>344563</t>
+          <t>344330</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>22380</t>
+          <t>22147</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10380,17 +10388,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>JESUS ADRIAN</t>
+          <t>CRISTOPHER LUCIANO</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>ZAVALA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>POMPA</t>
+          <t>ANGULO</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -10400,14 +10408,10 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>6672490628</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>VOLCAN S</t>
-        </is>
-      </c>
+          <t>6671833791</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -10415,64 +10419,56 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>15-07-1987</t>
+          <t>04-09-2013</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>JESUSADRIANSP@GMAIL.COM</t>
+          <t>CLOSETYCOCINASSR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>17-02-2026 16:22:49</t>
+          <t>16-02-2026 19:04:29</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>17-02-2026 16:47:28</t>
+          <t>16-02-2026 19:14:09</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>17-02-2026 16:27:05</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10480,36 +10476,36 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>26050522435210004433</t>
+          <t>26050522407600004347</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>Hector Noe Espinoza Ramirez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>346714</t>
+          <t>344408</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>88879</t>
+          <t>22225</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10519,17 +10515,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>JESUS ALEJANDRO</t>
+          <t>CLAUDIA VIANEY</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>CHAVARIN</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MANJARREZ</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -10539,79 +10535,63 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>6674159683</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>PRADOS</t>
-        </is>
-      </c>
+          <t>6677853393</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>24-11-2004</t>
+          <t>19-07-1994</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>AE753490@GMAIL.COM</t>
+          <t>EMIR.DAN103@GMAIL.COM</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>26-02-2026 14:31:17</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>17-02-2026 08:06:40</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>26-02-2026 16:08:54</t>
+          <t>19-02-2026 07:41:19</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>26-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>26-02-2026 16:07:26</t>
-        </is>
-      </c>
+          <t>19-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V76" t="inlineStr"/>
       <c r="W76" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10619,36 +10599,44 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>26050522686340005286</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr"/>
-      <c r="Z76" t="inlineStr"/>
+          <t>26050522488330004601</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>343911</t>
+          <t>344007</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>21728</t>
+          <t>21824</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -10658,17 +10646,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>CARLOS GABRIEL</t>
+          <t>JOSE LUIS</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -10678,12 +10666,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>6674119225</t>
+          <t>6671901876</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>RAFAEL MARTINEZ 2620</t>
+          <t>CERRO DEL TENAYO 1285</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10693,17 +10681,17 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>01-12-2000</t>
+          <t>08-10-1988</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>CMEZAGR10@GMAIL.COM</t>
+          <t>JOSELUISDIAZRIVERA68@GMAIL.COM</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>16-02-2026 05:00:53</t>
+          <t>16-02-2026 10:51:16</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -10728,7 +10716,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>16-02-2026 05:08:16</t>
+          <t>16-02-2026 10:56:29</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -10738,7 +10726,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>16-02-2026 05:04:59</t>
+          <t>16-02-2026 10:55:40</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -10758,7 +10746,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>26050522369740004204</t>
+          <t>26050522384660004235</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr"/>
@@ -10782,12 +10770,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>344007</t>
+          <t>344100</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>21824</t>
+          <t>21917</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -10797,17 +10785,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>JOSE LUIS</t>
+          <t>AIDEE</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>CORRALES</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -10817,57 +10805,53 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>6671901876</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>CERRO DEL TENAYO 1285</t>
-        </is>
-      </c>
+          <t>6673888721</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>08-10-1988</t>
+          <t>02-08-2004</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>JOSELUISDIAZRIVERA68@GMAIL.COM</t>
+          <t>AUDEESITI84@GMAIL.COM</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>16-02-2026 10:51:16</t>
+          <t>16-02-2026 14:42:18</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>16-02-2026 10:56:29</t>
+          <t>16-02-2026 14:44:30</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -10875,21 +10859,13 @@
           <t>16-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>16-02-2026 10:55:40</t>
-        </is>
-      </c>
+      <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10897,14 +10873,14 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>26050522384660004235</t>
+          <t>26050522390910004257</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="inlineStr"/>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
@@ -10921,12 +10897,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>344100</t>
+          <t>343911</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>21917</t>
+          <t>21728</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -10936,17 +10912,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>AIDEE</t>
+          <t>CARLOS GABRIEL</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CORRALES</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -10956,53 +10932,57 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>6673888721</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>6674119225</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>RAFAEL MARTINEZ 2620</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>02-08-2004</t>
+          <t>01-12-2000</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>AUDEESITI84@GMAIL.COM</t>
+          <t>CMEZAGR10@GMAIL.COM</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>16-02-2026 14:42:18</t>
+          <t>16-02-2026 05:00:53</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>16-02-2026 14:44:30</t>
+          <t>16-02-2026 05:08:16</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -11010,13 +10990,21 @@
           <t>16-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr"/>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>16-02-2026 05:04:59</t>
+        </is>
+      </c>
       <c r="U79" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V79" t="inlineStr"/>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W79" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11024,14 +11012,14 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>26050522390910004257</t>
+          <t>26050522369740004204</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="inlineStr"/>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
@@ -11048,12 +11036,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>344330</t>
+          <t>344602</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>22147</t>
+          <t>22419</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -11063,17 +11051,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>CRISTOPHER LUCIANO</t>
+          <t>ROXANA GABRIELA</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ZAVALA</t>
+          <t>SAMANIEGO</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ANGULO</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -11083,10 +11071,14 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>6671833791</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>6471226799</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>C MIGUEL HIDALGO</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -11094,56 +11086,64 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>04-09-2013</t>
+          <t>23-11-1999</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>CLOSETYCOCINASSR@GMAIL.COM</t>
+          <t>ROXANASAMANIEGO487@GMAIL.COM</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>16-02-2026 19:04:29</t>
+          <t>17-02-2026 17:21:04</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>16-02-2026 19:14:09</t>
+          <t>17-02-2026 17:25:35</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T80" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>17-02-2026 17:24:51</t>
+        </is>
+      </c>
       <c r="U80" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V80" t="inlineStr"/>
       <c r="W80" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11151,14 +11151,14 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>26050522407600004347</t>
+          <t>26050522437350004443</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
@@ -11175,12 +11175,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>345211</t>
+          <t>344544</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>87376</t>
+          <t>22361</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -11190,17 +11190,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>JOSE ISAIAS</t>
+          <t>JESUS ABRAHAM</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>MONTAÑO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -11210,79 +11210,63 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>6672019370</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>BELIZARIO DOMINGUEZ 5841</t>
-        </is>
-      </c>
+          <t>6675819023</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>14-11-1995</t>
+          <t>15-07-2006</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>ISAIASRODRIGUEZRZ@GMAIL.COM</t>
+          <t>M0NTAN0JSUS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>20-02-2026 04:41:44</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>17-02-2026 16:04:14</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>27-02-2026 04:59:12</t>
+          <t>17-02-2026 16:06:36</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>27-02-2026 04:58:02</t>
-        </is>
-      </c>
+          <t>17-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11290,22 +11274,14 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>26050522698610005338</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>Carmen Michel Navarrete  Nevarez</t>
-        </is>
-      </c>
+          <t>26050522432880004420</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
@@ -11322,12 +11298,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>344544</t>
+          <t>344563</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>22361</t>
+          <t>22380</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -11337,17 +11313,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>JESUS ABRAHAM</t>
+          <t>JESUS ADRIAN</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MONTAÑO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>POMPA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -11357,63 +11333,79 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>6675819023</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>6672490628</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>VOLCAN S</t>
+        </is>
+      </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>15-07-2006</t>
+          <t>15-07-1987</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>M0NTAN0JSUS@GMAIL.COM</t>
+          <t>JESUSADRIANSP@GMAIL.COM</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>17-02-2026 16:04:14</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+          <t>17-02-2026 16:22:49</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>17-02-2026 16:06:36</t>
+          <t>17-02-2026 16:47:28</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>17-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T82" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>17-02-2026 16:27:05</t>
+        </is>
+      </c>
       <c r="U82" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V82" t="inlineStr"/>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W82" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11421,36 +11413,36 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>26050522432880004420</t>
+          <t>26050522435210004433</t>
         </is>
       </c>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="inlineStr"/>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Hector Noe Espinoza Ramirez</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>344602</t>
+          <t>345211</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>22419</t>
+          <t>87376</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -11460,17 +11452,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ROXANA GABRIELA</t>
+          <t>JOSE ISAIAS</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SAMANIEGO</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -11480,12 +11472,12 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>6471226799</t>
+          <t>6672019370</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>C MIGUEL HIDALGO</t>
+          <t>BELIZARIO DOMINGUEZ 5841</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -11495,17 +11487,17 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>23-11-1999</t>
+          <t>14-11-1995</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>ROXANASAMANIEGO487@GMAIL.COM</t>
+          <t>ISAIASRODRIGUEZRZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>17-02-2026 17:21:04</t>
+          <t>20-02-2026 04:41:44</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -11530,17 +11522,17 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>17-02-2026 17:25:35</t>
+          <t>27-02-2026 04:59:12</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>27-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>17-02-2026 17:24:51</t>
+          <t>27-02-2026 04:58:02</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -11550,7 +11542,7 @@
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W83" t="inlineStr">
@@ -11560,11 +11552,19 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>26050522437350004443</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr"/>
-      <c r="Z83" t="inlineStr"/>
+          <t>26050522698610005338</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>Carmen Michel Navarrete  Nevarez</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>499</t>
@@ -12108,12 +12108,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>346302</t>
+          <t>345683</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>88467</t>
+          <t>87848</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -12123,17 +12123,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>HECTOR</t>
+          <t>MARTIN GUADALUPE</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MORGAN</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>VILLEGAS</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -12143,32 +12143,32 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>6671977767</t>
+          <t>6671537144</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>PROGRESO</t>
+          <t>DE LA CANTERA 736</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>01-08-1999</t>
+          <t>29-10-1985</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>HECTORMV@GMAIL.COM</t>
+          <t>MARTYNCYO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>24-02-2026 18:55:53</t>
+          <t>23-02-2026 09:46:26</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -12193,17 +12193,17 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>24-02-2026 19:20:16</t>
+          <t>23-02-2026 09:50:08</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>24-02-2026 19:19:39</t>
+          <t>23-02-2026 09:49:57</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W88" t="inlineStr">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>26050522634190005096</t>
+          <t>26050522575390004858</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr"/>
@@ -12235,24 +12235,24 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>345683</t>
+          <t>345824</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>87848</t>
+          <t>87989</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -12262,17 +12262,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>MARTIN GUADALUPE</t>
+          <t>CARLOS HUMBERTO</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>ONTIVEROS</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>ENRIQUEZ</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -12282,12 +12282,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>6671537144</t>
+          <t>6671012383</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>DE LA CANTERA 736</t>
+          <t>CALLE PRESIDENTE</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -12297,17 +12297,17 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>29-10-1985</t>
+          <t>02-02-2011</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>MARTYNCYO@GMAIL.COM</t>
+          <t>CARLOSHERRERA92242@GMAIL.COM</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>23-02-2026 09:46:26</t>
+          <t>23-02-2026 15:12:22</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -12332,7 +12332,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>23-02-2026 09:50:08</t>
+          <t>23-02-2026 15:14:50</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -12342,7 +12342,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>23-02-2026 09:49:57</t>
+          <t>23-02-2026 15:14:29</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W89" t="inlineStr">
@@ -12362,7 +12362,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>26050522575390004858</t>
+          <t>26050522584150004888</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr"/>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -12386,12 +12386,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>345824</t>
+          <t>346791</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>87989</t>
+          <t>88956</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -12401,17 +12401,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>CARLOS HUMBERTO</t>
+          <t xml:space="preserve">JESUS MIGUEL </t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ONTIVEROS</t>
+          <t xml:space="preserve">RAMOS </t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ENRIQUEZ</t>
+          <t>SOTELO</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -12421,14 +12421,10 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>6671012383</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>CALLE PRESIDENTE</t>
-        </is>
-      </c>
+          <t>6727252039</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -12436,64 +12432,56 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>02-02-2011</t>
+          <t>28-09-1990</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>CARLOSHERRERA92242@GMAIL.COM</t>
+          <t>JESUSMIGUE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>23-02-2026 15:12:22</t>
+          <t>26-02-2026 17:54:05</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>23-02-2026 15:14:50</t>
+          <t>26-02-2026 17:55:24</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>23-02-2026 15:14:29</t>
-        </is>
-      </c>
+          <t>26-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr"/>
       <c r="U90" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -12501,24 +12489,24 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>26050522584150004888</t>
+          <t>26050522691240005310</t>
         </is>
       </c>
       <c r="Y90" t="inlineStr"/>
       <c r="Z90" t="inlineStr"/>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -12652,12 +12640,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>346791</t>
+          <t>346302</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>88956</t>
+          <t>88467</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -12667,17 +12655,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESUS MIGUEL </t>
+          <t>HECTOR</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMOS </t>
+          <t>MORGAN</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>SOTELO</t>
+          <t>VILLEGAS</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -12687,67 +12675,79 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>6727252039</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>6671977767</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>PROGRESO</t>
+        </is>
+      </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>28-09-1990</t>
+          <t>01-08-1999</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>JESUSMIGUE@GMAIL.COM</t>
+          <t>HECTORMV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>26-02-2026 17:54:05</t>
+          <t>24-02-2026 18:55:53</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>26-02-2026 17:55:24</t>
+          <t>24-02-2026 19:20:16</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>26-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T92" t="inlineStr"/>
+          <t>24-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>24-02-2026 19:19:39</t>
+        </is>
+      </c>
       <c r="U92" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V92" t="inlineStr"/>
       <c r="W92" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -12755,14 +12755,14 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>26050522691240005310</t>
+          <t>26050522634190005096</t>
         </is>
       </c>
       <c r="Y92" t="inlineStr"/>
       <c r="Z92" t="inlineStr"/>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
@@ -12779,12 +12779,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>345682</t>
+          <t>346549</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>87847</t>
+          <t>88714</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -12794,17 +12794,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ALMA ROSA</t>
+          <t>VERONICA</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>ESPARZA</t>
+          <t>VACA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>BUENO</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -12814,14 +12814,10 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>6675066381</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>DE LA CANTERA 736</t>
-        </is>
-      </c>
+          <t>6672505019</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -12829,64 +12825,52 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>20-02-1985</t>
+          <t>27-06-1983</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>ALMA.ESPARZA.BUENO@GMAIL.COM</t>
+          <t>VERONICAHERNANDEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>23-02-2026 09:34:05</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>25-02-2026 17:38:31</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>23-02-2026 09:45:00</t>
+          <t>25-02-2026 17:39:49</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>23-02-2026 09:39:21</t>
-        </is>
-      </c>
+          <t>25-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V93" t="inlineStr"/>
       <c r="W93" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -12894,36 +12878,36 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>26050522575290004857</t>
+          <t>26050522660800005198</t>
         </is>
       </c>
       <c r="Y93" t="inlineStr"/>
       <c r="Z93" t="inlineStr"/>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>345749</t>
+          <t>345819</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>87914</t>
+          <t>87984</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -12933,17 +12917,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">SARA </t>
+          <t>HUMBERTO GUADALUPE</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ROCHA</t>
+          <t>ONTIVEROS</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>PARRA</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -12953,32 +12937,32 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>6675758326</t>
+          <t>6671837620</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>CALLE PRIMERA 697</t>
+          <t xml:space="preserve">CALLE PRESIDENTE </t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>05-01-1984</t>
+          <t>25-03-1990</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>SARA.13@GMAIL.COM</t>
+          <t>HUM60H2503@GMAIL.COM</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>23-02-2026 12:47:26</t>
+          <t>23-02-2026 15:08:17</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -13003,7 +12987,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>23-02-2026 12:53:53</t>
+          <t>23-02-2026 15:10:55</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -13013,7 +12997,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>23-02-2026 12:52:28</t>
+          <t>23-02-2026 15:10:21</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -13033,7 +13017,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>26050522579700004867</t>
+          <t>26050522583980004887</t>
         </is>
       </c>
       <c r="Y94" t="inlineStr"/>
@@ -13045,24 +13029,24 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>345819</t>
+          <t>345682</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>87984</t>
+          <t>87847</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -13072,17 +13056,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>HUMBERTO GUADALUPE</t>
+          <t>ALMA ROSA</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ONTIVEROS</t>
+          <t>ESPARZA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>BUENO</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -13092,32 +13076,32 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>6671837620</t>
+          <t>6675066381</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">CALLE PRESIDENTE </t>
+          <t>DE LA CANTERA 736</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>25-03-1990</t>
+          <t>20-02-1985</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>HUM60H2503@GMAIL.COM</t>
+          <t>ALMA.ESPARZA.BUENO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>23-02-2026 15:08:17</t>
+          <t>23-02-2026 09:34:05</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -13142,7 +13126,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>23-02-2026 15:10:55</t>
+          <t>23-02-2026 09:45:00</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -13152,7 +13136,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>23-02-2026 15:10:21</t>
+          <t>23-02-2026 09:39:21</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -13162,7 +13146,7 @@
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W95" t="inlineStr">
@@ -13172,7 +13156,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>26050522583980004887</t>
+          <t>26050522575290004857</t>
         </is>
       </c>
       <c r="Y95" t="inlineStr"/>
@@ -13184,7 +13168,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
@@ -13196,12 +13180,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>346549</t>
+          <t>345749</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>88714</t>
+          <t>87914</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -13211,17 +13195,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VERONICA</t>
+          <t xml:space="preserve">SARA </t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>VACA</t>
+          <t>ROCHA</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>PARRA</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -13231,10 +13215,14 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>6672505019</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>6675758326</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>CALLE PRIMERA 697</t>
+        </is>
+      </c>
       <c r="J96" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -13242,52 +13230,64 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>27-06-1983</t>
+          <t>05-01-1984</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>VERONICAHERNANDEZ@GMAIL.COM</t>
+          <t>SARA.13@GMAIL.COM</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>25-02-2026 17:38:31</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
+          <t>23-02-2026 12:47:26</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>25-02-2026 17:39:49</t>
+          <t>23-02-2026 12:53:53</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>25-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T96" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>23-02-2026 12:52:28</t>
+        </is>
+      </c>
       <c r="U96" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V96" t="inlineStr"/>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W96" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -13295,14 +13295,14 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>26050522660800005198</t>
+          <t>26050522579700004867</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr"/>
       <c r="Z96" t="inlineStr"/>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN ISIDRO CUL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN ISIDRO CUL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,12 +713,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>346278</t>
+          <t>343497</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>88443</t>
+          <t>21314</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MARIA EMILIA</t>
+          <t>JOSE ANGEL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>OCHOA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CAZAREZ</t>
+          <t>BEJARANO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -748,31 +748,31 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6671032248</t>
+          <t>6673417636</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>13-08-1969</t>
+          <t>30-08-2011</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>EMILIAOCHOAC@HOTMAIL.COM</t>
+          <t>CHANGELITOBAEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>24-02-2026 17:56:11</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>13-02-2026 13:37:52</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -780,22 +780,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 17:31:17</t>
+          <t>02-03-2026 14:19:08</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -812,7 +812,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26050522806750005604</t>
+          <t>26050522794430005558</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -822,12 +822,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>ABIGAIL AHUMADA MARTINEZ</t>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -844,12 +844,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>343497</t>
+          <t>334515</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21314</t>
+          <t>18082</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>JOSE ANGEL</t>
+          <t>LORENA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>ALARCON</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -879,39 +879,47 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6673417636</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>6674064116</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADOLFO LOPEZ </t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>30-08-2011</t>
+          <t>26-09-1974</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CHANGELITOBAEZ@GMAIL.COM</t>
+          <t>ALARCONBEJARANOS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>13-02-2026 13:37:52</t>
+          <t>13-01-2026 17:50:35</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -921,7 +929,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 14:19:08</t>
+          <t>02-03-2026 19:51:47</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -929,13 +937,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:51:10</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -943,7 +959,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26050522794430005558</t>
+          <t>26050522818160005664</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -953,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -975,12 +991,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>334515</t>
+          <t>101573</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18082</t>
+          <t>99325</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,17 +1006,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LORENA</t>
+          <t>JORDAN YOSIMAR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ALARCON</t>
+          <t>PANTOJA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BEJARANO</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1010,47 +1026,47 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6674064116</t>
+          <t>6673887174</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADOLFO LOPEZ </t>
+          <t>MINA PANUCO 444</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>26-09-1974</t>
+          <t>28-04-2010</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ALARCONBEJARANOS@GMAIL.COM</t>
+          <t>JORDAN230945@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>13-01-2026 17:50:35</t>
+          <t>20-06-2022 14:49:00</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1060,7 +1076,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 19:51:47</t>
+          <t>02-03-2026 13:51:54</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1068,21 +1084,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>02-03-2026 19:51:10</t>
-        </is>
-      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1090,19 +1098,11 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26050522818160005664</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>ABIGAIL AHUMADA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26050522793700005554</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
           <t>549</t>
@@ -1122,12 +1122,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347887</t>
+          <t>344955</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>90052</t>
+          <t>22772</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1137,17 +1137,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CHRISTIAN</t>
+          <t>TAHOTY YACSIREE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>VIZCARRA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BURGUEÑO</t>
+          <t>MILLAN</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1157,32 +1157,32 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6673329969</t>
+          <t>6674271403</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CHULAVISTA</t>
+          <t>CAPSITRANO</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>07-12-1995</t>
+          <t>28-07-1998</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>BURGUEÑO16@GMAIL.COM</t>
+          <t>VIZCARRAMILLANTAHOTY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 19:54:23</t>
+          <t>18-02-2026 19:56:22</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1207,17 +1207,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 20:31:17</t>
+          <t>03-03-2026 16:43:53</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>02-03-2026 20:30:51</t>
+          <t>02-03-2026 17:25:55</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26050522819670005672</t>
+          <t>26050522847830005765</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1269,12 +1269,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>101573</t>
+          <t>346278</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>99325</t>
+          <t>88443</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1284,17 +1284,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>JORDAN YOSIMAR</t>
+          <t>MARIA EMILIA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PANTOJA</t>
+          <t>OCHOA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>CAZAREZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1304,39 +1304,31 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6673887174</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>MINA PANUCO 444</t>
-        </is>
-      </c>
+          <t>6671032248</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>28-04-2010</t>
+          <t>13-08-1969</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>JORDAN230945@GMAIL.COM</t>
+          <t>EMILIAOCHOAC@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>20-06-2022 14:49:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>24-02-2026 17:56:11</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -1344,28 +1336,28 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 13:51:54</t>
+          <t>02-03-2026 17:31:17</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>02-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1376,36 +1368,44 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26050522793700005554</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+          <t>26050522806750005604</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347633</t>
+          <t>347887</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89798</t>
+          <t>90052</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ROGELIO</t>
+          <t>CHRISTIAN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CAMBERO</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>BURGUEÑO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1435,10 +1435,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3112033428</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>6673329969</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CHULAVISTA</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1446,32 +1450,32 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>22-06-1979</t>
+          <t>07-12-1995</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ROQEIROCAMBERO@YAHOO.COM</t>
+          <t>BURGUEÑO16@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 15:30:56</t>
+          <t>02-03-2026 19:54:23</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1481,21 +1485,29 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 15:38:54</t>
+          <t>02-03-2026 20:31:17</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:30:51</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1503,11 +1515,19 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26050522798030005567</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
+          <t>26050522819670005672</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>549</t>
@@ -1527,12 +1547,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347691</t>
+          <t>347633</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89856</t>
+          <t>89798</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1542,17 +1562,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FLOR DANIELA</t>
+          <t>ROGELIO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>CAMBERO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1562,57 +1582,53 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6673265018</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>LOMAS DE SAN ISIDRO</t>
-        </is>
-      </c>
+          <t>3112033428</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>14-03-2004</t>
+          <t>22-06-1979</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>SALAZAR16QUINTERO@GMAIL.COM</t>
+          <t>ROQEIROCAMBERO@YAHOO.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 16:40:39</t>
+          <t>02-03-2026 15:30:56</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 16:50:11</t>
+          <t>02-03-2026 15:38:54</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1620,21 +1636,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>02-03-2026 16:46:57</t>
-        </is>
-      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1642,36 +1650,36 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26050522803300005585</t>
+          <t>26050522798030005567</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347418</t>
+          <t>347691</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89583</t>
+          <t>89856</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1681,17 +1689,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MARIA ALEJANDRA</t>
+          <t>FLOR DANIELA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SARABIA</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1701,12 +1709,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6675515310</t>
+          <t>6673265018</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MONTE PERDIDO ESTES 410</t>
+          <t>LOMAS DE SAN ISIDRO</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1716,17 +1724,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>15-10-2007</t>
+          <t>14-03-2004</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>SARABIAALE19@GMAIL.COM</t>
+          <t>SALAZAR16QUINTERO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 07:21:17</t>
+          <t>02-03-2026 16:40:39</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1736,22 +1744,22 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 07:28:43</t>
+          <t>02-03-2026 16:50:11</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1761,7 +1769,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>02-03-2026 07:27:34</t>
+          <t>02-03-2026 16:46:57</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1781,36 +1789,36 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26050522782410005517</t>
+          <t>26050522803300005585</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347909</t>
+          <t>348064</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90074</t>
+          <t>90229</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1820,17 +1828,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HECTOR ABEL</t>
+          <t>ERIK BLADIMIR</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALEZUELA </t>
+          <t>ZARABIA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MERAZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1840,12 +1848,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6674085202</t>
+          <t>6674352372</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>LOMAS DE SAN ISIDRO</t>
+          <t>22 DE DIC</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1855,17 +1863,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>04-09-2011</t>
+          <t>23-02-1999</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>HECOR.VALENZUELA.HERNANDEZ.2011@GMAIL.COM</t>
+          <t>ERIKBLADIMIR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 20:50:24</t>
+          <t>03-03-2026 14:36:16</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1890,17 +1898,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-03-2026 20:55:34</t>
+          <t>03-03-2026 14:40:34</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>02-03-2026 20:54:49</t>
+          <t>03-03-2026 14:39:53</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1910,7 +1918,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1920,7 +1928,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26050522820290005675</t>
+          <t>26050522842200005742</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1932,10 +1940,840 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>Carlos Aurelio Monzon Ayala</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>348151</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>90316</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>JULIO CESAR</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ELIZALDE</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6673418071</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>PERISUR</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>25-02-1990</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>JULIOCESAR1@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:10:14</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:17:25</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:16:26</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>26050522849920005776</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>347418</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>89583</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MARIA ALEJANDRA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SARABIA</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6675515310</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MONTE PERDIDO ESTES 410</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>15-10-2007</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>SARABIAALE19@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>02-03-2026 07:21:17</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>02-03-2026 07:28:43</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>02-03-2026 07:27:34</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>26050522782410005517</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Carlos Aurelio Monzon Ayala</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>347881</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>90046</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>JESUS ALFREDO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>VILLEGAS</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SOTO</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6675443713</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>03-12-2011</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>JUNIORCLN03@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:44:31</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:22:41</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>26050522860730005831</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>348183</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>90348</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>KATIA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SALGUEIRO</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>MILLAN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6672541846</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>LAS QUINTAS</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>03-08-1991</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>SALGUEROMILLAN@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:37:58</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:57:41</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:55:26</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>26050522852830005793</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>348165</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>90330</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BRISEIDA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>MORALES</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6672667222</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>PERISUR</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>07-07-1996</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>MARLUI.M187@QICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:20:12</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:25:36</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:24:50</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>26050522850640005779</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Hector Noe Espinoza Ramirez</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>347909</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>90074</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>HECTOR ABEL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VALEZUELA </t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6674085202</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>LOMAS DE SAN ISIDRO</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>04-09-2011</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>HECOR.VALENZUELA.HERNANDEZ.2011@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:50:24</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:55:34</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:54:49</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>26050522820290005675</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN ISIDRO CUL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN ISIDRO CUL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>347380</t>
+          <t>343497</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>89545</t>
+          <t>21314</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>OMAR</t>
+          <t>JOSE ANGEL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BARRAZA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AYON</t>
+          <t>BEJARANO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,53 +613,49 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6672654267</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>COSTA ADRIATICA</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
+          <t>6673417636</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>27-05-1990</t>
+          <t>30-08-2011</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>OMAR_21@HOTMAIL.COM</t>
+          <t>CHANGELITOBAEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>02-03-2026 05:08:13</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>13-02-2026 13:37:52</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 05:18:15</t>
+          <t>02-03-2026 14:19:08</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -667,21 +663,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>02-03-2026 05:17:00</t>
-        </is>
-      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -689,14 +677,22 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26050522772930005500</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+          <t>26050522794430005558</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -713,12 +709,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>343497</t>
+          <t>101573</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21314</t>
+          <t>99325</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -728,17 +724,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>JOSE ANGEL</t>
+          <t>JORDAN YOSIMAR</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>PANTOJA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BEJARANO</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -748,24 +744,32 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6673417636</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>6673887174</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>MINA PANUCO 444</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>30-08-2011</t>
+          <t>28-04-2010</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CHANGELITOBAEZ@GMAIL.COM</t>
+          <t>JORDAN230945@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>13-02-2026 13:37:52</t>
+          <t>20-06-2022 14:49:00</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -790,7 +794,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 14:19:08</t>
+          <t>02-03-2026 13:51:54</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -801,7 +805,7 @@
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -812,19 +816,11 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26050522794430005558</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
-        </is>
-      </c>
+          <t>26050522793700005554</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
           <t>549</t>
@@ -844,12 +840,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>334515</t>
+          <t>343494</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18082</t>
+          <t>21311</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,17 +855,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LORENA</t>
+          <t>ALEXANDER</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ALARCON</t>
+          <t xml:space="preserve">ZEPEDA </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BEJARANO</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -879,47 +875,43 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6674064116</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ADOLFO LOPEZ </t>
-        </is>
-      </c>
+          <t>6679516592</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>26-09-1974</t>
+          <t>13-09-2011</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ALARCONBEJARANOS@GMAIL.COM</t>
+          <t>ALEXANDER2932@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>13-01-2026 17:50:35</t>
+          <t>13-02-2026 13:34:47</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -929,29 +921,21 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 19:51:47</t>
+          <t>04-03-2026 13:47:30</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>02-03-2026 19:51:10</t>
-        </is>
-      </c>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -959,7 +943,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26050522818160005664</t>
+          <t>26050522881960005889</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -969,7 +953,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>ABIGAIL AHUMADA MARTINEZ</t>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,12 +975,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>101573</t>
+          <t>334515</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>99325</t>
+          <t>18082</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1006,17 +990,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>JORDAN YOSIMAR</t>
+          <t>LORENA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PANTOJA</t>
+          <t>ALARCON</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>BEJARANO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1026,47 +1010,47 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6673887174</t>
+          <t>6674064116</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MINA PANUCO 444</t>
+          <t xml:space="preserve">ADOLFO LOPEZ </t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>28-04-2010</t>
+          <t>26-09-1974</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>JORDAN230945@GMAIL.COM</t>
+          <t>ALARCONBEJARANOS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>20-06-2022 14:49:00</t>
+          <t>13-01-2026 17:50:35</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1076,7 +1060,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 13:51:54</t>
+          <t>02-03-2026 19:51:47</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1084,13 +1068,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:51:10</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1098,11 +1090,19 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26050522793700005554</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+          <t>26050522818160005664</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>549</t>
@@ -1400,12 +1400,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347887</t>
+          <t>347337</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90052</t>
+          <t>89502</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CHRISTIAN</t>
+          <t>CHEYLA  NOHEMY</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t xml:space="preserve">FAUSTO </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BURGUEÑO</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6673329969</t>
+          <t>6673118630</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CHULAVISTA</t>
+          <t>CERRO EL TENAYO</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1450,52 +1450,52 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>07-12-1995</t>
+          <t>09-07-1986</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>BURGUEÑO16@GMAIL.COM</t>
+          <t>ALYEHS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 19:54:23</t>
+          <t>01-03-2026 12:22:14</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 20:31:17</t>
+          <t>04-03-2026 17:29:57</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>02-03-2026 20:30:51</t>
+          <t>04-03-2026 17:29:13</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1515,44 +1515,36 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26050522819670005672</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
-        </is>
-      </c>
+          <t>26050522890810005924</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347633</t>
+          <t>347418</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89798</t>
+          <t>89583</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1562,17 +1554,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ROGELIO</t>
+          <t>MARIA ALEJANDRA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CAMBERO</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>SARABIA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1582,43 +1574,47 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3112033428</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>6675515310</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MONTE PERDIDO ESTES 410</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>22-06-1979</t>
+          <t>15-10-2007</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ROQEIROCAMBERO@YAHOO.COM</t>
+          <t>SARABIAALE19@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 15:30:56</t>
+          <t>02-03-2026 07:21:17</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1628,7 +1624,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 15:38:54</t>
+          <t>02-03-2026 07:28:43</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1636,13 +1632,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>02-03-2026 07:27:34</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1650,7 +1654,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26050522798030005567</t>
+          <t>26050522782410005517</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1662,24 +1666,24 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347691</t>
+          <t>347380</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89856</t>
+          <t>89545</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1689,17 +1693,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FLOR DANIELA</t>
+          <t>OMAR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>BARRAZA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>AYON</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1709,39 +1713,35 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6673265018</t>
+          <t>6672654267</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>LOMAS DE SAN ISIDRO</t>
+          <t>COSTA ADRIATICA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>14-03-2004</t>
+          <t>27-05-1990</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>SALAZAR16QUINTERO@GMAIL.COM</t>
+          <t>OMAR_21@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 16:40:39</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>02-03-2026 05:08:13</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>No Forzoso</t>
@@ -1749,17 +1749,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 16:50:11</t>
+          <t>02-03-2026 05:18:15</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>02-03-2026 16:46:57</t>
+          <t>02-03-2026 05:17:00</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1789,24 +1789,24 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26050522803300005585</t>
+          <t>26050522772930005500</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -2091,12 +2091,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347418</t>
+          <t>347633</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>89583</t>
+          <t>89798</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2106,17 +2106,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MARIA ALEJANDRA</t>
+          <t>ROGELIO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>CAMBERO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SARABIA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2126,47 +2126,43 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6675515310</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>MONTE PERDIDO ESTES 410</t>
-        </is>
-      </c>
+          <t>3112033428</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>15-10-2007</t>
+          <t>22-06-1979</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>SARABIAALE19@GMAIL.COM</t>
+          <t>ROQEIROCAMBERO@YAHOO.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 07:21:17</t>
+          <t>02-03-2026 15:30:56</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2176,7 +2172,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 07:28:43</t>
+          <t>02-03-2026 15:38:54</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2184,21 +2180,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>02-03-2026 07:27:34</t>
-        </is>
-      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2206,7 +2194,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26050522782410005517</t>
+          <t>26050522798030005567</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2218,24 +2206,24 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347881</t>
+          <t>347691</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90046</t>
+          <t>89856</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2245,17 +2233,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>JESUS ALFREDO</t>
+          <t>FLOR DANIELA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VILLEGAS</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2265,10 +2253,14 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6675443713</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>6673265018</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>LOMAS DE SAN ISIDRO</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2276,56 +2268,64 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>03-12-2011</t>
+          <t>14-03-2004</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>JUNIORCLN03@GMAIL.COM</t>
+          <t>SALAZAR16QUINTERO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 19:44:31</t>
+          <t>02-03-2026 16:40:39</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03-03-2026 20:22:41</t>
+          <t>02-03-2026 16:50:11</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:46:57</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2333,44 +2333,36 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26050522860730005831</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
-        </is>
-      </c>
+          <t>26050522803300005585</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>348183</t>
+          <t>347568</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90348</t>
+          <t>89733</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2380,17 +2372,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>KATIA</t>
+          <t xml:space="preserve">JOSE LUIS </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SALGUEIRO</t>
+          <t>GUZMAN</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MILLAN</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2400,79 +2392,67 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6672541846</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>LAS QUINTAS</t>
-        </is>
-      </c>
+          <t>6671377797</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>03-08-1991</t>
+          <t>17-11-2010</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>SALGUEROMILLAN@GMAIL.COM</t>
+          <t>JOSELUISGUZMANMORENO0@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>03-03-2026 17:37:58</t>
+          <t>02-03-2026 13:32:21</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03-03-2026 17:57:41</t>
+          <t>05-03-2026 14:00:36</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>03-03-2026 17:55:26</t>
-        </is>
-      </c>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2480,14 +2460,22 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26050522852830005793</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
+          <t>26050522916410006008</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>CARLOS AURELIO MONZON AYALA</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2504,12 +2492,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>348165</t>
+          <t>343495</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90330</t>
+          <t>21312</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2519,17 +2507,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BRISEIDA</t>
+          <t>JESUS GUADALUPE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>PIZARRO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>MONZON</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2539,79 +2527,63 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6672667222</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>PERISUR</t>
-        </is>
-      </c>
+          <t>6675705316</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>07-07-1996</t>
+          <t>12-06-2011</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>MARLUI.M187@QICLOUD.COM</t>
+          <t>NICOLASFRANSUEP@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>03-03-2026 17:20:12</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>13-02-2026 13:34:52</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>03-03-2026 17:25:36</t>
+          <t>04-03-2026 15:11:20</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>03-03-2026 17:24:50</t>
-        </is>
-      </c>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2619,19 +2591,27 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26050522850640005779</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+          <t>26050522884580005898</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Hector Noe Espinoza Ramirez</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2643,12 +2623,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>347909</t>
+          <t>348165</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90074</t>
+          <t>90330</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2658,17 +2638,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HECTOR ABEL</t>
+          <t>BRISEIDA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALEZUELA </t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2678,32 +2658,32 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6674085202</t>
+          <t>6672667222</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>LOMAS DE SAN ISIDRO</t>
+          <t>PERISUR</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>04-09-2011</t>
+          <t>07-07-1996</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>HECOR.VALENZUELA.HERNANDEZ.2011@GMAIL.COM</t>
+          <t>MARLUI.M187@QICLOUD.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-03-2026 20:50:24</t>
+          <t>03-03-2026 17:20:12</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2728,17 +2708,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>02-03-2026 20:55:34</t>
+          <t>03-03-2026 17:25:36</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>02-03-2026 20:54:49</t>
+          <t>03-03-2026 17:24:50</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2748,7 +2728,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2758,7 +2738,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26050522820290005675</t>
+          <t>26050522850640005779</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2770,12 +2750,1096 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
+          <t>Hector Noe Espinoza Ramirez</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>347881</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>90046</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>JESUS ALFREDO</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>VILLEGAS</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SOTO</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>6675443713</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>03-12-2011</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>JUNIORCLN03@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:44:31</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:22:41</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>26050522860730005831</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>347887</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>90052</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CHRISTIAN</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>MORENO</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>BURGUEÑO</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6673329969</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>CHULAVISTA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>07-12-1995</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>BURGUEÑO16@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:54:23</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:31:17</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:30:51</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>26050522819670005672</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>347909</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>90074</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>HECTOR ABEL</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VALEZUELA </t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>6674085202</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>LOMAS DE SAN ISIDRO</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>04-09-2011</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>HECOR.VALENZUELA.HERNANDEZ.2011@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:50:24</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:55:34</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:54:49</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>26050522820290005675</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>348217</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>90382</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LORETO GUADALUPE</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SOLORIO</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>DELGADO</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>6673737751</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>29-01-1991</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>LUPITA_SOLORIO11@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:12:53</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:34:22</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>26050522921380006023</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Carlos Aurelio Monzon Ayala</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>348183</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>90348</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>KATIA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SALGUEIRO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>MILLAN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6672541846</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>LAS QUINTAS</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>03-08-1991</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>SALGUEROMILLAN@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:37:58</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:57:41</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:55:26</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>26050522852830005793</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>348220</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>90385</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ANA CECILIA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MENDOZA </t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>6671615721</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>08-06-1994</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>ANAC.M94@HTOMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:16:01</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:32:59</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>26050522921290006021</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Carlos Aurelio Monzon Ayala</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>348454</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>90619</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NICOLAS FRANSUE</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PIZARRO</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>MONZON</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6674366033</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>23-05-2009</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>MONZONN136@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:07:34</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:09:17</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>26050522884540005897</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Carlos Aurelio Monzon Ayala</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>348247</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>90412</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ANGEL</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ELIZALDE</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>6674201956</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>27-01-2001</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>ANGELELIZALDE001@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:50:39</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:31:51</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>05-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>26050522924250006040</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>Hector Noe Espinoza Ramirez</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN ISIDRO CUL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN ISIDRO CUL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC25"/>
+  <dimension ref="A1:AC29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>343497</t>
+          <t>334856</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21314</t>
+          <t>18423</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>JOSE ANGEL</t>
+          <t>LUIS MARIO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BEJARANO</t>
+          <t>ZAMUDIO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,39 +613,47 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6673417636</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>6676986831</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>CERRO QUEBRADA 2930</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>30-08-2011</t>
+          <t>24-08-2004</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CHANGELITOBAEZ@GMAIL.COM</t>
+          <t>LUISMARIOGONZALEZ@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>13-02-2026 13:37:52</t>
+          <t>14-01-2026 19:46:57</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -655,21 +663,29 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 14:19:08</t>
+          <t>06-03-2026 09:16:37</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>06-03-2026 09:08:41</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -677,7 +693,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26050522794430005558</t>
+          <t>26050522945400006113</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -709,12 +725,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>101573</t>
+          <t>343495</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>99325</t>
+          <t>21312</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,17 +740,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>JORDAN YOSIMAR</t>
+          <t>JESUS GUADALUPE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PANTOJA</t>
+          <t>PIZARRO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>MONZON</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -744,14 +760,10 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6673887174</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>MINA PANUCO 444</t>
-        </is>
-      </c>
+          <t>6675705316</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -759,24 +771,20 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>28-04-2010</t>
+          <t>12-06-2011</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>JORDAN230945@GMAIL.COM</t>
+          <t>NICOLASFRANSUEP@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>20-06-2022 14:49:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>13-02-2026 13:34:52</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -784,28 +792,28 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 13:51:54</t>
+          <t>04-03-2026 15:11:20</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -816,36 +824,44 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26050522793700005554</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+          <t>26050522884580005898</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>343494</t>
+          <t>346226</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21311</t>
+          <t>88391</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -855,17 +871,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ALEXANDER</t>
+          <t>EDGAR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZEPEDA </t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>CASTAÑEDA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -875,10 +891,14 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6679516592</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>6181597612</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>FCO I MADERO</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -886,32 +906,32 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>13-09-2011</t>
+          <t>21-08-1995</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ALEXANDER2932@GMAIL.COM</t>
+          <t>MERCADOCASTAÑEDA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>13-02-2026 13:34:47</t>
+          <t>24-02-2026 16:46:59</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -921,21 +941,29 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>04-03-2026 13:47:30</t>
+          <t>06-03-2026 16:16:57</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>06-03-2026 16:15:56</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -943,7 +971,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26050522881960005889</t>
+          <t>26050522953900006135</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1065,7 +1093,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1122,12 +1150,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>344955</t>
+          <t>101573</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22772</t>
+          <t>99325</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1137,17 +1165,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TAHOTY YACSIREE</t>
+          <t>JORDAN YOSIMAR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>VIZCARRA</t>
+          <t>PANTOJA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MILLAN</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1157,47 +1185,47 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6674271403</t>
+          <t>6673887174</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CAPSITRANO</t>
+          <t>MINA PANUCO 444</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>28-07-1998</t>
+          <t>28-04-2010</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>VIZCARRAMILLANTAHOTY@GMAIL.COM</t>
+          <t>JORDAN230945@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>18-02-2026 19:56:22</t>
+          <t>20-06-2022 14:49:00</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1207,29 +1235,21 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>03-03-2026 16:43:53</t>
+          <t>02-03-2026 13:51:54</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>02-03-2026 17:25:55</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1237,19 +1257,11 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26050522847830005765</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
-        </is>
-      </c>
+          <t>26050522793700005554</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
           <t>549</t>
@@ -1269,12 +1281,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>346278</t>
+          <t>343494</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>88443</t>
+          <t>21311</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1284,17 +1296,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MARIA EMILIA</t>
+          <t>ALEXANDER</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>OCHOA</t>
+          <t xml:space="preserve">ZEPEDA </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CAZAREZ</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1304,31 +1316,35 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6671032248</t>
+          <t>6679516592</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>13-08-1969</t>
+          <t>13-09-2011</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>EMILIAOCHOAC@HOTMAIL.COM</t>
+          <t>ALEXANDER2932@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>24-02-2026 17:56:11</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>13-02-2026 13:34:47</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -1336,28 +1352,28 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 17:31:17</t>
+          <t>04-03-2026 13:47:30</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1368,7 +1384,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26050522806750005604</t>
+          <t>26050522881960005889</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1378,34 +1394,34 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>ABIGAIL AHUMADA MARTINEZ</t>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347337</t>
+          <t>343497</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89502</t>
+          <t>21314</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1415,17 +1431,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CHEYLA  NOHEMY</t>
+          <t>JOSE ANGEL</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAUSTO </t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>BEJARANO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1435,79 +1451,63 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6673118630</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>CERRO EL TENAYO</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
+          <t>6673417636</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>09-07-1986</t>
+          <t>30-08-2011</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ALYEHS@GMAIL.COM</t>
+          <t>CHANGELITOBAEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>01-03-2026 12:22:14</t>
+          <t>13-02-2026 13:37:52</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>04-03-2026 17:29:57</t>
+          <t>02-03-2026 14:19:08</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>04-03-2026 17:29:13</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1515,36 +1515,44 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26050522890810005924</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
+          <t>26050522794430005558</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347418</t>
+          <t>347380</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89583</t>
+          <t>89545</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1554,17 +1562,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MARIA ALEJANDRA</t>
+          <t>OMAR</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>BARRAZA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SARABIA</t>
+          <t>AYON</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1574,67 +1582,63 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6675515310</t>
+          <t>6672654267</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MONTE PERDIDO ESTES 410</t>
+          <t>COSTA ADRIATICA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>15-10-2007</t>
+          <t>27-05-1990</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>SARABIAALE19@GMAIL.COM</t>
+          <t>OMAR_21@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 07:21:17</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>02-03-2026 05:08:13</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 07:28:43</t>
+          <t>02-03-2026 05:18:15</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>02-03-2026 07:27:34</t>
+          <t>02-03-2026 05:17:00</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1644,7 +1648,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1654,36 +1658,36 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26050522782410005517</t>
+          <t>26050522772930005500</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347380</t>
+          <t>344955</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89545</t>
+          <t>22772</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1693,17 +1697,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>OMAR</t>
+          <t>TAHOTY YACSIREE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BARRAZA</t>
+          <t>VIZCARRA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AYON</t>
+          <t>MILLAN</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1713,63 +1717,67 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6672654267</t>
+          <t>6674271403</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COSTA ADRIATICA</t>
+          <t>CAPSITRANO</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>27-05-1990</t>
+          <t>28-07-1998</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>OMAR_21@HOTMAIL.COM</t>
+          <t>VIZCARRAMILLANTAHOTY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 05:08:13</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>18-02-2026 19:56:22</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 05:18:15</t>
+          <t>03-03-2026 16:43:53</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>02-03-2026 05:17:00</t>
+          <t>02-03-2026 17:25:55</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1779,7 +1787,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1789,14 +1797,22 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26050522772930005500</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+          <t>26050522847830005765</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1813,12 +1829,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>348064</t>
+          <t>346278</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90229</t>
+          <t>88443</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1828,17 +1844,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ERIK BLADIMIR</t>
+          <t>MARIA EMILIA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ZARABIA</t>
+          <t>OCHOA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MERAZ</t>
+          <t>CAZAREZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1848,79 +1864,63 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6674352372</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>22 DE DIC</t>
-        </is>
-      </c>
+          <t>6671032248</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>23-02-1999</t>
+          <t>13-08-1969</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>ERIKBLADIMIR@GMAIL.COM</t>
+          <t>EMILIAOCHOAC@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>03-03-2026 14:36:16</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>24-02-2026 17:56:11</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>03-03-2026 14:40:34</t>
+          <t>02-03-2026 17:31:17</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>03-03-2026 14:39:53</t>
-        </is>
-      </c>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1928,14 +1928,22 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26050522842200005742</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+          <t>26050522806750005604</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1952,12 +1960,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>348151</t>
+          <t>347337</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90316</t>
+          <t>89502</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1967,17 +1975,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>JULIO CESAR</t>
+          <t>CHEYLA  NOHEMY</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ELIZALDE</t>
+          <t xml:space="preserve">FAUSTO </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1987,12 +1995,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6673418071</t>
+          <t>6673118630</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PERISUR</t>
+          <t>CERRO EL TENAYO</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2002,17 +2010,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>25-02-1990</t>
+          <t>09-07-1986</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>JULIOCESAR1@GMAIL.COM</t>
+          <t>ALYEHS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>03-03-2026 17:10:14</t>
+          <t>01-03-2026 12:22:14</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2037,7 +2045,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>03-03-2026 17:17:25</t>
+          <t>04-03-2026 17:29:57</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2047,7 +2055,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>03-03-2026 17:16:26</t>
+          <t>04-03-2026 17:29:13</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2067,7 +2075,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26050522849920005776</t>
+          <t>26050522890810005924</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -2079,24 +2087,24 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347633</t>
+          <t>347418</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>89798</t>
+          <t>89583</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2106,17 +2114,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ROGELIO</t>
+          <t>MARIA ALEJANDRA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CAMBERO</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>SARABIA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2126,43 +2134,47 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3112033428</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>6675515310</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MONTE PERDIDO ESTES 410</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>22-06-1979</t>
+          <t>15-10-2007</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>ROQEIROCAMBERO@YAHOO.COM</t>
+          <t>SARABIAALE19@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 15:30:56</t>
+          <t>02-03-2026 07:21:17</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2172,21 +2184,29 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 15:38:54</t>
+          <t>02-03-2026 07:28:43</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>02-03-2026 07:27:34</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2194,7 +2214,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26050522798030005567</t>
+          <t>26050522782410005517</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2206,24 +2226,24 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347691</t>
+          <t>347887</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>89856</t>
+          <t>90052</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2233,17 +2253,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FLOR DANIELA</t>
+          <t>CHRISTIAN</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>BURGUEÑO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2253,57 +2273,57 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6673265018</t>
+          <t>6673329969</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>LOMAS DE SAN ISIDRO</t>
+          <t>CHULAVISTA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>14-03-2004</t>
+          <t>07-12-1995</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>SALAZAR16QUINTERO@GMAIL.COM</t>
+          <t>BURGUEÑO16@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 16:40:39</t>
+          <t>02-03-2026 19:54:23</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-03-2026 16:50:11</t>
+          <t>02-03-2026 20:31:17</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2313,7 +2333,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>02-03-2026 16:46:57</t>
+          <t>02-03-2026 20:30:51</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2333,24 +2353,32 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26050522803300005585</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+          <t>26050522819670005672</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2471,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2480,24 +2508,24 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>343495</t>
+          <t>347633</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21312</t>
+          <t>89798</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2507,17 +2535,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>JESUS GUADALUPE</t>
+          <t>ROGELIO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PIZARRO</t>
+          <t>CAMBERO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MONZON</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2527,7 +2555,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6675705316</t>
+          <t>3112033428</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2538,20 +2566,24 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>12-06-2011</t>
+          <t>22-06-1979</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>NICOLASFRANSUEP@GMAIL.COM</t>
+          <t>ROQEIROCAMBERO@YAHOO.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>13-02-2026 13:34:52</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>02-03-2026 15:30:56</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -2559,22 +2591,22 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>04-03-2026 15:11:20</t>
+          <t>02-03-2026 15:38:54</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>04-06-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2591,44 +2623,36 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26050522884580005898</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>ABIGAIL AHUMADA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26050522798030005567</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>348165</t>
+          <t>347691</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90330</t>
+          <t>89856</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2638,17 +2662,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BRISEIDA</t>
+          <t>FLOR DANIELA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2658,12 +2682,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6672667222</t>
+          <t>6673265018</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>PERISUR</t>
+          <t>LOMAS DE SAN ISIDRO</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2673,17 +2697,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>07-07-1996</t>
+          <t>14-03-2004</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>MARLUI.M187@QICLOUD.COM</t>
+          <t>SALAZAR16QUINTERO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>03-03-2026 17:20:12</t>
+          <t>02-03-2026 16:40:39</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2708,17 +2732,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>03-03-2026 17:25:36</t>
+          <t>02-03-2026 16:50:11</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>03-03-2026 17:24:50</t>
+          <t>02-03-2026 16:46:57</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2738,7 +2762,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26050522850640005779</t>
+          <t>26050522803300005585</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2750,7 +2774,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Hector Noe Espinoza Ramirez</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2762,12 +2786,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>347881</t>
+          <t>348217</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90046</t>
+          <t>90382</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2777,17 +2801,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>JESUS ALFREDO</t>
+          <t>LORETO GUADALUPE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>VILLEGAS</t>
+          <t>SOLORIO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>DELGADO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2797,7 +2821,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6675443713</t>
+          <t>6673737751</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2808,17 +2832,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>03-12-2011</t>
+          <t>29-01-1991</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>JUNIORCLN03@GMAIL.COM</t>
+          <t>LUPITA_SOLORIO11@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>02-03-2026 19:44:31</t>
+          <t>03-03-2026 18:12:53</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2843,12 +2867,12 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>03-03-2026 20:22:41</t>
+          <t>05-03-2026 16:34:22</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2865,7 +2889,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26050522860730005831</t>
+          <t>26050522921380006023</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2885,24 +2909,24 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>347887</t>
+          <t>347909</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90052</t>
+          <t>90074</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2912,17 +2936,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CHRISTIAN</t>
+          <t>HECTOR ABEL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t xml:space="preserve">VALEZUELA </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BURGUEÑO</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2932,12 +2956,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6673329969</t>
+          <t>6674085202</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CHULAVISTA</t>
+          <t>LOMAS DE SAN ISIDRO</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2947,52 +2971,52 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>07-12-1995</t>
+          <t>04-09-2011</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>BURGUEÑO16@GMAIL.COM</t>
+          <t>HECOR.VALENZUELA.HERNANDEZ.2011@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-03-2026 19:54:23</t>
+          <t>02-03-2026 20:50:24</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>02-03-2026 20:31:17</t>
+          <t>02-03-2026 20:55:34</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>02-03-2026 20:30:51</t>
+          <t>02-03-2026 20:54:49</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3002,7 +3026,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -3012,22 +3036,14 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26050522819670005672</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
-        </is>
-      </c>
+          <t>26050522820290005675</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -3044,12 +3060,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>347909</t>
+          <t>347881</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90074</t>
+          <t>90046</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3059,17 +3075,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>HECTOR ABEL</t>
+          <t>JESUS ALFREDO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALEZUELA </t>
+          <t>VILLEGAS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3079,57 +3095,53 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6674085202</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>LOMAS DE SAN ISIDRO</t>
-        </is>
-      </c>
+          <t>6675443713</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>04-09-2011</t>
+          <t>03-12-2011</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>HECOR.VALENZUELA.HERNANDEZ.2011@GMAIL.COM</t>
+          <t>JUNIORCLN03@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-03-2026 20:50:24</t>
+          <t>02-03-2026 19:44:31</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>02-03-2026 20:55:34</t>
+          <t>03-03-2026 20:22:41</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -3137,21 +3149,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>02-03-2026 20:54:49</t>
-        </is>
-      </c>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3159,14 +3163,22 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26050522820290005675</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+          <t>26050522860730005831</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3183,12 +3195,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>348217</t>
+          <t>348247</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90382</t>
+          <t>90412</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3198,17 +3210,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LORETO GUADALUPE</t>
+          <t>ANGEL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SOLORIO</t>
+          <t>ELIZALDE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>DELGADO</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3218,35 +3230,31 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6673737751</t>
+          <t>6674201956</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>29-01-1991</t>
+          <t>27-01-2001</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>LUPITA_SOLORIO11@HOTMAIL.COM</t>
+          <t>ANGELELIZALDE001@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>03-03-2026 18:12:53</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>03-03-2026 18:50:39</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -3254,22 +3262,22 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>05-03-2026 16:34:22</t>
+          <t>05-03-2026 17:31:51</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>04-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -3286,7 +3294,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26050522921380006023</t>
+          <t>26050522924250006040</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3296,17 +3304,17 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>Hector Noe Espinoza Ramirez</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3318,12 +3326,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>348183</t>
+          <t>348334</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>90348</t>
+          <t>90499</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3333,17 +3341,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KATIA</t>
+          <t>KARLA FABIOLA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SALGUEIRO</t>
+          <t>YEE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MILLAN</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3353,12 +3361,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6672541846</t>
+          <t>6673209514</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>LAS QUINTAS</t>
+          <t>FRAY SERVANDO 4369</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3368,52 +3376,52 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>03-08-1991</t>
+          <t>29-10-1989</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>SALGUEROMILLAN@GMAIL.COM</t>
+          <t>KARLAYEE89@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>03-03-2026 17:37:58</t>
+          <t>04-03-2026 07:40:53</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>03-03-2026 17:57:41</t>
+          <t>06-03-2026 08:02:02</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>03-03-2026 17:55:26</t>
+          <t>06-03-2026 08:00:48</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3423,7 +3431,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3433,36 +3441,44 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26050522852830005793</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
+          <t>26050522943920006105</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Carmen Michel Navarrete  Nevarez</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Gilberto Tavarez Soto</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>348220</t>
+          <t>348183</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>90385</t>
+          <t>90348</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3472,17 +3488,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ANA CECILIA</t>
+          <t>KATIA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">MENDOZA </t>
+          <t>SALGUEIRO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>MILLAN</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3492,10 +3508,14 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6671615721</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>6672541846</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>LAS QUINTAS</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3503,56 +3523,64 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>08-06-1994</t>
+          <t>03-08-1991</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ANAC.M94@HTOMAIL.COM</t>
+          <t>SALGUEROMILLAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>03-03-2026 18:16:01</t>
+          <t>03-03-2026 17:37:58</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>05-03-2026 16:32:59</t>
+          <t>03-03-2026 17:57:41</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:55:26</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3560,44 +3588,36 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26050522921290006021</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
-        </is>
-      </c>
+          <t>26050522852830005793</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>348454</t>
+          <t>348220</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>90619</t>
+          <t>90385</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3607,17 +3627,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NICOLAS FRANSUE</t>
+          <t>ANA CECILIA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PIZARRO</t>
+          <t xml:space="preserve">MENDOZA </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MONZON</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3627,31 +3647,35 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6674366033</t>
+          <t>6671615721</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>23-05-2009</t>
+          <t>08-06-1994</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>MONZONN136@GMAIL.COM</t>
+          <t>ANAC.M94@HTOMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>04-03-2026 15:07:34</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>03-03-2026 18:16:01</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -3659,22 +3683,22 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>04-03-2026 15:09:17</t>
+          <t>05-03-2026 16:32:59</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>04-06-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -3691,14 +3715,22 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26050522884540005897</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
+          <t>26050522921290006021</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3715,12 +3747,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>348247</t>
+          <t>348454</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>90412</t>
+          <t>90619</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3730,17 +3762,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ANGEL</t>
+          <t>NICOLAS FRANSUE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ELIZALDE</t>
+          <t>PIZARRO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MONZON</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3750,7 +3782,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6674201956</t>
+          <t>6674366033</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3761,17 +3793,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>27-01-2001</t>
+          <t>23-05-2009</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ANGELELIZALDE001@GMAIL.COM</t>
+          <t>MONZONN136@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>03-03-2026 18:50:39</t>
+          <t>04-03-2026 15:07:34</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3782,22 +3814,22 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>05-03-2026 17:31:51</t>
+          <t>04-03-2026 15:09:17</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>05-06-2026 23:59:59</t>
+          <t>03-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -3814,32 +3846,580 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26050522924250006040</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>ABIGAIL AHUMADA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26050522884540005897</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
+          <t>Carlos Aurelio Monzon Ayala</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>348165</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>90330</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>BRISEIDA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>MORALES</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>6672667222</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>PERISUR</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>07-07-1996</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>MARLUI.M187@QICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:20:12</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:25:36</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:24:50</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>26050522850640005779</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
           <t>Hector Noe Espinoza Ramirez</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>349034</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>91199</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BERENICE </t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>FUENTES</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>AGUILAR</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6676693845</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ORIV.MONTANESA</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>25-01-1992</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>MARIAAGUILAR2501@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>06-03-2026 19:18:53</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>06-03-2026 19:24:57</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>06-03-2026 19:22:43</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>26050522960420006170</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>348064</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>90229</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ERIK BLADIMIR</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ZARABIA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>MERAZ</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6674352372</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>22 DE DIC</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>23-02-1999</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>ERIKBLADIMIR@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>03-03-2026 14:36:16</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>03-03-2026 14:40:34</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>03-03-2026 14:39:53</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>26050522842200005742</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>Carlos Aurelio Monzon Ayala</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>348151</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>90316</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>JULIO CESAR</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ELIZALDE</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>6673418071</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>PERISUR</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>25-02-1990</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>JULIOCESAR1@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:10:14</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:17:25</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:16:26</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>26050522849920005776</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN ISIDRO CUL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SAN ISIDRO CUL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC29"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>334856</t>
+          <t>198767</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18423</t>
+          <t>96274</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LUIS MARIO</t>
+          <t>MANUEL EDAURDO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>LÓPEZ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ZAMUDIO</t>
+          <t>LARA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,14 +613,10 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6676986831</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>CERRO QUEBRADA 2930</t>
-        </is>
-      </c>
+          <t>6676584657</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -628,32 +624,32 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>24-08-2004</t>
+          <t>03-12-2006</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>LUISMARIOGONZALEZ@HOTMAIL.COM</t>
+          <t>LOPEZLARAMANUELEDUARDO2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>14-01-2026 19:46:57</t>
+          <t>25-09-2023 19:29:28</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -663,29 +659,21 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>06-03-2026 09:16:37</t>
+          <t>10-03-2026 19:11:57</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>06-03-2026 09:08:41</t>
-        </is>
-      </c>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -693,19 +681,11 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26050522945400006113</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
-        </is>
-      </c>
+          <t>26050523067090006480</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
           <t>549</t>
@@ -725,12 +705,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>343495</t>
+          <t>246508</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21312</t>
+          <t>44013</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -740,17 +720,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>JESUS GUADALUPE</t>
+          <t xml:space="preserve">MARIO RAFAEL </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PIZARRO</t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MONZON</t>
+          <t>FIGUEROA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -760,10 +740,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6675705316</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>6691434328</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>LOMAS DE SAN ISIDRO</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -771,52 +755,64 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>12-06-2011</t>
+          <t>04-08-1978</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>NICOLASFRANSUEP@GMAIL.COM</t>
+          <t>CARLOSSANCHEZ22040307@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>13-02-2026 13:34:52</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>17-07-2024 07:42:19</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>04-03-2026 15:11:20</t>
+          <t>12-03-2026 21:06:30</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>03-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>12-03-2026 21:05:38</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -824,44 +820,36 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26050522884580005898</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>ABIGAIL AHUMADA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26050523138130006767</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>346226</t>
+          <t>334515</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>88391</t>
+          <t>18082</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -871,17 +859,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EDGAR</t>
+          <t>LORENA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>ALARCON</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CASTAÑEDA</t>
+          <t>BEJARANO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -891,32 +879,32 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6181597612</t>
+          <t>6674064116</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FCO I MADERO</t>
+          <t xml:space="preserve">ADOLFO LOPEZ </t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>21-08-1995</t>
+          <t>26-09-1974</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>MERCADOCASTAÑEDA@GMAIL.COM</t>
+          <t>ALARCONBEJARANOS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>24-02-2026 16:46:59</t>
+          <t>13-01-2026 17:50:35</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -941,17 +929,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>06-03-2026 16:16:57</t>
+          <t>02-03-2026 19:51:47</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>06-03-2026 16:15:56</t>
+          <t>02-03-2026 19:51:10</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -961,7 +949,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -971,7 +959,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26050522953900006135</t>
+          <t>26050522818160005664</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -981,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +991,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>334515</t>
+          <t>101573</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18082</t>
+          <t>99325</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1018,17 +1006,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LORENA</t>
+          <t>JORDAN YOSIMAR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ALARCON</t>
+          <t>PANTOJA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BEJARANO</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1038,47 +1026,47 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6674064116</t>
+          <t>6673887174</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADOLFO LOPEZ </t>
+          <t>MINA PANUCO 444</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>26-09-1974</t>
+          <t>28-04-2010</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ALARCONBEJARANOS@GMAIL.COM</t>
+          <t>JORDAN230945@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>13-01-2026 17:50:35</t>
+          <t>20-06-2022 14:49:00</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1088,7 +1076,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 19:51:47</t>
+          <t>02-03-2026 13:51:54</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1096,21 +1084,13 @@
           <t>01-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>02-03-2026 19:51:10</t>
-        </is>
-      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1118,19 +1098,11 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26050522818160005664</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>ABIGAIL AHUMADA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26050522793700005554</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
           <t>549</t>
@@ -1150,12 +1122,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>101573</t>
+          <t>344955</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>99325</t>
+          <t>22772</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1165,17 +1137,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>JORDAN YOSIMAR</t>
+          <t>TAHOTY YACSIREE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PANTOJA</t>
+          <t>VIZCARRA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>MILLAN</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1185,47 +1157,47 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6673887174</t>
+          <t>6674271403</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MINA PANUCO 444</t>
+          <t>CAPSITRANO</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>28-04-2010</t>
+          <t>28-07-1998</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>JORDAN230945@GMAIL.COM</t>
+          <t>VIZCARRAMILLANTAHOTY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>20-06-2022 14:49:00</t>
+          <t>18-02-2026 19:56:22</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1235,7 +1207,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 13:51:54</t>
+          <t>03-03-2026 16:43:53</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1243,13 +1215,21 @@
           <t>01-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:25:55</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1257,11 +1237,19 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26050522793700005554</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+          <t>26050522847830005765</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>549</t>
@@ -1281,12 +1269,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>343494</t>
+          <t>346278</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21311</t>
+          <t>88443</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1296,17 +1284,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ALEXANDER</t>
+          <t>MARIA EMILIA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZEPEDA </t>
+          <t>OCHOA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>CAZAREZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1316,35 +1304,31 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6679516592</t>
+          <t>6671032248</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>13-09-2011</t>
+          <t>13-08-1969</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ALEXANDER2932@GMAIL.COM</t>
+          <t>EMILIAOCHOAC@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>13-02-2026 13:34:47</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>24-02-2026 17:56:11</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -1352,28 +1336,28 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>04-03-2026 13:47:30</t>
+          <t>02-03-2026 17:31:17</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1384,7 +1368,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26050522881960005889</t>
+          <t>26050522806750005604</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1394,34 +1378,34 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>343497</t>
+          <t>334856</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21314</t>
+          <t>18423</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1431,17 +1415,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JOSE ANGEL</t>
+          <t>LUIS MARIO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BEJARANO</t>
+          <t>ZAMUDIO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1451,39 +1435,47 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6673417636</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>6676986831</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CERRO QUEBRADA 2930</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>30-08-2011</t>
+          <t>24-08-2004</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CHANGELITOBAEZ@GMAIL.COM</t>
+          <t>LUISMARIOGONZALEZ@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>13-02-2026 13:37:52</t>
+          <t>14-01-2026 19:46:57</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1493,21 +1485,29 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 14:19:08</t>
+          <t>06-03-2026 09:16:37</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>06-03-2026 09:08:41</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26050522794430005558</t>
+          <t>26050522945400006113</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347380</t>
+          <t>343495</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89545</t>
+          <t>21312</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1562,17 +1562,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>OMAR</t>
+          <t>JESUS GUADALUPE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BARRAZA</t>
+          <t>PIZARRO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AYON</t>
+          <t>MONZON</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1582,14 +1582,10 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6672654267</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>COSTA ADRIATICA</t>
-        </is>
-      </c>
+          <t>6675705316</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1597,60 +1593,52 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>27-05-1990</t>
+          <t>12-06-2011</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>OMAR_21@HOTMAIL.COM</t>
+          <t>NICOLASFRANSUEP@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 05:08:13</t>
+          <t>13-02-2026 13:34:52</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 05:18:15</t>
+          <t>04-03-2026 15:11:20</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>02-03-2026 05:17:00</t>
-        </is>
-      </c>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1658,36 +1646,44 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26050522772930005500</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+          <t>26050522884580005898</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>344955</t>
+          <t>343494</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22772</t>
+          <t>21311</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1697,17 +1693,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>TAHOTY YACSIREE</t>
+          <t>ALEXANDER</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VIZCARRA</t>
+          <t xml:space="preserve">ZEPEDA </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MILLAN</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1717,47 +1713,43 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6674271403</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>CAPSITRANO</t>
-        </is>
-      </c>
+          <t>6679516592</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>28-07-1998</t>
+          <t>13-09-2011</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>VIZCARRAMILLANTAHOTY@GMAIL.COM</t>
+          <t>ALEXANDER2932@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>18-02-2026 19:56:22</t>
+          <t>13-02-2026 13:34:47</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1767,29 +1759,21 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-03-2026 16:43:53</t>
+          <t>04-03-2026 13:47:30</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>02-03-2026 17:25:55</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1797,12 +1781,12 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26050522847830005765</t>
+          <t>26050522881960005889</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1829,12 +1813,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>346278</t>
+          <t>343497</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>88443</t>
+          <t>21314</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1844,17 +1828,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MARIA EMILIA</t>
+          <t>JOSE ANGEL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OCHOA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CAZAREZ</t>
+          <t>BEJARANO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1864,31 +1848,31 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6671032248</t>
+          <t>6673417636</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>13-08-1969</t>
+          <t>30-08-2011</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>EMILIAOCHOAC@HOTMAIL.COM</t>
+          <t>CHANGELITOBAEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>24-02-2026 17:56:11</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>13-02-2026 13:37:52</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -1896,22 +1880,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-03-2026 17:31:17</t>
+          <t>02-03-2026 14:19:08</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1928,7 +1912,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26050522806750005604</t>
+          <t>26050522794430005558</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1938,34 +1922,34 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>ABIGAIL AHUMADA MARTINEZ</t>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347337</t>
+          <t>347170</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>89502</t>
+          <t>89335</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1975,17 +1959,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CHEYLA  NOHEMY</t>
+          <t>FERNANDO ARTURO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAUSTO </t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>GASTELUM</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1995,12 +1979,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6673118630</t>
+          <t>6674868380</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CERRO EL TENAYO</t>
+          <t>RAFAEL OCEGERA RAMOS</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2010,52 +1994,52 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>09-07-1986</t>
+          <t>28-01-1992</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>ALYEHS@GMAIL.COM</t>
+          <t>FERNANDOARTUROGARCIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>01-03-2026 12:22:14</t>
+          <t>28-02-2026 09:48:15</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>04-03-2026 17:29:57</t>
+          <t>16-03-2026 09:36:41</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>15-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>04-03-2026 17:29:13</t>
+          <t>16-03-2026 09:31:36</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2075,36 +2059,44 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26050522890810005924</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+          <t>26050523212760006946</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347418</t>
+          <t>346226</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>89583</t>
+          <t>88391</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2114,17 +2106,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MARIA ALEJANDRA</t>
+          <t>EDGAR</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SARABIA</t>
+          <t>CASTAÑEDA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2134,37 +2126,37 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6675515310</t>
+          <t>6181597612</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MONTE PERDIDO ESTES 410</t>
+          <t>FCO I MADERO</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>15-10-2007</t>
+          <t>21-08-1995</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>SARABIAALE19@GMAIL.COM</t>
+          <t>MERCADOCASTAÑEDA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 07:21:17</t>
+          <t>24-02-2026 16:46:59</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2174,7 +2166,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2184,17 +2176,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 07:28:43</t>
+          <t>06-03-2026 16:16:57</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>02-03-2026 07:27:34</t>
+          <t>06-03-2026 16:15:56</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2204,7 +2196,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2214,11 +2206,19 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26050522782410005517</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+          <t>26050522953900006135</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>549</t>
@@ -2226,24 +2226,24 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347887</t>
+          <t>321868</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90052</t>
+          <t>18807</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2253,17 +2253,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CHRISTIAN</t>
+          <t>JUAN ENRIQUE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>BURGUEÑO</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2273,32 +2273,32 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6673329969</t>
+          <t>6673942874</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CHULAVISTA</t>
+          <t>ADOLFO LOPEZ</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>07-12-1995</t>
+          <t>20-11-1998</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>BURGUEÑO16@GMAIL.COM</t>
+          <t>ENRIQUELOPEZVARGAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 19:54:23</t>
+          <t>03-11-2025 18:09:14</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-03-2026 20:31:17</t>
+          <t>10-03-2026 19:23:34</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>09-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>02-03-2026 20:30:51</t>
+          <t>10-03-2026 19:22:32</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26050522819670005672</t>
+          <t>26050523068030006489</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2373,24 +2373,24 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347568</t>
+          <t>321997</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>89733</t>
+          <t>18936</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2400,17 +2400,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE LUIS </t>
+          <t>FAITH ALEJANDRA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>GUZMAN</t>
+          <t>SAUCEDA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>SAUCEDA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2420,67 +2420,79 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6671377797</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>6677577645</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>VILLA BONITA</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>17-11-2010</t>
+          <t>04-06-2005</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>JOSELUISGUZMANMORENO0@GMAIL.COM</t>
+          <t>ALEXANDRASAUCEDA22@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-03-2026 13:32:21</t>
+          <t>04-11-2025 10:19:26</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>05-03-2026 14:00:36</t>
+          <t>11-03-2026 17:15:24</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
+          <t>10-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>11-03-2026 17:15:06</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2488,7 +2500,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26050522916410006008</t>
+          <t>26050523094700006589</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2498,34 +2510,34 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>CARLOS AURELIO MONZON AYALA</t>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347633</t>
+          <t>347380</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>89798</t>
+          <t>89545</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2535,17 +2547,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ROGELIO</t>
+          <t>OMAR</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CAMBERO</t>
+          <t>BARRAZA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>AYON</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2555,10 +2567,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3112033428</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>6672654267</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>COSTA ADRIATICA</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2566,42 +2582,38 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>22-06-1979</t>
+          <t>27-05-1990</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ROQEIROCAMBERO@YAHOO.COM</t>
+          <t>OMAR_21@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-03-2026 15:30:56</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>02-03-2026 05:08:13</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-03-2026 15:38:54</t>
+          <t>02-03-2026 05:18:15</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2609,13 +2621,21 @@
           <t>01-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>02-03-2026 05:17:00</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2623,14 +2643,14 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26050522798030005567</t>
+          <t>26050522772930005500</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2647,12 +2667,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>347691</t>
+          <t>347633</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>89856</t>
+          <t>89798</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2662,17 +2682,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FLOR DANIELA</t>
+          <t>ROGELIO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>CAMBERO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2682,57 +2702,53 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6673265018</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>LOMAS DE SAN ISIDRO</t>
-        </is>
-      </c>
+          <t>3112033428</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>14-03-2004</t>
+          <t>22-06-1979</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>SALAZAR16QUINTERO@GMAIL.COM</t>
+          <t>ROQEIROCAMBERO@YAHOO.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-03-2026 16:40:39</t>
+          <t>02-03-2026 15:30:56</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>02-03-2026 16:50:11</t>
+          <t>02-03-2026 15:38:54</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2740,21 +2756,13 @@
           <t>01-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>02-03-2026 16:46:57</t>
-        </is>
-      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2762,36 +2770,36 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26050522803300005585</t>
+          <t>26050522798030005567</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>348217</t>
+          <t>347691</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90382</t>
+          <t>89856</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2801,17 +2809,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LORETO GUADALUPE</t>
+          <t>FLOR DANIELA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SOLORIO</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>DELGADO</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2821,10 +2829,14 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6673737751</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>6673265018</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>LOMAS DE SAN ISIDRO</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2832,56 +2844,64 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>29-01-1991</t>
+          <t>14-03-2004</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>LUPITA_SOLORIO11@HOTMAIL.COM</t>
+          <t>SALAZAR16QUINTERO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>03-03-2026 18:12:53</t>
+          <t>02-03-2026 16:40:39</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>05-03-2026 16:34:22</t>
+          <t>02-03-2026 16:50:11</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:46:57</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2889,22 +2909,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26050522921380006023</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
-        </is>
-      </c>
+          <t>26050522803300005585</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2921,12 +2933,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>347909</t>
+          <t>347337</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90074</t>
+          <t>89502</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2936,17 +2948,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HECTOR ABEL</t>
+          <t>CHEYLA  NOHEMY</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALEZUELA </t>
+          <t xml:space="preserve">FAUSTO </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2956,12 +2968,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6674085202</t>
+          <t>6673118630</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>LOMAS DE SAN ISIDRO</t>
+          <t>CERRO EL TENAYO</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2971,17 +2983,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>04-09-2011</t>
+          <t>09-07-1986</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>HECOR.VALENZUELA.HERNANDEZ.2011@GMAIL.COM</t>
+          <t>ALYEHS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-03-2026 20:50:24</t>
+          <t>01-03-2026 12:22:14</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3006,17 +3018,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>02-03-2026 20:55:34</t>
+          <t>04-03-2026 17:29:57</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>02-03-2026 20:54:49</t>
+          <t>04-03-2026 17:29:13</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3026,7 +3038,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -3036,7 +3048,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26050522820290005675</t>
+          <t>26050522890810005924</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
@@ -3048,24 +3060,24 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>347881</t>
+          <t>347418</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90046</t>
+          <t>89583</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3075,17 +3087,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>JESUS ALFREDO</t>
+          <t>MARIA ALEJANDRA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>VILLEGAS</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>SARABIA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3095,10 +3107,14 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6675443713</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>6675515310</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MONTE PERDIDO ESTES 410</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3106,32 +3122,32 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>03-12-2011</t>
+          <t>15-10-2007</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>JUNIORCLN03@GMAIL.COM</t>
+          <t>SARABIAALE19@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-03-2026 19:44:31</t>
+          <t>02-03-2026 07:21:17</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -3141,21 +3157,29 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>03-03-2026 20:22:41</t>
+          <t>02-03-2026 07:28:43</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>02-03-2026 07:27:34</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3163,19 +3187,11 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26050522860730005831</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
-        </is>
-      </c>
+          <t>26050522782410005517</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
           <t>549</t>
@@ -3183,24 +3199,24 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>348247</t>
+          <t>347254</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90412</t>
+          <t>89419</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3210,17 +3226,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ANGEL</t>
+          <t>SHAKTI DOMINIKA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ELIZALDE</t>
+          <t xml:space="preserve">ESCOBAR </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3230,31 +3246,35 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6674201956</t>
+          <t>6674182835</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>27-01-2001</t>
+          <t>07-07-2006</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ANGELELIZALDE001@GMAIL.COM</t>
+          <t>ESCOBARQUINTEROSHAKTI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>03-03-2026 18:50:39</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>28-02-2026 14:04:03</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -3262,22 +3282,22 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>05-03-2026 17:31:51</t>
+          <t>17-03-2026 17:32:33</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>04-06-2026 23:59:59</t>
+          <t>16-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -3294,22 +3314,14 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26050522924250006040</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>ABIGAIL AHUMADA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26050523261970007089</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3326,12 +3338,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>348334</t>
+          <t>347779</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>90499</t>
+          <t>89944</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3341,17 +3353,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KARLA FABIOLA</t>
+          <t>MARTIN ALBERTO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>YEE</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>VILLA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3361,47 +3373,43 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6673209514</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>FRAY SERVANDO 4369</t>
-        </is>
-      </c>
+          <t>6671836658</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>29-10-1989</t>
+          <t>13-07-2005</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>KARLAYEE89@GMAIL.COM</t>
+          <t>MARTINPEREZVR613@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>04-03-2026 07:40:53</t>
+          <t>02-03-2026 17:58:49</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -3411,29 +3419,21 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>06-03-2026 08:02:02</t>
+          <t>09-03-2026 10:51:07</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>06-03-2026 08:00:48</t>
-        </is>
-      </c>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26050522943920006105</t>
+          <t>26050523003720006278</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>Carmen Michel Navarrete  Nevarez</t>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3461,24 +3461,24 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Gilberto Tavarez Soto</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>348183</t>
+          <t>347881</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>90348</t>
+          <t>90046</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>KATIA</t>
+          <t>JESUS ALFREDO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SALGUEIRO</t>
+          <t>VILLEGAS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MILLAN</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3508,14 +3508,10 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6672541846</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>LAS QUINTAS</t>
-        </is>
-      </c>
+          <t>6675443713</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3523,42 +3519,42 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>03-08-1991</t>
+          <t>03-12-2011</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>SALGUEROMILLAN@GMAIL.COM</t>
+          <t>JUNIORCLN03@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>03-03-2026 17:37:58</t>
+          <t>02-03-2026 19:44:31</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>03-03-2026 17:57:41</t>
+          <t>03-03-2026 20:22:41</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3566,21 +3562,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>03-03-2026 17:55:26</t>
-        </is>
-      </c>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3588,14 +3576,22 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26050522852830005793</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
+          <t>26050522860730005831</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3612,12 +3608,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>348220</t>
+          <t>347568</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>90385</t>
+          <t>89733</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3627,17 +3623,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ANA CECILIA</t>
+          <t xml:space="preserve">JOSE LUIS </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">MENDOZA </t>
+          <t>GUZMAN</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3647,28 +3643,28 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6671615721</t>
+          <t>6671377797</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>08-06-1994</t>
+          <t>17-11-2010</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>ANAC.M94@HTOMAIL.COM</t>
+          <t>JOSELUISGUZMANMORENO0@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>03-03-2026 18:16:01</t>
+          <t>02-03-2026 13:32:21</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3693,7 +3689,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>05-03-2026 16:32:59</t>
+          <t>05-03-2026 14:00:36</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3704,7 +3700,7 @@
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V24" t="inlineStr"/>
@@ -3715,7 +3711,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26050522921290006021</t>
+          <t>26050522916410006008</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3725,7 +3721,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+          <t>CARLOS AURELIO MONZON AYALA</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3747,12 +3743,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>348454</t>
+          <t>347887</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>90619</t>
+          <t>90052</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3762,17 +3758,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NICOLAS FRANSUE</t>
+          <t>CHRISTIAN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PIZARRO</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MONZON</t>
+          <t>BURGUEÑO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3782,10 +3778,14 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6674366033</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>6673329969</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>CHULAVISTA</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3793,52 +3793,64 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>23-05-2009</t>
+          <t>07-12-1995</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>MONZONN136@GMAIL.COM</t>
+          <t>BURGUEÑO16@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>04-03-2026 15:07:34</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>02-03-2026 19:54:23</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>04-03-2026 15:09:17</t>
+          <t>02-03-2026 20:31:17</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>03-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:30:51</t>
+        </is>
+      </c>
       <c r="U25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W25" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3846,36 +3858,44 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26050522884540005897</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
+          <t>26050522819670005672</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>348165</t>
+          <t>348183</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>90330</t>
+          <t>90348</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3885,17 +3905,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>BRISEIDA</t>
+          <t>KATIA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>SALGUEIRO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>MILLAN</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3905,12 +3925,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6672667222</t>
+          <t>6672541846</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PERISUR</t>
+          <t>LAS QUINTAS</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3920,17 +3940,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>07-07-1996</t>
+          <t>03-08-1991</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>MARLUI.M187@QICLOUD.COM</t>
+          <t>SALGUEROMILLAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>03-03-2026 17:20:12</t>
+          <t>03-03-2026 17:37:58</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3955,7 +3975,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>03-03-2026 17:25:36</t>
+          <t>03-03-2026 17:57:41</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3965,7 +3985,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>03-03-2026 17:24:50</t>
+          <t>03-03-2026 17:55:26</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3975,7 +3995,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3985,7 +4005,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26050522850640005779</t>
+          <t>26050522852830005793</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
@@ -3997,24 +4017,24 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Hector Noe Espinoza Ramirez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>349034</t>
+          <t>348220</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>91199</t>
+          <t>90385</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4024,17 +4044,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">BERENICE </t>
+          <t>ANA CECILIA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FUENTES</t>
+          <t xml:space="preserve">MENDOZA </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4044,14 +4064,10 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6676693845</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>ORIV.MONTANESA</t>
-        </is>
-      </c>
+          <t>6671615721</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4059,32 +4075,32 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>25-01-1992</t>
+          <t>08-06-1994</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>MARIAAGUILAR2501@GMAIL.COM</t>
+          <t>ANAC.M94@HTOMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>06-03-2026 19:18:53</t>
+          <t>03-03-2026 18:16:01</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -4094,29 +4110,21 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>06-03-2026 19:24:57</t>
+          <t>05-03-2026 16:32:59</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>06-03-2026 19:22:43</t>
-        </is>
-      </c>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4124,11 +4132,19 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26050522960420006170</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
+          <t>26050522921290006021</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>549</t>
@@ -4136,24 +4152,24 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Aurelio Monzon Ayala</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>348064</t>
+          <t>348165</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>90229</t>
+          <t>90330</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4163,17 +4179,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ERIK BLADIMIR</t>
+          <t>BRISEIDA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ZARABIA</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MERAZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4183,32 +4199,32 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6674352372</t>
+          <t>6672667222</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>22 DE DIC</t>
+          <t>PERISUR</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>23-02-1999</t>
+          <t>07-07-1996</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>ERIKBLADIMIR@GMAIL.COM</t>
+          <t>MARLUI.M187@QICLOUD.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>03-03-2026 14:36:16</t>
+          <t>03-03-2026 17:20:12</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4233,7 +4249,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>03-03-2026 14:40:34</t>
+          <t>03-03-2026 17:25:36</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -4243,7 +4259,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>03-03-2026 14:39:53</t>
+          <t>03-03-2026 17:24:50</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4263,7 +4279,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26050522842200005742</t>
+          <t>26050522850640005779</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
@@ -4275,7 +4291,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Carlos Aurelio Monzon Ayala</t>
+          <t>Hector Noe Espinoza Ramirez</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4287,139 +4303,4332 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>348247</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>90412</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ANGEL</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ELIZALDE</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>6674201956</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>27-01-2001</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>ANGELELIZALDE001@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:50:39</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:31:51</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>26050522924250006040</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>ABIGAIL AHUMADA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>Hector Noe Espinoza Ramirez</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>347909</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>90074</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>HECTOR ABEL</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VALEZUELA </t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>6674085202</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>LOMAS DE SAN ISIDRO</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>04-09-2011</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>HECOR.VALENZUELA.HERNANDEZ.2011@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:50:24</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:55:34</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:54:49</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>26050522820290005675</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>348064</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>90229</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ERIK BLADIMIR</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ZARABIA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>MERAZ</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>6674352372</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>22 DE DIC</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>23-02-1999</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>ERIKBLADIMIR@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>03-03-2026 14:36:16</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>03-03-2026 14:40:34</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>03-03-2026 14:39:53</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>26050522842200005742</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>Carlos Aurelio Monzon Ayala</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>348151</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>90316</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>SAN ISIDRO CUL</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>JULIO CESAR</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>ELIZALDE</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>HERNANDEZ</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>6673418071</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>PERISUR</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Masculino</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>25-02-1990</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>JULIOCESAR1@GMAIL.COM</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>03-03-2026 17:10:14</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Culiacan pago</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>No Forzoso</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>RECURRENTE $649 LE</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>649</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>03-03-2026 17:17:25</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>03-03-2026 17:16:26</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>26050522849920005776</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr">
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
         <is>
           <t>649</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>348454</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>90619</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NICOLAS FRANSUE</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PIZARRO</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>MONZON</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>6674366033</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>23-05-2009</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>MONZONN136@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:07:34</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:09:17</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>26050522884540005897</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>Carlos Aurelio Monzon Ayala</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>348623</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>90788</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CECILIA ABIGAIL</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>DELGADO</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>CHAIDEZ</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>6674050741</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>DE LAS FUENTES 5078</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>01-01-1991</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>JORGILLO_2707@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>05-03-2026 07:48:29</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>17-03-2026 08:59:06</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>17-03-2026 08:58:18</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>26050523247640007043</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>Carmen Michel Navarrete  Nevarez</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Gilberto Tavarez Soto</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>348217</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>90382</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LORETO GUADALUPE</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>SOLORIO</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>DELGADO</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>6673737751</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>29-01-1991</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>LUPITA_SOLORIO11@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:12:53</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:34:22</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>26050522921380006023</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>Carlos Aurelio Monzon Ayala</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>349034</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>91199</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BERENICE </t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>FUENTES</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>AGUILAR</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>6676693845</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ORIV.MONTANESA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>25-01-1992</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>MARIAAGUILAR2501@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>06-03-2026 19:18:53</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>06-03-2026 19:24:57</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>06-03-2026 19:22:43</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>26050522960420006170</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>348334</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>90499</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>KARLA FABIOLA</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>YEE</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>DIAZ</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>6673209514</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>FRAY SERVANDO 4369</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>29-10-1989</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>KARLAYEE89@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>04-03-2026 07:40:53</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>06-03-2026 08:02:02</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>06-03-2026 08:00:48</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>26050522943920006105</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>Carmen Michel Navarrete  Nevarez</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Gilberto Tavarez Soto</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>349530</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>91695</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>BELEN</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>BELTRAN</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>FELIX</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>6671012774</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>29-11-2002</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>BELEN727FELIX@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:04:00</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:05:59</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>26050523016130006306</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>349299</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>91464</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CARLA PAOLA</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>CORTES</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>6673214474</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>28-01-2007</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>PAYOLA123LOPEZCORTES@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>09-03-2026 07:08:08</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>09-03-2026 07:10:38</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>26050522998600006260</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>349989</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>92154</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LUIS ALFONSO</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ANGULO</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>MADRID</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6679964224</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>EL PALMAR</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>26-08-1999</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>LUISMADRIDL@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:23:11</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>17-03-2026 20:16:10</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>17-03-2026 20:15:51</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>26050523272870007133</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>Carlos Aurelio Monzon Ayala</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>350518</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>92682</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>MARTHA KARMINA</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>SILLAS</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>6673460785</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>12-05-1980</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>MARTHAHERNANDEZ580@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>13-03-2026 09:21:22</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>13-03-2026 09:24:32</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>12-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>26050523148910006814</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>349528</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>91693</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LESLIE VANESSA</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HAUCHBAUM </t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>MENDOZA</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>6675735838</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>13-07-2011</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>ANAC.M99@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:01:58</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>11-03-2026 14:55:25</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>10-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>26050523090780006572</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>349626</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>91791</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>KARLA MARIANA</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>MORENO</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>DIAZ</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>6674209736</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ALTURAS</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>10-10-1999</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>KARLAMARIANA34@OUTLOOK.ES</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:48:00</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:58:38</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:58:03</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>26050523025040006344</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>349975</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>92140</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CARLOS VENTURA</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LUNA</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6671532654</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>12-02-2008</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>CARLOS81811202@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:03:46</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>11-03-2026 18:47:31</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>10-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>26050523100340006632</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>349800</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>91965</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>ROBLES</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6624640894</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CIRCUITO KHALAJARI</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>10-10-1996</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>OR18@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>10-03-2026 10:16:41</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>10-03-2026 10:23:48</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>10-03-2026 10:23:17</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>26050523048010006419</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>Gilberto Tavarez Soto</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>350153</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>92318</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ABDIEL AARON</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ACOSTA</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>PLAZOLA</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6672327097</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>MINA TOYOLTITA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>21-05-2025</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>AARONPLAZOLA919@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>11-03-2026 16:27:44</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>16-03-2026 13:14:35</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>16-03-2026 13:13:10</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>26050523221030006970</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>351347</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>93511</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>OSCAR ARNULFO</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>GUICHO</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>6671058225</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>VILLA BONITA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>19-07-1998</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>OSCARGT_19@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:38:50</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:43:17</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:42:46</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>26050523233760007001</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>350438</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>92602</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOSE JUAN </t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>CANALES</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>GASPAR</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>6671421714</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>ADOLFO RUIZ CORTINEZ</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>13-01-2003</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>CANALES13.135@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>12-03-2026 18:42:55</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>16-03-2026 20:24:39</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>16-03-2026 20:15:09</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>26050523235020007006</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>350186</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>92351</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ERIKA AIDE</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>FAVELA</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>BOJORQUEZ</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>6673959762</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>ADOLFO LOPEZ MATEOS</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>15-06-1975</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>ERIKA.FAVELA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>11-03-2026 18:04:25</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>17-03-2026 18:47:07</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>17-03-2026 18:45:50</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>26050523267120007113</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>351413</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>93577</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SERGIO LUIS</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ARAUJO</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>6673213267</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>08-09-1962</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>SERGIOARAUJO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>17-03-2026 07:17:20</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>17-03-2026 07:21:06</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>26050523244960007038</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>351049</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>93213</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ALAN YAMIR</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>SALOMON</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>CASTRO</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>6674763444</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>03-04-2002</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>CASTROALAN@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>16-03-2026 10:03:56</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>16-03-2026 10:08:23</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>16-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>26050523213950006951</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>Carmen Michel Navarrete  Nevarez</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>351708</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>93872</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DIANA ABIGAIL</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>QUINTERO</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>CERVANTES</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>6672445146</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>29 SEP</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>29-10-1993</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>DA_29_6@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>17-03-2026 20:10:14</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>17-03-2026 20:19:50</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>17-03-2026 20:19:12</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>26050523273160007135</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Carlos Aurelio Monzon Ayala</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>352019</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>94183</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>PERLA ARACELY</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>SILVA</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>URIAS</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>6673026624</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>ADOLFO LOPEZ MATEOS</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>22-06-1993</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>PERLA_SILVA98@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>18-03-2026 21:17:34</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>18-03-2026 21:25:17</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>18-03-2026 21:23:59</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>26050523311190007263</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>351771</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>93935</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>JESUS YAHIR</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>MAGDALENO PACHECO</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>MAGDALENO PACHECO</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>6671634412</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Mina san jose de gracia 596</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>31-12-9999</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>jesusyahirpacheco@gmail.com</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>18-03-2026 09:10:54</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>18-03-2026 09:10:55</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>26050523286830007180</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>351808</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>93972</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VALERIA</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>SARACCO</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>6677679943</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>XOCHIAPA 1608-2</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>25-05-1990</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>VSARACCOM@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>18-03-2026 13:01:36</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>18-03-2026 13:09:05</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>18-03-2026 13:07:37</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>26050523290710007195</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>Carlos Aurelio Monzon Ayala</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>351627</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>93791</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>JAZMIN ROSARIO</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>FELIX</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>ACOSTA</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>6672273548</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>27-07-1994</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>JAZMIN_2794@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>17-03-2026 18:15:38</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>19-03-2026 06:58:57</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>26050523321050007281</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>MARIA LUISA  VILLALOBOS VALDEZ</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>Carlos Aurelio Monzon Ayala</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>351460</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>93624</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>MIRIAM ITZEL</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>SARABIA</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>RUBIO</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>6673461412</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>06-07-1992</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>MIRIAMSARABIAA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>17-03-2026 10:57:09</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>17-03-2026 11:01:02</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>26050523250050007051</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>Gilberto Tavarez Soto</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>351709</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>93873</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>DULCE ROCIO</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>QUINTERO</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>CERVANTES</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>6675817185</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>PROGRESO</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>07-01-1995</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>QUINCERDULCE@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>17-03-2026 20:12:32</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>17-03-2026 20:21:19</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>17-03-2026 20:21:02</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>26050523273270007136</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>Carlos Aurelio Monzon Ayala</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>352015</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>94179</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>VELAZQUEZ</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>6671322215</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>02-01-2008</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>CEDU3693@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>18-03-2026 20:58:37</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>18-03-2026 21:00:40</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>17-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>26050523310650007261</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>352160</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>94324</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>CARLOS AMADO</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>VALDEZ</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>ACOSTA</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>6677480774</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>17-12-1988</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>DEGOR_PIS@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>19-03-2026 17:43:16</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>19-03-2026 17:45:33</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>26050523335890007337</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>Carlos Aurelio Monzon Ayala</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
